--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hajibashi.Saba\Desktop\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81199750-C776-4F57-B6C8-9BE5A60C92EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4C2157-2824-4D0F-BA84-EB5DEE09B216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="392">
   <si>
     <t>Entity Category</t>
   </si>
@@ -964,13 +964,250 @@
   </si>
   <si>
     <t>Comments, narratives, and supporting information</t>
+  </si>
+  <si>
+    <t>OFAC-SDN TYPE</t>
+  </si>
+  <si>
+    <t>OFAC-SDN</t>
+  </si>
+  <si>
+    <t>generalInfo.identityId</t>
+  </si>
+  <si>
+    <t>generalInfo.entityType.text</t>
+  </si>
+  <si>
+    <t>features.feature[].type.text | Gender | features.feature[].value</t>
+  </si>
+  <si>
+    <t>sanctionsLists.sanctionsList.datePublished</t>
+  </si>
+  <si>
+    <t>"OFAC-SDN"</t>
+  </si>
+  <si>
+    <t>"OFAC"</t>
+  </si>
+  <si>
+    <t>"https://ofac.treasury.gov/specially-designated-nationals-list-data-formats-data-schemas"</t>
+  </si>
+  <si>
+    <t>sanctionsLists.sanctionsList.text</t>
+  </si>
+  <si>
+    <t>names.name[]</t>
+  </si>
+  <si>
+    <t>isPrimary | true | "Primary"</t>
+  </si>
+  <si>
+    <t>isPrimary | true | translations.translation.formattedFullName</t>
+  </si>
+  <si>
+    <t>isPrimary | true | translations.translation.formattedFirstName</t>
+  </si>
+  <si>
+    <t>isPrimary | true | translations.translation.formattedLastName</t>
+  </si>
+  <si>
+    <t>isPrimary | true | translations.translation.script.text</t>
+  </si>
+  <si>
+    <t>isPrimary | true | isLowQuality</t>
+  </si>
+  <si>
+    <t>features.feature[]</t>
+  </si>
+  <si>
+    <t>type.text | Birthdate | valueDate.fromDateBegin</t>
+  </si>
+  <si>
+    <t>type.text | Birthdate | "Birthdate"</t>
+  </si>
+  <si>
+    <t>type.text | Birthdate | valueDate.isApproximate</t>
+  </si>
+  <si>
+    <t>type.text | Birthdate | value</t>
+  </si>
+  <si>
+    <t>type.text | Place of Birth | value</t>
+  </si>
+  <si>
+    <t>type.text | Nationality Country | "Nationality" OR type.text | Citizenship Country | "Citizenship"</t>
+  </si>
+  <si>
+    <t>type.text | Nationality Country, Citizenship Country | value</t>
+  </si>
+  <si>
+    <t>identityDocuments.identityDocument[]</t>
+  </si>
+  <si>
+    <t>type.text</t>
+  </si>
+  <si>
+    <t>documentNumber</t>
+  </si>
+  <si>
+    <t>expirationDate.fromDateBegin</t>
+  </si>
+  <si>
+    <t>issueDate.fromDateBegin</t>
+  </si>
+  <si>
+    <t>issuingCountry.text</t>
+  </si>
+  <si>
+    <t>isPrimary | false | aliasType.text</t>
+  </si>
+  <si>
+    <t>isPrimary | false | translations.translation.formattedFullName</t>
+  </si>
+  <si>
+    <t>isPrimary | false | isLowQuality</t>
+  </si>
+  <si>
+    <t>sanctionsPrograms.sanctionsProgram[]</t>
+  </si>
+  <si>
+    <t>"sanctions program"</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>"U.S. Department of the Treasury - OFAC"</t>
+  </si>
+  <si>
+    <t>legalAuthorities.legalAuthority.text</t>
+  </si>
+  <si>
+    <t>generalInfo.title</t>
+  </si>
+  <si>
+    <t>addresses.address[]</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].type.text | ADDRESS1 | translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].type.text | ADDRESS2 | translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].type.text | ADDRESS3 | translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].type.text | CITY | translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>country.text</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].type.text | STATE/PROVINCE | translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>translations.translation.addressParts.addressPart[].type.text | POSTAL CODE | translations.translation.addressParts.addressPart[].value</t>
+  </si>
+  <si>
+    <t>relationships.relationship[]</t>
+  </si>
+  <si>
+    <t>relatedEntity.entityId</t>
+  </si>
+  <si>
+    <t>relatedEntity.text</t>
+  </si>
+  <si>
+    <t>quality.text</t>
+  </si>
+  <si>
+    <t>constant*constant</t>
+  </si>
+  <si>
+    <t>"remarks"*"additional info"</t>
+  </si>
+  <si>
+    <t>path*conditional_path</t>
+  </si>
+  <si>
+    <t>generalInfo.remarks*features.feature[].type.text | Additional Sanctions Information -, Secondary sanctions risk:, Executive Order 13846 information:, Transactions Prohibited For Persons Owned or Controlled By U.S. Financial Institutions: | features.feature[].value</t>
+  </si>
+  <si>
+    <t>sanctionsTypes.sanctionsType[]</t>
+  </si>
+  <si>
+    <t>"Active"</t>
+  </si>
+  <si>
+    <t>type.text | Organization Established Date | valueDate.fromDateBegin</t>
+  </si>
+  <si>
+    <t>type.text | Organization Established Date | "Organization Established Date"</t>
+  </si>
+  <si>
+    <t>type.text | Organization Established Date | valueDate.isApproximate</t>
+  </si>
+  <si>
+    <t>type.text | Organization Established Date | value</t>
+  </si>
+  <si>
+    <t>type.text | Nationality of Registration | "Registration"</t>
+  </si>
+  <si>
+    <t>type.text | Nationality of Registration | value</t>
+  </si>
+  <si>
+    <t>type.text | Website, Email Address, Phone Number, SWIFT/BIC | type.text</t>
+  </si>
+  <si>
+    <t>type.text | Website, Email Address, Phone Number, SWIFT/BIC | value</t>
+  </si>
+  <si>
+    <t>type.text | Organization Type:, Target Type | type.text</t>
+  </si>
+  <si>
+    <t>type.text | Organization Type:, Target Type | value</t>
+  </si>
+  <si>
+    <t>type.text | Vessel Year of Build | value</t>
+  </si>
+  <si>
+    <t>type.text | Vessel Year of Build | "Vessel Year of Build"</t>
+  </si>
+  <si>
+    <t>type.text | Vessel Flag, Former Vessel Flag, Other Vessel Flag | type.text</t>
+  </si>
+  <si>
+    <t>type.text | Vessel Flag, Former Vessel Flag, Other Vessel Flag | value</t>
+  </si>
+  <si>
+    <t>features.feature[].type.text | Vessel Flag | features.feature[].value</t>
+  </si>
+  <si>
+    <t>features.feature[].type.text | VESSEL TYPE, Other Vessel Type | features.feature[].value</t>
+  </si>
+  <si>
+    <t>features.feature[].type.text | Vessel Year of Build | features.feature[].value</t>
+  </si>
+  <si>
+    <t>features.feature[].type.text | Vessel Tonnage, Vessel Gross Registered Tonnage | features.feature[].value</t>
+  </si>
+  <si>
+    <t>sanctionsTypes.sanctionsType.text</t>
+  </si>
+  <si>
+    <t>features.feature[].type.text | Secondary sanctions risk:, Additional Sanctions Information - | features.feature[].value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,6 +1226,14 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1044,10 +1289,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1067,8 +1313,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1356,9 +1606,11 @@
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="55.81640625" customWidth="1"/>
     <col min="7" max="7" width="33.7265625" customWidth="1"/>
+    <col min="8" max="8" width="20.36328125" customWidth="1"/>
+    <col min="9" max="9" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1380,8 +1632,12 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -1401,7 +1657,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1421,8 +1677,12 @@
       <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1442,7 +1702,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1462,8 +1722,12 @@
       <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="H3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1483,7 +1747,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1499,8 +1763,12 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="H4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1520,7 +1788,7 @@
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1536,8 +1804,12 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="H5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1655,8 +1927,12 @@
       <c r="G8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1676,7 +1952,7 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1698,8 +1974,12 @@
       <c r="G9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="H9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1741,8 +2021,12 @@
       <c r="G10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="H10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1762,7 +2046,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
@@ -1784,8 +2068,12 @@
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1805,7 +2093,7 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1827,8 +2115,12 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="H12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1848,7 +2140,7 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
@@ -1870,8 +2162,12 @@
       <c r="G13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="H13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1891,7 +2187,7 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1913,8 +2209,12 @@
       <c r="G14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="H14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1934,7 +2234,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1956,8 +2256,12 @@
       <c r="G15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="H15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1977,7 +2281,7 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
@@ -1999,8 +2303,12 @@
       <c r="G16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="H16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -2020,7 +2328,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
@@ -2038,8 +2346,12 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="H17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -2098,7 +2410,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
@@ -2116,8 +2428,12 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="H19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2137,7 +2453,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2155,8 +2471,12 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="H20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2176,7 +2496,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2194,8 +2514,12 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="H21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -2722,7 +3046,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
@@ -2740,8 +3064,12 @@
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="H35" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2839,7 +3167,7 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>5</v>
       </c>
@@ -2857,8 +3185,12 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
+      <c r="H38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -2878,7 +3210,7 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
         <v>5</v>
       </c>
@@ -2896,8 +3228,12 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="H39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>332</v>
+      </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -2917,7 +3253,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
         <v>5</v>
       </c>
@@ -2935,8 +3271,12 @@
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="H40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>333</v>
+      </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -2956,7 +3296,7 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2978,8 +3318,12 @@
       <c r="G41" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="H41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>334</v>
+      </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -2999,7 +3343,7 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3361,12 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="H42" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3038,7 +3386,7 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3060,8 +3408,12 @@
       <c r="G43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="H43" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>335</v>
+      </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -3120,7 +3472,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3138,8 +3490,12 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="H45" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -3159,7 +3515,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3181,8 +3537,12 @@
       <c r="G46" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="H46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>336</v>
+      </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -3202,7 +3562,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3224,8 +3584,12 @@
       <c r="G47" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="H47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>337</v>
+      </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -3284,7 +3648,7 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3302,8 +3666,12 @@
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+      <c r="H49" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3323,7 +3691,7 @@
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
     </row>
-    <row r="50" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3" t="s">
         <v>5</v>
       </c>
@@ -3345,8 +3713,12 @@
       <c r="G50" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
+      <c r="H50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3388,8 +3760,12 @@
       <c r="G51" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
+      <c r="H51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -3409,7 +3785,7 @@
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
     </row>
-    <row r="52" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3427,8 +3803,12 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
+      <c r="H52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -3448,7 +3828,7 @@
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
     </row>
-    <row r="53" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
         <v>5</v>
       </c>
@@ -3466,8 +3846,12 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
+      <c r="H53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3487,7 +3871,7 @@
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
     </row>
-    <row r="54" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3505,8 +3889,12 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
+      <c r="H54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -3544,8 +3932,12 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
+      <c r="H55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -3565,7 +3957,7 @@
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
     </row>
-    <row r="56" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3" t="s">
         <v>5</v>
       </c>
@@ -3587,8 +3979,12 @@
       <c r="G56" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
+      <c r="H56" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -3608,7 +4004,7 @@
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
     </row>
-    <row r="57" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3630,8 +4026,12 @@
       <c r="G57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
+      <c r="H57" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>344</v>
+      </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -3651,7 +4051,7 @@
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3673,8 +4073,12 @@
       <c r="G58" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
+      <c r="H58" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>345</v>
+      </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
@@ -3694,7 +4098,7 @@
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3716,8 +4120,12 @@
       <c r="G59" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
+      <c r="H59" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -3737,7 +4145,7 @@
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3755,8 +4163,12 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
+      <c r="H60" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -3776,7 +4188,7 @@
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3" t="s">
         <v>5</v>
       </c>
@@ -3798,8 +4210,12 @@
       <c r="G61" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
+      <c r="H61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -3819,7 +4235,7 @@
       <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
     </row>
-    <row r="62" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3841,8 +4257,12 @@
       <c r="G62" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
+      <c r="H62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -3862,7 +4282,7 @@
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
     </row>
-    <row r="63" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3" t="s">
         <v>5</v>
       </c>
@@ -3884,8 +4304,12 @@
       <c r="G63" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
+      <c r="H63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
@@ -3927,8 +4351,12 @@
       <c r="G64" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
+      <c r="H64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -3987,7 +4415,7 @@
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4005,8 +4433,12 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
+      <c r="H66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -4065,7 +4497,7 @@
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
         <v>5</v>
       </c>
@@ -4083,8 +4515,12 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
+      <c r="H68" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -4104,7 +4540,7 @@
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
     </row>
-    <row r="69" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
         <v>5</v>
       </c>
@@ -4126,8 +4562,12 @@
       <c r="G69" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
+      <c r="H69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4147,7 +4587,7 @@
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
         <v>5</v>
       </c>
@@ -4165,8 +4605,12 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
+      <c r="H70" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -4186,7 +4630,7 @@
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
         <v>5</v>
       </c>
@@ -4204,8 +4648,12 @@
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
+      <c r="H71" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
@@ -4225,7 +4673,7 @@
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
     </row>
-    <row r="72" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4243,8 +4691,12 @@
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
+      <c r="H72" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
@@ -4264,7 +4716,7 @@
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:27" ht="218" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
         <v>5</v>
       </c>
@@ -4282,8 +4734,12 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
+      <c r="H73" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
@@ -4303,7 +4759,7 @@
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
     </row>
-    <row r="74" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3" t="s">
         <v>5</v>
       </c>
@@ -4321,8 +4777,12 @@
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
+      <c r="H74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
@@ -4342,7 +4802,7 @@
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="75" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:27" ht="247" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3" t="s">
         <v>5</v>
       </c>
@@ -4360,8 +4820,12 @@
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
+      <c r="H75" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
@@ -4381,7 +4845,7 @@
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
     </row>
-    <row r="76" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4399,8 +4863,12 @@
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
+      <c r="H76" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
@@ -4459,7 +4927,7 @@
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
     </row>
-    <row r="78" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3" t="s">
         <v>5</v>
       </c>
@@ -4477,8 +4945,12 @@
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
+      <c r="H78" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
@@ -4516,8 +4988,12 @@
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
+      <c r="H79" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
@@ -4537,7 +5013,7 @@
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
     </row>
-    <row r="80" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3" t="s">
         <v>5</v>
       </c>
@@ -4555,8 +5031,12 @@
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
+      <c r="H80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
@@ -4576,7 +5056,7 @@
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
     </row>
-    <row r="81" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3" t="s">
         <v>5</v>
       </c>
@@ -4594,8 +5074,12 @@
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="H81" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
@@ -4711,8 +5195,12 @@
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
+      <c r="H84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
@@ -4771,7 +5259,7 @@
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
     </row>
-    <row r="86" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3" t="s">
         <v>5</v>
       </c>
@@ -4793,8 +5281,12 @@
       <c r="G86" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
+      <c r="H86" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
@@ -4814,7 +5306,7 @@
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
     </row>
-    <row r="87" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:27" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="3" t="s">
         <v>5</v>
       </c>
@@ -4836,8 +5328,12 @@
       <c r="G87" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
+      <c r="H87" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>369</v>
+      </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
@@ -4857,7 +5353,7 @@
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
     </row>
-    <row r="88" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
         <v>5</v>
       </c>
@@ -4875,8 +5371,12 @@
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
+      <c r="H88" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
@@ -4896,7 +5396,7 @@
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
     </row>
-    <row r="89" spans="1:27" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3" t="s">
         <v>5</v>
       </c>
@@ -4918,8 +5418,12 @@
       <c r="G89" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
+      <c r="H89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
@@ -4939,7 +5443,7 @@
       <c r="Z89" s="2"/>
       <c r="AA89" s="2"/>
     </row>
-    <row r="90" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3" t="s">
         <v>5</v>
       </c>
@@ -4961,8 +5465,12 @@
       <c r="G90" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
+      <c r="H90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
@@ -5021,7 +5529,7 @@
       <c r="Z91" s="2"/>
       <c r="AA91" s="2"/>
     </row>
-    <row r="92" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
         <v>5</v>
       </c>
@@ -5043,8 +5551,12 @@
       <c r="G92" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
+      <c r="H92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>371</v>
+      </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
@@ -5064,7 +5576,7 @@
       <c r="Z92" s="2"/>
       <c r="AA92" s="2"/>
     </row>
-    <row r="93" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3" t="s">
         <v>5</v>
       </c>
@@ -5082,8 +5594,12 @@
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
+      <c r="H93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
@@ -5103,7 +5619,7 @@
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
     </row>
-    <row r="94" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
         <v>142</v>
       </c>
@@ -5123,8 +5639,12 @@
       <c r="G94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
+      <c r="H94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
@@ -5144,7 +5664,7 @@
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
     </row>
-    <row r="95" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3" t="s">
         <v>142</v>
       </c>
@@ -5164,8 +5684,12 @@
       <c r="G95" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
+      <c r="H95" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
@@ -5185,7 +5709,7 @@
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
     </row>
-    <row r="96" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3" t="s">
         <v>142</v>
       </c>
@@ -5201,8 +5725,12 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
+      <c r="H96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
@@ -5320,8 +5848,12 @@
       <c r="G99" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
+      <c r="H99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
@@ -5341,7 +5873,7 @@
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
     </row>
-    <row r="100" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3" t="s">
         <v>142</v>
       </c>
@@ -5363,8 +5895,12 @@
       <c r="G100" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
+      <c r="H100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
@@ -5406,8 +5942,12 @@
       <c r="G101" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
@@ -5427,7 +5967,7 @@
       <c r="Z101" s="2"/>
       <c r="AA101" s="2"/>
     </row>
-    <row r="102" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
         <v>142</v>
       </c>
@@ -5449,8 +5989,12 @@
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
+      <c r="H102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
@@ -5470,7 +6014,7 @@
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
     </row>
-    <row r="103" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
         <v>142</v>
       </c>
@@ -5492,8 +6036,12 @@
       <c r="G103" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
+      <c r="H103" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
@@ -5513,7 +6061,7 @@
       <c r="Z103" s="2"/>
       <c r="AA103" s="2"/>
     </row>
-    <row r="104" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
         <v>142</v>
       </c>
@@ -5535,8 +6083,12 @@
       <c r="G104" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
+      <c r="H104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
@@ -5578,8 +6130,12 @@
       <c r="G105" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
+      <c r="H105" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
@@ -5599,7 +6155,7 @@
       <c r="Z105" s="2"/>
       <c r="AA105" s="2"/>
     </row>
-    <row r="106" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
         <v>142</v>
       </c>
@@ -5621,8 +6177,12 @@
       <c r="G106" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
+      <c r="H106" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
@@ -5642,7 +6202,7 @@
       <c r="Z106" s="2"/>
       <c r="AA106" s="2"/>
     </row>
-    <row r="107" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
         <v>142</v>
       </c>
@@ -5664,8 +6224,12 @@
       <c r="G107" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
+      <c r="H107" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
@@ -5685,7 +6249,7 @@
       <c r="Z107" s="2"/>
       <c r="AA107" s="2"/>
     </row>
-    <row r="108" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
         <v>142</v>
       </c>
@@ -5703,8 +6267,12 @@
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
+      <c r="H108" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
@@ -5724,7 +6292,7 @@
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
     </row>
-    <row r="109" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
         <v>142</v>
       </c>
@@ -5746,8 +6314,12 @@
       <c r="G109" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
+      <c r="H109" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
@@ -5767,7 +6339,7 @@
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
     </row>
-    <row r="110" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
         <v>142</v>
       </c>
@@ -5785,8 +6357,12 @@
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
+      <c r="H110" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
@@ -5884,7 +6460,7 @@
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
     </row>
-    <row r="113" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
         <v>142</v>
       </c>
@@ -5902,8 +6478,12 @@
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
+      <c r="H113" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
@@ -5923,7 +6503,7 @@
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
     </row>
-    <row r="114" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
         <v>142</v>
       </c>
@@ -5941,8 +6521,12 @@
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
+      <c r="H114" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
@@ -5962,7 +6546,7 @@
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
     </row>
-    <row r="115" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
         <v>142</v>
       </c>
@@ -5980,8 +6564,12 @@
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
+      <c r="H115" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>374</v>
+      </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
@@ -6001,7 +6589,7 @@
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
     </row>
-    <row r="116" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
         <v>142</v>
       </c>
@@ -6019,8 +6607,12 @@
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
+      <c r="H116" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>375</v>
+      </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
@@ -6058,8 +6650,12 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
+      <c r="H117" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
@@ -6079,7 +6675,7 @@
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
     </row>
-    <row r="118" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
         <v>142</v>
       </c>
@@ -6097,8 +6693,12 @@
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
+      <c r="H118" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
@@ -6118,7 +6718,7 @@
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
     </row>
-    <row r="119" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
         <v>142</v>
       </c>
@@ -6136,8 +6736,12 @@
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
+      <c r="H119" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>377</v>
+      </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
@@ -6196,7 +6800,7 @@
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
     </row>
-    <row r="121" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
         <v>142</v>
       </c>
@@ -6214,8 +6818,12 @@
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
+      <c r="H121" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
@@ -6235,7 +6843,7 @@
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
     </row>
-    <row r="122" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
         <v>142</v>
       </c>
@@ -6257,8 +6865,12 @@
       <c r="G122" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H122" s="2"/>
-      <c r="I122" s="2"/>
+      <c r="H122" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
@@ -6278,7 +6890,7 @@
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
     </row>
-    <row r="123" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
         <v>142</v>
       </c>
@@ -6296,8 +6908,12 @@
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="2"/>
+      <c r="H123" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
@@ -6317,7 +6933,7 @@
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
     </row>
-    <row r="124" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
         <v>142</v>
       </c>
@@ -6335,8 +6951,12 @@
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-      <c r="H124" s="2"/>
-      <c r="I124" s="2"/>
+      <c r="H124" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
@@ -6356,7 +6976,7 @@
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
     </row>
-    <row r="125" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
         <v>142</v>
       </c>
@@ -6374,8 +6994,12 @@
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
+      <c r="H125" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
@@ -6395,7 +7019,7 @@
       <c r="Z125" s="2"/>
       <c r="AA125" s="2"/>
     </row>
-    <row r="126" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:27" ht="218" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
         <v>142</v>
       </c>
@@ -6413,8 +7037,12 @@
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="2"/>
+      <c r="H126" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
@@ -6434,7 +7062,7 @@
       <c r="Z126" s="2"/>
       <c r="AA126" s="2"/>
     </row>
-    <row r="127" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:27" ht="247" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
         <v>142</v>
       </c>
@@ -6452,8 +7080,12 @@
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
+      <c r="H127" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
@@ -6473,7 +7105,7 @@
       <c r="Z127" s="2"/>
       <c r="AA127" s="2"/>
     </row>
-    <row r="128" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
         <v>142</v>
       </c>
@@ -6491,8 +7123,12 @@
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
-      <c r="I128" s="2"/>
+      <c r="H128" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
@@ -6512,7 +7148,7 @@
       <c r="Z128" s="2"/>
       <c r="AA128" s="2"/>
     </row>
-    <row r="129" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
         <v>142</v>
       </c>
@@ -6530,8 +7166,12 @@
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
+      <c r="H129" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
@@ -6612,8 +7252,12 @@
       <c r="G131" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
+      <c r="H131" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
@@ -6633,7 +7277,7 @@
       <c r="Z131" s="2"/>
       <c r="AA131" s="2"/>
     </row>
-    <row r="132" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
         <v>142</v>
       </c>
@@ -6655,8 +7299,12 @@
       <c r="G132" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
+      <c r="H132" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>344</v>
+      </c>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
@@ -6676,7 +7324,7 @@
       <c r="Z132" s="2"/>
       <c r="AA132" s="2"/>
     </row>
-    <row r="133" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
         <v>142</v>
       </c>
@@ -6698,8 +7346,12 @@
       <c r="G133" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
+      <c r="H133" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>345</v>
+      </c>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
@@ -6719,7 +7371,7 @@
       <c r="Z133" s="2"/>
       <c r="AA133" s="2"/>
     </row>
-    <row r="134" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
         <v>142</v>
       </c>
@@ -6741,8 +7393,12 @@
       <c r="G134" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
+      <c r="H134" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
@@ -6762,7 +7418,7 @@
       <c r="Z134" s="2"/>
       <c r="AA134" s="2"/>
     </row>
-    <row r="135" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
         <v>142</v>
       </c>
@@ -6780,8 +7436,12 @@
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
+      <c r="H135" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
@@ -6801,7 +7461,7 @@
       <c r="Z135" s="2"/>
       <c r="AA135" s="2"/>
     </row>
-    <row r="136" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
         <v>142</v>
       </c>
@@ -6823,8 +7483,12 @@
       <c r="G136" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
+      <c r="H136" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
@@ -6844,7 +7508,7 @@
       <c r="Z136" s="2"/>
       <c r="AA136" s="2"/>
     </row>
-    <row r="137" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
         <v>142</v>
       </c>
@@ -6866,8 +7530,12 @@
       <c r="G137" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2"/>
+      <c r="H137" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
@@ -6887,7 +7555,7 @@
       <c r="Z137" s="2"/>
       <c r="AA137" s="2"/>
     </row>
-    <row r="138" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
         <v>142</v>
       </c>
@@ -6909,8 +7577,12 @@
       <c r="G138" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
+      <c r="H138" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
@@ -6952,8 +7624,12 @@
       <c r="G139" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
+      <c r="H139" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
@@ -6973,7 +7649,7 @@
       <c r="Z139" s="2"/>
       <c r="AA139" s="2"/>
     </row>
-    <row r="140" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
         <v>142</v>
       </c>
@@ -6991,8 +7667,12 @@
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
+      <c r="H140" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
@@ -7030,8 +7710,12 @@
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-      <c r="H141" s="2"/>
-      <c r="I141" s="2"/>
+      <c r="H141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
@@ -7051,7 +7735,7 @@
       <c r="Z141" s="2"/>
       <c r="AA141" s="2"/>
     </row>
-    <row r="142" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
         <v>142</v>
       </c>
@@ -7069,8 +7753,12 @@
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
+      <c r="H142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
@@ -7090,7 +7778,7 @@
       <c r="Z142" s="2"/>
       <c r="AA142" s="2"/>
     </row>
-    <row r="143" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
         <v>142</v>
       </c>
@@ -7108,8 +7796,12 @@
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-      <c r="H143" s="2"/>
-      <c r="I143" s="2"/>
+      <c r="H143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
@@ -7225,8 +7917,12 @@
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-      <c r="H146" s="2"/>
-      <c r="I146" s="2"/>
+      <c r="H146" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
@@ -7246,7 +7942,7 @@
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
     </row>
-    <row r="147" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3" t="s">
         <v>142</v>
       </c>
@@ -7264,8 +7960,12 @@
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-      <c r="H147" s="2"/>
-      <c r="I147" s="2"/>
+      <c r="H147" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
@@ -7285,7 +7985,7 @@
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
     </row>
-    <row r="148" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3" t="s">
         <v>142</v>
       </c>
@@ -7307,8 +8007,12 @@
       <c r="G148" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H148" s="2"/>
-      <c r="I148" s="2"/>
+      <c r="H148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
@@ -7350,8 +8054,12 @@
       <c r="G149" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H149" s="2"/>
-      <c r="I149" s="2"/>
+      <c r="H149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
@@ -7371,7 +8079,7 @@
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
     </row>
-    <row r="150" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
         <v>142</v>
       </c>
@@ -7389,8 +8097,12 @@
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
-      <c r="I150" s="2"/>
+      <c r="H150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
@@ -7410,7 +8122,7 @@
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
     </row>
-    <row r="151" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
         <v>142</v>
       </c>
@@ -7428,8 +8140,12 @@
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-      <c r="H151" s="2"/>
-      <c r="I151" s="2"/>
+      <c r="H151" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
@@ -7449,7 +8165,7 @@
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
     </row>
-    <row r="152" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
         <v>142</v>
       </c>
@@ -7467,8 +8183,12 @@
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-      <c r="H152" s="2"/>
-      <c r="I152" s="2"/>
+      <c r="H152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
@@ -7506,8 +8226,12 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-      <c r="H153" s="2"/>
-      <c r="I153" s="2"/>
+      <c r="H153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
@@ -7545,8 +8269,12 @@
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
-      <c r="I154" s="2"/>
+      <c r="H154" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
@@ -7566,7 +8294,7 @@
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
     </row>
-    <row r="155" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
         <v>142</v>
       </c>
@@ -7584,8 +8312,12 @@
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
-      <c r="H155" s="2"/>
-      <c r="I155" s="2"/>
+      <c r="H155" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
@@ -7605,7 +8337,7 @@
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
     </row>
-    <row r="156" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
         <v>142</v>
       </c>
@@ -7623,8 +8355,12 @@
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="2"/>
-      <c r="I156" s="2"/>
+      <c r="H156" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
@@ -7701,8 +8437,12 @@
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="2"/>
-      <c r="I158" s="2"/>
+      <c r="H158" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
@@ -7722,7 +8462,7 @@
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
     </row>
-    <row r="159" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
         <v>142</v>
       </c>
@@ -7740,8 +8480,12 @@
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
-      <c r="H159" s="2"/>
-      <c r="I159" s="2"/>
+      <c r="H159" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
@@ -7761,7 +8505,7 @@
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
     </row>
-    <row r="160" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
         <v>142</v>
       </c>
@@ -7783,8 +8527,12 @@
       <c r="G160" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H160" s="2"/>
-      <c r="I160" s="2"/>
+      <c r="H160" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>381</v>
+      </c>
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
@@ -7843,7 +8591,7 @@
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
     </row>
-    <row r="162" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
         <v>142</v>
       </c>
@@ -7861,8 +8609,12 @@
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-      <c r="H162" s="2"/>
-      <c r="I162" s="2"/>
+      <c r="H162" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
@@ -7882,7 +8634,7 @@
       <c r="Z162" s="2"/>
       <c r="AA162" s="2"/>
     </row>
-    <row r="163" spans="1:27" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
         <v>142</v>
       </c>
@@ -7904,8 +8656,12 @@
       <c r="G163" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H163" s="2"/>
-      <c r="I163" s="2"/>
+      <c r="H163" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
@@ -7925,7 +8681,7 @@
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
     </row>
-    <row r="164" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
         <v>142</v>
       </c>
@@ -7947,8 +8703,12 @@
       <c r="G164" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H164" s="2"/>
-      <c r="I164" s="2"/>
+      <c r="H164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
@@ -8007,7 +8767,7 @@
       <c r="Z165" s="2"/>
       <c r="AA165" s="2"/>
     </row>
-    <row r="166" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3" t="s">
         <v>142</v>
       </c>
@@ -8029,8 +8789,12 @@
       <c r="G166" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H166" s="2"/>
-      <c r="I166" s="2"/>
+      <c r="H166" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>371</v>
+      </c>
       <c r="J166" s="2"/>
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
@@ -8050,7 +8814,7 @@
       <c r="Z166" s="2"/>
       <c r="AA166" s="2"/>
     </row>
-    <row r="167" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3" t="s">
         <v>142</v>
       </c>
@@ -8068,8 +8832,12 @@
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
-      <c r="H167" s="2"/>
-      <c r="I167" s="2"/>
+      <c r="H167" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
@@ -8128,7 +8896,7 @@
       <c r="Z168" s="2"/>
       <c r="AA168" s="2"/>
     </row>
-    <row r="169" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3" t="s">
         <v>142</v>
       </c>
@@ -8150,8 +8918,12 @@
       <c r="G169" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H169" s="2"/>
-      <c r="I169" s="2"/>
+      <c r="H169" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
@@ -8171,7 +8943,7 @@
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
     </row>
-    <row r="170" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:27" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3" t="s">
         <v>142</v>
       </c>
@@ -8193,8 +8965,12 @@
       <c r="G170" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H170" s="2"/>
-      <c r="I170" s="2"/>
+      <c r="H170" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>369</v>
+      </c>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
@@ -8214,7 +8990,7 @@
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
     </row>
-    <row r="171" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3" t="s">
         <v>154</v>
       </c>
@@ -8234,8 +9010,12 @@
       <c r="G171" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H171" s="2"/>
-      <c r="I171" s="2"/>
+      <c r="H171" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
@@ -8255,7 +9035,7 @@
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
     </row>
-    <row r="172" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3" t="s">
         <v>154</v>
       </c>
@@ -8275,8 +9055,12 @@
       <c r="G172" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H172" s="2"/>
-      <c r="I172" s="2"/>
+      <c r="H172" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
@@ -8296,7 +9080,7 @@
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
     </row>
-    <row r="173" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3" t="s">
         <v>154</v>
       </c>
@@ -8312,8 +9096,12 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
-      <c r="H173" s="2"/>
-      <c r="I173" s="2"/>
+      <c r="H173" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
@@ -8431,8 +9219,12 @@
       <c r="G176" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H176" s="2"/>
-      <c r="I176" s="2"/>
+      <c r="H176" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
@@ -8452,7 +9244,7 @@
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
     </row>
-    <row r="177" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3" t="s">
         <v>154</v>
       </c>
@@ -8474,8 +9266,12 @@
       <c r="G177" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H177" s="2"/>
-      <c r="I177" s="2"/>
+      <c r="H177" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
@@ -8517,8 +9313,12 @@
       <c r="G178" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H178" s="2"/>
-      <c r="I178" s="2"/>
+      <c r="H178" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
@@ -8538,7 +9338,7 @@
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
     </row>
-    <row r="179" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3" t="s">
         <v>154</v>
       </c>
@@ -8560,8 +9360,12 @@
       <c r="G179" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H179" s="2"/>
-      <c r="I179" s="2"/>
+      <c r="H179" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
@@ -8581,7 +9385,7 @@
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
     </row>
-    <row r="180" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3" t="s">
         <v>154</v>
       </c>
@@ -8603,8 +9407,12 @@
       <c r="G180" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H180" s="2"/>
-      <c r="I180" s="2"/>
+      <c r="H180" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
@@ -8624,7 +9432,7 @@
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
     </row>
-    <row r="181" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3" t="s">
         <v>154</v>
       </c>
@@ -8646,8 +9454,12 @@
       <c r="G181" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H181" s="2"/>
-      <c r="I181" s="2"/>
+      <c r="H181" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
@@ -8667,7 +9479,7 @@
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
     </row>
-    <row r="182" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3" t="s">
         <v>154</v>
       </c>
@@ -8689,8 +9501,12 @@
       <c r="G182" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H182" s="2"/>
-      <c r="I182" s="2"/>
+      <c r="H182" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
@@ -8710,7 +9526,7 @@
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
     </row>
-    <row r="183" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3" t="s">
         <v>154</v>
       </c>
@@ -8732,8 +9548,12 @@
       <c r="G183" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H183" s="2"/>
-      <c r="I183" s="2"/>
+      <c r="H183" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
       <c r="L183" s="2"/>
@@ -8753,7 +9573,7 @@
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
     </row>
-    <row r="184" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3" t="s">
         <v>154</v>
       </c>
@@ -8775,8 +9595,12 @@
       <c r="G184" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H184" s="2"/>
-      <c r="I184" s="2"/>
+      <c r="H184" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
@@ -8796,7 +9620,7 @@
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
     </row>
-    <row r="185" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3" t="s">
         <v>154</v>
       </c>
@@ -8814,8 +9638,12 @@
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-      <c r="H185" s="2"/>
-      <c r="I185" s="2"/>
+      <c r="H185" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
@@ -8835,7 +9663,7 @@
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
     </row>
-    <row r="186" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3" t="s">
         <v>154</v>
       </c>
@@ -8853,8 +9681,12 @@
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
-      <c r="H186" s="2"/>
-      <c r="I186" s="2"/>
+      <c r="H186" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
@@ -8896,8 +9728,12 @@
       <c r="G187" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H187" s="2"/>
-      <c r="I187" s="2"/>
+      <c r="H187" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
       <c r="L187" s="2"/>
@@ -8917,7 +9753,7 @@
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
     </row>
-    <row r="188" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3" t="s">
         <v>154</v>
       </c>
@@ -8939,8 +9775,12 @@
       <c r="G188" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H188" s="2"/>
-      <c r="I188" s="2"/>
+      <c r="H188" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>344</v>
+      </c>
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
@@ -8960,7 +9800,7 @@
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
     </row>
-    <row r="189" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3" t="s">
         <v>154</v>
       </c>
@@ -8982,8 +9822,12 @@
       <c r="G189" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H189" s="2"/>
-      <c r="I189" s="2"/>
+      <c r="H189" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>345</v>
+      </c>
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
@@ -9003,7 +9847,7 @@
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
     </row>
-    <row r="190" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3" t="s">
         <v>154</v>
       </c>
@@ -9025,8 +9869,12 @@
       <c r="G190" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H190" s="2"/>
-      <c r="I190" s="2"/>
+      <c r="H190" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="J190" s="2"/>
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
@@ -9046,7 +9894,7 @@
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
     </row>
-    <row r="191" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3" t="s">
         <v>154</v>
       </c>
@@ -9064,8 +9912,12 @@
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-      <c r="H191" s="2"/>
-      <c r="I191" s="2"/>
+      <c r="H191" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
@@ -9085,7 +9937,7 @@
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
     </row>
-    <row r="192" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3" t="s">
         <v>154</v>
       </c>
@@ -9107,8 +9959,12 @@
       <c r="G192" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2"/>
+      <c r="H192" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
@@ -9128,7 +9984,7 @@
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
     </row>
-    <row r="193" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3" t="s">
         <v>154</v>
       </c>
@@ -9150,8 +10006,12 @@
       <c r="G193" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2"/>
+      <c r="H193" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
       <c r="L193" s="2"/>
@@ -9171,7 +10031,7 @@
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
     </row>
-    <row r="194" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3" t="s">
         <v>154</v>
       </c>
@@ -9189,8 +10049,12 @@
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2"/>
+      <c r="H194" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
       <c r="L194" s="2"/>
@@ -9210,7 +10074,7 @@
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
     </row>
-    <row r="195" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3" t="s">
         <v>154</v>
       </c>
@@ -9228,8 +10092,12 @@
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2"/>
+      <c r="H195" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
@@ -9249,7 +10117,7 @@
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
     </row>
-    <row r="196" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3" t="s">
         <v>154</v>
       </c>
@@ -9267,8 +10135,12 @@
       </c>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2"/>
+      <c r="H196" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
       <c r="L196" s="2"/>
@@ -9306,8 +10178,12 @@
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
+      <c r="H197" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
@@ -9327,7 +10203,7 @@
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
     </row>
-    <row r="198" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3" t="s">
         <v>154</v>
       </c>
@@ -9345,8 +10221,12 @@
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="2"/>
+      <c r="H198" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
@@ -9444,7 +10324,7 @@
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
     </row>
-    <row r="201" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3" t="s">
         <v>154</v>
       </c>
@@ -9462,8 +10342,12 @@
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
-      <c r="H201" s="2"/>
-      <c r="I201" s="2"/>
+      <c r="H201" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>382</v>
+      </c>
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
       <c r="L201" s="2"/>
@@ -9483,7 +10367,7 @@
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
     </row>
-    <row r="202" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3" t="s">
         <v>154</v>
       </c>
@@ -9501,8 +10385,12 @@
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
-      <c r="H202" s="2"/>
-      <c r="I202" s="2"/>
+      <c r="H202" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>383</v>
+      </c>
       <c r="J202" s="2"/>
       <c r="K202" s="2"/>
       <c r="L202" s="2"/>
@@ -9600,7 +10488,7 @@
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
     </row>
-    <row r="205" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3" t="s">
         <v>154</v>
       </c>
@@ -9618,8 +10506,12 @@
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
+      <c r="H205" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
       <c r="L205" s="2"/>
@@ -9639,7 +10531,7 @@
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
     </row>
-    <row r="206" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3" t="s">
         <v>154</v>
       </c>
@@ -9657,8 +10549,12 @@
       </c>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
-      <c r="H206" s="2"/>
-      <c r="I206" s="2"/>
+      <c r="H206" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>384</v>
+      </c>
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
       <c r="L206" s="2"/>
@@ -9678,7 +10574,7 @@
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
     </row>
-    <row r="207" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3" t="s">
         <v>154</v>
       </c>
@@ -9696,8 +10592,12 @@
       </c>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="2"/>
+      <c r="H207" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
       <c r="L207" s="2"/>
@@ -9756,7 +10656,7 @@
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
     </row>
-    <row r="209" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3" t="s">
         <v>154</v>
       </c>
@@ -9774,8 +10674,12 @@
       </c>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
-      <c r="H209" s="2"/>
-      <c r="I209" s="2"/>
+      <c r="H209" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="J209" s="2"/>
       <c r="K209" s="2"/>
       <c r="L209" s="2"/>
@@ -9795,7 +10699,7 @@
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
     </row>
-    <row r="210" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3" t="s">
         <v>154</v>
       </c>
@@ -9817,8 +10721,12 @@
       <c r="G210" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H210" s="2"/>
-      <c r="I210" s="2"/>
+      <c r="H210" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
       <c r="L210" s="2"/>
@@ -9838,7 +10746,7 @@
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
     </row>
-    <row r="211" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3" t="s">
         <v>154</v>
       </c>
@@ -9856,8 +10764,12 @@
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
-      <c r="H211" s="2"/>
-      <c r="I211" s="2"/>
+      <c r="H211" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="J211" s="2"/>
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
@@ -9877,7 +10789,7 @@
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
     </row>
-    <row r="212" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3" t="s">
         <v>154</v>
       </c>
@@ -9895,8 +10807,12 @@
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="2"/>
+      <c r="H212" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="J212" s="2"/>
       <c r="K212" s="2"/>
       <c r="L212" s="2"/>
@@ -9916,7 +10832,7 @@
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
     </row>
-    <row r="213" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3" t="s">
         <v>154</v>
       </c>
@@ -9934,8 +10850,12 @@
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2"/>
+      <c r="H213" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="J213" s="2"/>
       <c r="K213" s="2"/>
       <c r="L213" s="2"/>
@@ -9955,7 +10875,7 @@
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
     </row>
-    <row r="214" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:27" ht="218" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3" t="s">
         <v>154</v>
       </c>
@@ -9973,8 +10893,12 @@
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
+      <c r="H214" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="J214" s="2"/>
       <c r="K214" s="2"/>
       <c r="L214" s="2"/>
@@ -9994,7 +10918,7 @@
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
     </row>
-    <row r="215" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:27" ht="247" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3" t="s">
         <v>154</v>
       </c>
@@ -10012,8 +10936,12 @@
       </c>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2"/>
+      <c r="H215" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="J215" s="2"/>
       <c r="K215" s="2"/>
       <c r="L215" s="2"/>
@@ -10033,7 +10961,7 @@
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
     </row>
-    <row r="216" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3" t="s">
         <v>154</v>
       </c>
@@ -10051,8 +10979,12 @@
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="2"/>
+      <c r="H216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>359</v>
+      </c>
       <c r="J216" s="2"/>
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
@@ -10072,7 +11004,7 @@
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
     </row>
-    <row r="217" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3" t="s">
         <v>154</v>
       </c>
@@ -10090,8 +11022,12 @@
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
-      <c r="H217" s="2"/>
-      <c r="I217" s="2"/>
+      <c r="H217" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="J217" s="2"/>
       <c r="K217" s="2"/>
       <c r="L217" s="2"/>
@@ -10189,7 +11125,7 @@
       <c r="Z219" s="2"/>
       <c r="AA219" s="2"/>
     </row>
-    <row r="220" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3" t="s">
         <v>154</v>
       </c>
@@ -10207,8 +11143,12 @@
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
+      <c r="H220" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>386</v>
+      </c>
       <c r="J220" s="2"/>
       <c r="K220" s="2"/>
       <c r="L220" s="2"/>
@@ -10228,7 +11168,7 @@
       <c r="Z220" s="2"/>
       <c r="AA220" s="2"/>
     </row>
-    <row r="221" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3" t="s">
         <v>154</v>
       </c>
@@ -10246,8 +11186,12 @@
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2"/>
+      <c r="H221" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>387</v>
+      </c>
       <c r="J221" s="2"/>
       <c r="K221" s="2"/>
       <c r="L221" s="2"/>
@@ -10267,7 +11211,7 @@
       <c r="Z221" s="2"/>
       <c r="AA221" s="2"/>
     </row>
-    <row r="222" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3" t="s">
         <v>154</v>
       </c>
@@ -10285,8 +11229,12 @@
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
+      <c r="H222" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>388</v>
+      </c>
       <c r="J222" s="2"/>
       <c r="K222" s="2"/>
       <c r="L222" s="2"/>
@@ -10345,7 +11293,7 @@
       <c r="Z223" s="2"/>
       <c r="AA223" s="2"/>
     </row>
-    <row r="224" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:27" ht="203.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3" t="s">
         <v>154</v>
       </c>
@@ -10363,8 +11311,12 @@
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2"/>
+      <c r="H224" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="J224" s="2"/>
       <c r="K224" s="2"/>
       <c r="L224" s="2"/>
@@ -10423,7 +11375,7 @@
       <c r="Z225" s="2"/>
       <c r="AA225" s="2"/>
     </row>
-    <row r="226" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="3" t="s">
         <v>154</v>
       </c>
@@ -10445,8 +11397,12 @@
       <c r="G226" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H226" s="2"/>
-      <c r="I226" s="2"/>
+      <c r="H226" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>390</v>
+      </c>
       <c r="J226" s="2"/>
       <c r="K226" s="2"/>
       <c r="L226" s="2"/>
@@ -10466,7 +11422,7 @@
       <c r="Z226" s="2"/>
       <c r="AA226" s="2"/>
     </row>
-    <row r="227" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3" t="s">
         <v>154</v>
       </c>
@@ -10488,8 +11444,12 @@
       <c r="G227" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H227" s="2"/>
-      <c r="I227" s="2"/>
+      <c r="H227" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="J227" s="2"/>
       <c r="K227" s="2"/>
       <c r="L227" s="2"/>
@@ -10509,7 +11469,7 @@
       <c r="Z227" s="2"/>
       <c r="AA227" s="2"/>
     </row>
-    <row r="228" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="3" t="s">
         <v>154</v>
       </c>
@@ -10527,8 +11487,12 @@
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
-      <c r="H228" s="2"/>
-      <c r="I228" s="2"/>
+      <c r="H228" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="J228" s="2"/>
       <c r="K228" s="2"/>
       <c r="L228" s="2"/>
@@ -10548,7 +11512,7 @@
       <c r="Z228" s="2"/>
       <c r="AA228" s="2"/>
     </row>
-    <row r="229" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="3" t="s">
         <v>154</v>
       </c>
@@ -10570,8 +11534,12 @@
       <c r="G229" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H229" s="2"/>
-      <c r="I229" s="2"/>
+      <c r="H229" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="J229" s="2"/>
       <c r="K229" s="2"/>
       <c r="L229" s="2"/>
@@ -10591,7 +11559,7 @@
       <c r="Z229" s="2"/>
       <c r="AA229" s="2"/>
     </row>
-    <row r="230" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="3" t="s">
         <v>154</v>
       </c>
@@ -10613,8 +11581,12 @@
       <c r="G230" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
+      <c r="H230" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="J230" s="2"/>
       <c r="K230" s="2"/>
       <c r="L230" s="2"/>
@@ -10634,7 +11606,7 @@
       <c r="Z230" s="2"/>
       <c r="AA230" s="2"/>
     </row>
-    <row r="231" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="3" t="s">
         <v>154</v>
       </c>
@@ -10656,8 +11628,12 @@
       <c r="G231" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H231" s="2"/>
-      <c r="I231" s="2"/>
+      <c r="H231" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="J231" s="2"/>
       <c r="K231" s="2"/>
       <c r="L231" s="2"/>
@@ -10699,8 +11675,12 @@
       <c r="G232" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H232" s="2"/>
-      <c r="I232" s="2"/>
+      <c r="H232" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="J232" s="2"/>
       <c r="K232" s="2"/>
       <c r="L232" s="2"/>
@@ -10720,7 +11700,7 @@
       <c r="Z232" s="2"/>
       <c r="AA232" s="2"/>
     </row>
-    <row r="233" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3" t="s">
         <v>154</v>
       </c>
@@ -10738,8 +11718,12 @@
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
-      <c r="H233" s="2"/>
-      <c r="I233" s="2"/>
+      <c r="H233" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="J233" s="2"/>
       <c r="K233" s="2"/>
       <c r="L233" s="2"/>
@@ -10759,7 +11743,7 @@
       <c r="Z233" s="2"/>
       <c r="AA233" s="2"/>
     </row>
-    <row r="234" spans="1:27" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="3" t="s">
         <v>154</v>
       </c>
@@ -10781,8 +11765,12 @@
       <c r="G234" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
+      <c r="H234" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="J234" s="2"/>
       <c r="K234" s="2"/>
       <c r="L234" s="2"/>
@@ -10802,7 +11790,7 @@
       <c r="Z234" s="2"/>
       <c r="AA234" s="2"/>
     </row>
-    <row r="235" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3" t="s">
         <v>154</v>
       </c>
@@ -10824,8 +11812,12 @@
       <c r="G235" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H235" s="2"/>
-      <c r="I235" s="2"/>
+      <c r="H235" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="J235" s="2"/>
       <c r="K235" s="2"/>
       <c r="L235" s="2"/>
@@ -10884,7 +11876,7 @@
       <c r="Z236" s="2"/>
       <c r="AA236" s="2"/>
     </row>
-    <row r="237" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="3" t="s">
         <v>154</v>
       </c>
@@ -10906,8 +11898,12 @@
       <c r="G237" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H237" s="2"/>
-      <c r="I237" s="2"/>
+      <c r="H237" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>371</v>
+      </c>
       <c r="J237" s="2"/>
       <c r="K237" s="2"/>
       <c r="L237" s="2"/>
@@ -10927,7 +11923,7 @@
       <c r="Z237" s="2"/>
       <c r="AA237" s="2"/>
     </row>
-    <row r="238" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="3" t="s">
         <v>154</v>
       </c>
@@ -10945,8 +11941,12 @@
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
+      <c r="H238" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="J238" s="2"/>
       <c r="K238" s="2"/>
       <c r="L238" s="2"/>
@@ -10966,7 +11966,7 @@
       <c r="Z238" s="2"/>
       <c r="AA238" s="2"/>
     </row>
-    <row r="239" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="3" t="s">
         <v>154</v>
       </c>
@@ -10984,8 +11984,12 @@
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
+      <c r="H239" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="J239" s="2"/>
       <c r="K239" s="2"/>
       <c r="L239" s="2"/>
@@ -11023,8 +12027,12 @@
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
-      <c r="H240" s="2"/>
-      <c r="I240" s="2"/>
+      <c r="H240" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="J240" s="2"/>
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
@@ -11044,7 +12052,7 @@
       <c r="Z240" s="2"/>
       <c r="AA240" s="2"/>
     </row>
-    <row r="241" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="3" t="s">
         <v>154</v>
       </c>
@@ -11062,8 +12070,12 @@
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
-      <c r="H241" s="2"/>
-      <c r="I241" s="2"/>
+      <c r="H241" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
       <c r="L241" s="2"/>
@@ -11083,7 +12095,7 @@
       <c r="Z241" s="2"/>
       <c r="AA241" s="2"/>
     </row>
-    <row r="242" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3" t="s">
         <v>154</v>
       </c>
@@ -11101,8 +12113,12 @@
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
-      <c r="H242" s="2"/>
-      <c r="I242" s="2"/>
+      <c r="H242" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="J242" s="2"/>
       <c r="K242" s="2"/>
       <c r="L242" s="2"/>
@@ -11218,8 +12234,12 @@
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
-      <c r="H245" s="2"/>
-      <c r="I245" s="2"/>
+      <c r="H245" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="J245" s="2"/>
       <c r="K245" s="2"/>
       <c r="L245" s="2"/>
@@ -11278,7 +12298,7 @@
       <c r="Z246" s="2"/>
       <c r="AA246" s="2"/>
     </row>
-    <row r="247" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3" t="s">
         <v>154</v>
       </c>
@@ -11300,8 +12320,12 @@
       <c r="G247" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H247" s="2"/>
-      <c r="I247" s="2"/>
+      <c r="H247" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="J247" s="2"/>
       <c r="K247" s="2"/>
       <c r="L247" s="2"/>
@@ -11321,7 +12345,7 @@
       <c r="Z247" s="2"/>
       <c r="AA247" s="2"/>
     </row>
-    <row r="248" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:27" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="3" t="s">
         <v>154</v>
       </c>
@@ -11343,8 +12367,12 @@
       <c r="G248" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
+      <c r="H248" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>369</v>
+      </c>
       <c r="J248" s="2"/>
       <c r="K248" s="2"/>
       <c r="L248" s="2"/>
@@ -32361,7 +33389,10 @@
       <c r="AA972" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I11" r:id="rId1" display="https://ofac.treasury.gov/specially-designated-nationals-list-data-formats-data-schemas" xr:uid="{3831C74C-DC9A-48D3-824A-E1DF02A0AF41}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hajibashi.Saba\Desktop\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4C2157-2824-4D0F-BA84-EB5DEE09B216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CABC98-CB4A-4323-B840-888F0062AD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -306,9 +306,6 @@
     <t>programs</t>
   </si>
   <si>
-    <t>"committee"</t>
-  </si>
-  <si>
     <t>Programs[].Program</t>
   </si>
   <si>
@@ -1201,6 +1198,9 @@
   </si>
   <si>
     <t>features.feature[].type.text | Secondary sanctions risk:, Additional Sanctions Information - | features.feature[].value</t>
+  </si>
+  <si>
+    <t>"Sanctions"</t>
   </si>
 </sst>
 </file>
@@ -1310,10 +1310,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1610,7 +1610,7 @@
     <col min="9" max="9" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1633,10 +1633,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1657,7 +1657,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1665,10 +1665,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
@@ -1681,7 +1681,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1702,7 +1702,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1710,10 +1710,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3" t="s">
@@ -1726,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1747,7 +1747,7 @@
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
     </row>
-    <row r="4" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1755,10 +1755,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1767,7 +1767,7 @@
         <v>86</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1788,7 +1788,7 @@
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
     </row>
-    <row r="5" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1796,10 +1796,10 @@
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1808,7 +1808,7 @@
         <v>7</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1837,10 +1837,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1874,10 +1874,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>16</v>
@@ -1913,10 +1913,10 @@
         <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>16</v>
@@ -1952,7 +1952,7 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1960,10 +1960,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>16</v>
@@ -1978,7 +1978,7 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2007,10 +2007,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>16</v>
@@ -2025,7 +2025,7 @@
         <v>17</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2046,7 +2046,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
@@ -2054,10 +2054,10 @@
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>16</v>
@@ -2071,8 +2071,8 @@
       <c r="H11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>321</v>
+      <c r="I11" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2093,7 +2093,7 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -2101,10 +2101,10 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>16</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2140,7 +2140,7 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
@@ -2148,10 +2148,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>16</v>
@@ -2166,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2187,7 +2187,7 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
@@ -2195,25 +2195,25 @@
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2234,7 +2234,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
         <v>5</v>
       </c>
@@ -2242,10 +2242,10 @@
         <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
@@ -2260,7 +2260,7 @@
         <v>86</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2281,7 +2281,7 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
@@ -2289,10 +2289,10 @@
         <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
@@ -2307,7 +2307,7 @@
         <v>86</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2328,7 +2328,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
@@ -2336,10 +2336,10 @@
         <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
@@ -2350,7 +2350,7 @@
         <v>86</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2379,10 +2379,10 @@
         <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>29</v>
@@ -2410,7 +2410,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
@@ -2418,10 +2418,10 @@
         <v>36</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>29</v>
@@ -2432,7 +2432,7 @@
         <v>86</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2453,7 +2453,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2461,10 +2461,10 @@
         <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>29</v>
@@ -2475,7 +2475,7 @@
         <v>86</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2496,7 +2496,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2504,10 +2504,10 @@
         <v>38</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>29</v>
@@ -2518,7 +2518,7 @@
         <v>86</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -2547,10 +2547,10 @@
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>41</v>
@@ -2586,10 +2586,10 @@
         <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>41</v>
@@ -2625,10 +2625,10 @@
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>41</v>
@@ -2664,10 +2664,10 @@
         <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>41</v>
@@ -2703,10 +2703,10 @@
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>41</v>
@@ -2742,10 +2742,10 @@
         <v>45</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>41</v>
@@ -2781,10 +2781,10 @@
         <v>46</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>41</v>
@@ -2820,10 +2820,10 @@
         <v>47</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>41</v>
@@ -2859,10 +2859,10 @@
         <v>48</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>41</v>
@@ -2898,10 +2898,10 @@
         <v>49</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>41</v>
@@ -2937,10 +2937,10 @@
         <v>50</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>41</v>
@@ -2976,10 +2976,10 @@
         <v>51</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>41</v>
@@ -3015,10 +3015,10 @@
         <v>52</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>41</v>
@@ -3046,7 +3046,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>53</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>55</v>
@@ -3065,10 +3065,10 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -3097,10 +3097,10 @@
         <v>54</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>55</v>
@@ -3136,10 +3136,10 @@
         <v>56</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>55</v>
@@ -3167,7 +3167,7 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>5</v>
       </c>
@@ -3175,10 +3175,10 @@
         <v>57</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>55</v>
@@ -3189,7 +3189,7 @@
         <v>86</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -3210,7 +3210,7 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
         <v>5</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>59</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>55</v>
@@ -3232,7 +3232,7 @@
         <v>86</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -3253,7 +3253,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
         <v>5</v>
       </c>
@@ -3261,10 +3261,10 @@
         <v>60</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>55</v>
@@ -3275,7 +3275,7 @@
         <v>86</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -3296,7 +3296,7 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>58</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>55</v>
@@ -3322,7 +3322,7 @@
         <v>86</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -3343,7 +3343,7 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3351,10 +3351,10 @@
         <v>62</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>64</v>
@@ -3362,10 +3362,10 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -3386,7 +3386,7 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3394,10 +3394,10 @@
         <v>63</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>64</v>
@@ -3412,7 +3412,7 @@
         <v>86</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -3441,10 +3441,10 @@
         <v>66</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>64</v>
@@ -3472,7 +3472,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3480,10 +3480,10 @@
         <v>67</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>69</v>
@@ -3491,10 +3491,10 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -3515,7 +3515,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3523,10 +3523,10 @@
         <v>68</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>69</v>
@@ -3541,7 +3541,7 @@
         <v>86</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -3562,7 +3562,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3570,10 +3570,10 @@
         <v>71</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>69</v>
@@ -3588,7 +3588,7 @@
         <v>86</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -3617,10 +3617,10 @@
         <v>73</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>69</v>
@@ -3648,7 +3648,7 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3656,10 +3656,10 @@
         <v>74</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>76</v>
@@ -3667,10 +3667,10 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -3699,10 +3699,10 @@
         <v>75</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>76</v>
@@ -3717,7 +3717,7 @@
         <v>7</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -3738,7 +3738,7 @@
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
     </row>
-    <row r="51" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3" t="s">
         <v>5</v>
       </c>
@@ -3746,10 +3746,10 @@
         <v>78</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>76</v>
@@ -3764,7 +3764,7 @@
         <v>7</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -3785,7 +3785,7 @@
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
     </row>
-    <row r="52" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3793,10 +3793,10 @@
         <v>79</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>76</v>
@@ -3807,7 +3807,7 @@
         <v>7</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -3828,7 +3828,7 @@
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
     </row>
-    <row r="53" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
         <v>5</v>
       </c>
@@ -3836,10 +3836,10 @@
         <v>80</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>76</v>
@@ -3850,7 +3850,7 @@
         <v>7</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -3871,7 +3871,7 @@
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
     </row>
-    <row r="54" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3879,10 +3879,10 @@
         <v>81</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>76</v>
@@ -3893,7 +3893,7 @@
         <v>7</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -3922,10 +3922,10 @@
         <v>82</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>76</v>
@@ -3936,7 +3936,7 @@
         <v>7</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -3957,7 +3957,7 @@
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
     </row>
-    <row r="56" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3" t="s">
         <v>5</v>
       </c>
@@ -3965,25 +3965,25 @@
         <v>83</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -4004,7 +4004,7 @@
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
     </row>
-    <row r="57" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4012,10 +4012,10 @@
         <v>84</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>85</v>
@@ -4030,7 +4030,7 @@
         <v>86</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -4051,7 +4051,7 @@
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
     </row>
-    <row r="58" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4059,10 +4059,10 @@
         <v>87</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>85</v>
@@ -4077,7 +4077,7 @@
         <v>86</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -4098,7 +4098,7 @@
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
     </row>
-    <row r="59" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4106,10 +4106,10 @@
         <v>88</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>85</v>
@@ -4124,7 +4124,7 @@
         <v>86</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -4145,7 +4145,7 @@
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
     </row>
-    <row r="60" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4153,21 +4153,21 @@
         <v>90</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E60" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>92</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -4188,7 +4188,7 @@
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
     </row>
-    <row r="61" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3" t="s">
         <v>5</v>
       </c>
@@ -4196,25 +4196,25 @@
         <v>91</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E61" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>92</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>93</v>
+        <v>391</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -4240,28 +4240,28 @@
         <v>5</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E62" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>92</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -4282,33 +4282,33 @@
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
     </row>
-    <row r="63" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E63" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>92</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -4329,33 +4329,33 @@
       <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
     </row>
-    <row r="64" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E64" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>92</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -4381,16 +4381,16 @@
         <v>5</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -4415,21 +4415,21 @@
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
     </row>
-    <row r="66" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -4437,7 +4437,7 @@
         <v>7</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -4463,16 +4463,16 @@
         <v>5</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -4497,29 +4497,29 @@
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
     </row>
-    <row r="68" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
@@ -4540,33 +4540,33 @@
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
     </row>
-    <row r="69" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -4587,21 +4587,21 @@
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
     </row>
-    <row r="70" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -4609,7 +4609,7 @@
         <v>86</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -4630,21 +4630,21 @@
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
     </row>
-    <row r="71" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -4652,7 +4652,7 @@
         <v>86</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -4673,21 +4673,21 @@
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
     </row>
-    <row r="72" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -4695,7 +4695,7 @@
         <v>86</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -4716,21 +4716,21 @@
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
     </row>
-    <row r="73" spans="1:27" ht="218" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -4738,7 +4738,7 @@
         <v>86</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -4759,21 +4759,21 @@
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
     </row>
-    <row r="74" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -4781,7 +4781,7 @@
         <v>7</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -4802,21 +4802,21 @@
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
     </row>
-    <row r="75" spans="1:27" ht="247" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4824,7 +4824,7 @@
         <v>86</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
@@ -4845,21 +4845,21 @@
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
     </row>
-    <row r="76" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -4867,7 +4867,7 @@
         <v>86</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -4893,16 +4893,16 @@
         <v>5</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -4927,29 +4927,29 @@
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
     </row>
-    <row r="78" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -4975,16 +4975,16 @@
         <v>5</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -4992,7 +4992,7 @@
         <v>7</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
@@ -5013,21 +5013,21 @@
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
     </row>
-    <row r="80" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -5035,7 +5035,7 @@
         <v>7</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -5056,21 +5056,21 @@
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
     </row>
-    <row r="81" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -5078,7 +5078,7 @@
         <v>7</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
@@ -5104,16 +5104,16 @@
         <v>5</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -5143,16 +5143,16 @@
         <v>5</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -5182,16 +5182,16 @@
         <v>5</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -5199,7 +5199,7 @@
         <v>7</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
@@ -5225,16 +5225,16 @@
         <v>5</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -5259,33 +5259,33 @@
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
     </row>
-    <row r="86" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H86" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
@@ -5306,33 +5306,33 @@
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
     </row>
-    <row r="87" spans="1:27" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H87" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I87" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -5353,29 +5353,29 @@
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
     </row>
-    <row r="88" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
@@ -5401,28 +5401,28 @@
         <v>5</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
@@ -5443,33 +5443,33 @@
       <c r="Z89" s="2"/>
       <c r="AA89" s="2"/>
     </row>
-    <row r="90" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
@@ -5495,16 +5495,16 @@
         <v>5</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -5534,28 +5534,28 @@
         <v>5</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F92" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F92" s="3" t="s">
+      <c r="G92" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
@@ -5576,21 +5576,21 @@
       <c r="Z92" s="2"/>
       <c r="AA92" s="2"/>
     </row>
-    <row r="93" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -5598,7 +5598,7 @@
         <v>7</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -5619,18 +5619,18 @@
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
     </row>
-    <row r="94" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="3" t="s">
@@ -5643,7 +5643,7 @@
         <v>7</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
@@ -5664,18 +5664,18 @@
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
     </row>
-    <row r="95" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="3" t="s">
@@ -5688,7 +5688,7 @@
         <v>7</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
@@ -5709,18 +5709,18 @@
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
     </row>
-    <row r="96" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
@@ -5729,7 +5729,7 @@
         <v>7</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -5752,16 +5752,16 @@
     </row>
     <row r="97" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
@@ -5789,16 +5789,16 @@
     </row>
     <row r="98" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>16</v>
@@ -5828,16 +5828,16 @@
     </row>
     <row r="99" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>16</v>
@@ -5873,18 +5873,18 @@
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
     </row>
-    <row r="100" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>16</v>
@@ -5899,7 +5899,7 @@
         <v>17</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
@@ -5922,16 +5922,16 @@
     </row>
     <row r="101" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>16</v>
@@ -5946,7 +5946,7 @@
         <v>17</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
@@ -5967,18 +5967,18 @@
       <c r="Z101" s="2"/>
       <c r="AA101" s="2"/>
     </row>
-    <row r="102" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>16</v>
@@ -5993,7 +5993,7 @@
         <v>17</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
@@ -6014,18 +6014,18 @@
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
     </row>
-    <row r="103" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>16</v>
@@ -6040,7 +6040,7 @@
         <v>7</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
@@ -6061,18 +6061,18 @@
       <c r="Z103" s="2"/>
       <c r="AA103" s="2"/>
     </row>
-    <row r="104" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>16</v>
@@ -6087,7 +6087,7 @@
         <v>7</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -6110,31 +6110,31 @@
     </row>
     <row r="105" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
@@ -6155,18 +6155,18 @@
       <c r="Z105" s="2"/>
       <c r="AA105" s="2"/>
     </row>
-    <row r="106" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>29</v>
@@ -6181,7 +6181,7 @@
         <v>86</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
@@ -6202,18 +6202,18 @@
       <c r="Z106" s="2"/>
       <c r="AA106" s="2"/>
     </row>
-    <row r="107" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>29</v>
@@ -6228,7 +6228,7 @@
         <v>86</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
@@ -6249,18 +6249,18 @@
       <c r="Z107" s="2"/>
       <c r="AA107" s="2"/>
     </row>
-    <row r="108" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>29</v>
@@ -6271,7 +6271,7 @@
         <v>86</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
@@ -6292,18 +6292,18 @@
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
     </row>
-    <row r="109" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>29</v>
@@ -6312,13 +6312,13 @@
         <v>7</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
@@ -6339,9 +6339,9 @@
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
     </row>
-    <row r="110" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>53</v>
@@ -6350,7 +6350,7 @@
         <v>53</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>55</v>
@@ -6358,10 +6358,10 @@
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
@@ -6384,16 +6384,16 @@
     </row>
     <row r="111" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>55</v>
@@ -6423,16 +6423,16 @@
     </row>
     <row r="112" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>55</v>
@@ -6460,18 +6460,18 @@
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
     </row>
-    <row r="113" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>55</v>
@@ -6482,7 +6482,7 @@
         <v>86</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
@@ -6503,9 +6503,9 @@
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
     </row>
-    <row r="114" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>58</v>
@@ -6514,7 +6514,7 @@
         <v>59</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>55</v>
@@ -6525,7 +6525,7 @@
         <v>86</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
@@ -6546,18 +6546,18 @@
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
     </row>
-    <row r="115" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>55</v>
@@ -6568,7 +6568,7 @@
         <v>86</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
@@ -6589,9 +6589,9 @@
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
     </row>
-    <row r="116" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>59</v>
@@ -6600,7 +6600,7 @@
         <v>58</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>55</v>
@@ -6611,7 +6611,7 @@
         <v>86</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
@@ -6634,16 +6634,16 @@
     </row>
     <row r="117" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>69</v>
@@ -6651,10 +6651,10 @@
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
@@ -6675,18 +6675,18 @@
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
     </row>
-    <row r="118" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>69</v>
@@ -6697,7 +6697,7 @@
         <v>86</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -6718,18 +6718,18 @@
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
     </row>
-    <row r="119" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>69</v>
@@ -6740,7 +6740,7 @@
         <v>86</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
@@ -6763,16 +6763,16 @@
     </row>
     <row r="120" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>69</v>
@@ -6800,29 +6800,29 @@
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
     </row>
-    <row r="121" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
@@ -6843,33 +6843,33 @@
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
     </row>
-    <row r="122" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
@@ -6890,21 +6890,21 @@
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
     </row>
-    <row r="123" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
@@ -6912,7 +6912,7 @@
         <v>86</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
@@ -6933,21 +6933,21 @@
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
     </row>
-    <row r="124" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
@@ -6955,7 +6955,7 @@
         <v>86</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
@@ -6976,21 +6976,21 @@
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
     </row>
-    <row r="125" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -6998,7 +6998,7 @@
         <v>86</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
@@ -7019,21 +7019,21 @@
       <c r="Z125" s="2"/>
       <c r="AA125" s="2"/>
     </row>
-    <row r="126" spans="1:27" ht="218" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -7041,7 +7041,7 @@
         <v>86</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
@@ -7062,21 +7062,21 @@
       <c r="Z126" s="2"/>
       <c r="AA126" s="2"/>
     </row>
-    <row r="127" spans="1:27" ht="247" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -7084,7 +7084,7 @@
         <v>86</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
@@ -7105,21 +7105,21 @@
       <c r="Z127" s="2"/>
       <c r="AA127" s="2"/>
     </row>
-    <row r="128" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -7127,7 +7127,7 @@
         <v>7</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
@@ -7148,21 +7148,21 @@
       <c r="Z128" s="2"/>
       <c r="AA128" s="2"/>
     </row>
-    <row r="129" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -7170,7 +7170,7 @@
         <v>86</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
@@ -7193,19 +7193,19 @@
     </row>
     <row r="130" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -7232,31 +7232,31 @@
     </row>
     <row r="131" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
@@ -7277,18 +7277,18 @@
       <c r="Z131" s="2"/>
       <c r="AA131" s="2"/>
     </row>
-    <row r="132" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>85</v>
@@ -7303,7 +7303,7 @@
         <v>86</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
@@ -7324,18 +7324,18 @@
       <c r="Z132" s="2"/>
       <c r="AA132" s="2"/>
     </row>
-    <row r="133" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>85</v>
@@ -7350,7 +7350,7 @@
         <v>86</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
@@ -7371,18 +7371,18 @@
       <c r="Z133" s="2"/>
       <c r="AA133" s="2"/>
     </row>
-    <row r="134" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>85</v>
@@ -7397,7 +7397,7 @@
         <v>86</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
@@ -7418,18 +7418,18 @@
       <c r="Z134" s="2"/>
       <c r="AA134" s="2"/>
     </row>
-    <row r="135" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>92</v>
@@ -7437,10 +7437,10 @@
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
@@ -7461,18 +7461,18 @@
       <c r="Z135" s="2"/>
       <c r="AA135" s="2"/>
     </row>
-    <row r="136" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>92</v>
@@ -7481,13 +7481,13 @@
         <v>17</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>93</v>
+        <v>391</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
@@ -7510,16 +7510,16 @@
     </row>
     <row r="137" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>92</v>
@@ -7528,13 +7528,13 @@
         <v>7</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
@@ -7555,18 +7555,18 @@
       <c r="Z137" s="2"/>
       <c r="AA137" s="2"/>
     </row>
-    <row r="138" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>92</v>
@@ -7575,13 +7575,13 @@
         <v>17</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
@@ -7602,18 +7602,18 @@
       <c r="Z138" s="2"/>
       <c r="AA138" s="2"/>
     </row>
-    <row r="139" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>92</v>
@@ -7622,13 +7622,13 @@
         <v>7</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
@@ -7649,29 +7649,29 @@
       <c r="Z139" s="2"/>
       <c r="AA139" s="2"/>
     </row>
-    <row r="140" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
@@ -7694,19 +7694,19 @@
     </row>
     <row r="141" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -7714,7 +7714,7 @@
         <v>7</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
@@ -7735,21 +7735,21 @@
       <c r="Z141" s="2"/>
       <c r="AA141" s="2"/>
     </row>
-    <row r="142" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -7757,7 +7757,7 @@
         <v>7</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
@@ -7778,21 +7778,21 @@
       <c r="Z142" s="2"/>
       <c r="AA142" s="2"/>
     </row>
-    <row r="143" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -7800,7 +7800,7 @@
         <v>7</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
@@ -7823,19 +7823,19 @@
     </row>
     <row r="144" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -7862,19 +7862,19 @@
     </row>
     <row r="145" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -7901,19 +7901,19 @@
     </row>
     <row r="146" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -7921,7 +7921,7 @@
         <v>7</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
@@ -7942,18 +7942,18 @@
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
     </row>
-    <row r="147" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>76</v>
@@ -7961,10 +7961,10 @@
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
@@ -7987,16 +7987,16 @@
     </row>
     <row r="148" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>76</v>
@@ -8011,7 +8011,7 @@
         <v>7</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
@@ -8032,18 +8032,18 @@
       <c r="Z148" s="2"/>
       <c r="AA148" s="2"/>
     </row>
-    <row r="149" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>76</v>
@@ -8058,7 +8058,7 @@
         <v>7</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
@@ -8079,18 +8079,18 @@
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
     </row>
-    <row r="150" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>76</v>
@@ -8101,7 +8101,7 @@
         <v>7</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
@@ -8122,18 +8122,18 @@
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
     </row>
-    <row r="151" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>76</v>
@@ -8144,7 +8144,7 @@
         <v>7</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
@@ -8165,18 +8165,18 @@
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
     </row>
-    <row r="152" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>76</v>
@@ -8187,7 +8187,7 @@
         <v>7</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
@@ -8210,16 +8210,16 @@
     </row>
     <row r="153" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>76</v>
@@ -8230,7 +8230,7 @@
         <v>7</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
@@ -8253,27 +8253,27 @@
     </row>
     <row r="154" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
@@ -8294,21 +8294,21 @@
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
     </row>
-    <row r="155" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E155" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
@@ -8316,7 +8316,7 @@
         <v>86</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
@@ -8337,21 +8337,21 @@
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
     </row>
-    <row r="156" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
@@ -8359,7 +8359,7 @@
         <v>86</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
@@ -8382,19 +8382,19 @@
     </row>
     <row r="157" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
@@ -8421,27 +8421,27 @@
     </row>
     <row r="158" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
@@ -8462,21 +8462,21 @@
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
     </row>
-    <row r="159" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E159" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
@@ -8484,7 +8484,7 @@
         <v>86</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
@@ -8505,33 +8505,33 @@
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
     </row>
-    <row r="160" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
@@ -8554,19 +8554,19 @@
     </row>
     <row r="161" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
@@ -8591,29 +8591,29 @@
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
     </row>
-    <row r="162" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
@@ -8636,31 +8636,31 @@
     </row>
     <row r="163" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E163" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C163" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E163" s="3" t="s">
+      <c r="F163" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="G163" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
@@ -8681,33 +8681,33 @@
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
     </row>
-    <row r="164" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H164" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
@@ -8730,19 +8730,19 @@
     </row>
     <row r="165" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
@@ -8769,31 +8769,31 @@
     </row>
     <row r="166" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B166" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F166" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C166" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F166" s="3" t="s">
+      <c r="G166" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="H166" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J166" s="2"/>
       <c r="K166" s="2"/>
@@ -8814,21 +8814,21 @@
       <c r="Z166" s="2"/>
       <c r="AA166" s="2"/>
     </row>
-    <row r="167" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
@@ -8836,7 +8836,7 @@
         <v>7</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
@@ -8859,19 +8859,19 @@
     </row>
     <row r="168" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
@@ -8896,33 +8896,33 @@
       <c r="Z168" s="2"/>
       <c r="AA168" s="2"/>
     </row>
-    <row r="169" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B169" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E169" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H169" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I169" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="I169" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
@@ -8943,33 +8943,33 @@
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
     </row>
-    <row r="170" spans="1:27" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H170" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I170" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="I170" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
@@ -8990,18 +8990,18 @@
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
     </row>
-    <row r="171" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" s="3" t="s">
@@ -9014,7 +9014,7 @@
         <v>7</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
@@ -9035,18 +9035,18 @@
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
     </row>
-    <row r="172" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" s="3" t="s">
@@ -9059,7 +9059,7 @@
         <v>7</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
@@ -9080,18 +9080,18 @@
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
     </row>
-    <row r="173" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
@@ -9100,7 +9100,7 @@
         <v>7</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
@@ -9123,16 +9123,16 @@
     </row>
     <row r="174" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
@@ -9160,16 +9160,16 @@
     </row>
     <row r="175" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>16</v>
@@ -9199,16 +9199,16 @@
     </row>
     <row r="176" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>16</v>
@@ -9244,18 +9244,18 @@
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
     </row>
-    <row r="177" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>16</v>
@@ -9270,7 +9270,7 @@
         <v>17</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
@@ -9293,16 +9293,16 @@
     </row>
     <row r="178" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>16</v>
@@ -9317,7 +9317,7 @@
         <v>17</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
@@ -9338,18 +9338,18 @@
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
     </row>
-    <row r="179" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>16</v>
@@ -9364,7 +9364,7 @@
         <v>17</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
@@ -9385,18 +9385,18 @@
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
     </row>
-    <row r="180" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>16</v>
@@ -9411,7 +9411,7 @@
         <v>7</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
@@ -9432,18 +9432,18 @@
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
     </row>
-    <row r="181" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>16</v>
@@ -9458,7 +9458,7 @@
         <v>7</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
@@ -9479,33 +9479,33 @@
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
     </row>
-    <row r="182" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
@@ -9526,18 +9526,18 @@
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
     </row>
-    <row r="183" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>29</v>
@@ -9552,7 +9552,7 @@
         <v>86</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
@@ -9573,18 +9573,18 @@
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
     </row>
-    <row r="184" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>29</v>
@@ -9599,7 +9599,7 @@
         <v>86</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
@@ -9620,18 +9620,18 @@
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
     </row>
-    <row r="185" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>29</v>
@@ -9642,7 +9642,7 @@
         <v>86</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
@@ -9663,18 +9663,18 @@
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
     </row>
-    <row r="186" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>29</v>
@@ -9685,7 +9685,7 @@
         <v>86</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
@@ -9708,31 +9708,31 @@
     </row>
     <row r="187" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
@@ -9753,18 +9753,18 @@
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
     </row>
-    <row r="188" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>85</v>
@@ -9779,7 +9779,7 @@
         <v>86</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
@@ -9800,18 +9800,18 @@
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
     </row>
-    <row r="189" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>85</v>
@@ -9826,7 +9826,7 @@
         <v>86</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
@@ -9847,18 +9847,18 @@
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
     </row>
-    <row r="190" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>85</v>
@@ -9873,7 +9873,7 @@
         <v>86</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J190" s="2"/>
       <c r="K190" s="2"/>
@@ -9894,18 +9894,18 @@
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
     </row>
-    <row r="191" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>76</v>
@@ -9913,10 +9913,10 @@
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
@@ -9939,31 +9939,31 @@
     </row>
     <row r="192" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
@@ -9984,33 +9984,33 @@
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
     </row>
-    <row r="193" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
@@ -10031,18 +10031,18 @@
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
     </row>
-    <row r="194" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>76</v>
@@ -10053,7 +10053,7 @@
         <v>7</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
@@ -10074,18 +10074,18 @@
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
     </row>
-    <row r="195" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>76</v>
@@ -10096,7 +10096,7 @@
         <v>7</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
@@ -10117,18 +10117,18 @@
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
     </row>
-    <row r="196" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>76</v>
@@ -10139,7 +10139,7 @@
         <v>7</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
@@ -10162,16 +10162,16 @@
     </row>
     <row r="197" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>76</v>
@@ -10182,7 +10182,7 @@
         <v>7</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
@@ -10203,9 +10203,9 @@
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
     </row>
-    <row r="198" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>53</v>
@@ -10214,7 +10214,7 @@
         <v>53</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>55</v>
@@ -10222,10 +10222,10 @@
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
@@ -10248,16 +10248,16 @@
     </row>
     <row r="199" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>55</v>
@@ -10287,16 +10287,16 @@
     </row>
     <row r="200" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>55</v>
@@ -10324,18 +10324,18 @@
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
     </row>
-    <row r="201" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>55</v>
@@ -10346,7 +10346,7 @@
         <v>86</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
@@ -10367,9 +10367,9 @@
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
     </row>
-    <row r="202" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>58</v>
@@ -10378,7 +10378,7 @@
         <v>59</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>55</v>
@@ -10389,7 +10389,7 @@
         <v>86</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J202" s="2"/>
       <c r="K202" s="2"/>
@@ -10412,16 +10412,16 @@
     </row>
     <row r="203" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>55</v>
@@ -10451,7 +10451,7 @@
     </row>
     <row r="204" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>59</v>
@@ -10460,7 +10460,7 @@
         <v>58</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>55</v>
@@ -10488,18 +10488,18 @@
       <c r="Z204" s="2"/>
       <c r="AA204" s="2"/>
     </row>
-    <row r="205" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>69</v>
@@ -10507,10 +10507,10 @@
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
@@ -10531,18 +10531,18 @@
       <c r="Z205" s="2"/>
       <c r="AA205" s="2"/>
     </row>
-    <row r="206" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>69</v>
@@ -10553,7 +10553,7 @@
         <v>86</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
@@ -10574,18 +10574,18 @@
       <c r="Z206" s="2"/>
       <c r="AA206" s="2"/>
     </row>
-    <row r="207" spans="1:27" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>69</v>
@@ -10596,7 +10596,7 @@
         <v>86</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
@@ -10619,16 +10619,16 @@
     </row>
     <row r="208" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>69</v>
@@ -10656,29 +10656,29 @@
       <c r="Z208" s="2"/>
       <c r="AA208" s="2"/>
     </row>
-    <row r="209" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
       <c r="H209" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J209" s="2"/>
       <c r="K209" s="2"/>
@@ -10699,33 +10699,33 @@
       <c r="Z209" s="2"/>
       <c r="AA209" s="2"/>
     </row>
-    <row r="210" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B210" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E210" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
@@ -10746,21 +10746,21 @@
       <c r="Z210" s="2"/>
       <c r="AA210" s="2"/>
     </row>
-    <row r="211" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -10768,7 +10768,7 @@
         <v>86</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J211" s="2"/>
       <c r="K211" s="2"/>
@@ -10789,21 +10789,21 @@
       <c r="Z211" s="2"/>
       <c r="AA211" s="2"/>
     </row>
-    <row r="212" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
@@ -10811,7 +10811,7 @@
         <v>86</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J212" s="2"/>
       <c r="K212" s="2"/>
@@ -10832,21 +10832,21 @@
       <c r="Z212" s="2"/>
       <c r="AA212" s="2"/>
     </row>
-    <row r="213" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
@@ -10854,7 +10854,7 @@
         <v>86</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J213" s="2"/>
       <c r="K213" s="2"/>
@@ -10875,21 +10875,21 @@
       <c r="Z213" s="2"/>
       <c r="AA213" s="2"/>
     </row>
-    <row r="214" spans="1:27" ht="218" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -10897,7 +10897,7 @@
         <v>86</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J214" s="2"/>
       <c r="K214" s="2"/>
@@ -10918,21 +10918,21 @@
       <c r="Z214" s="2"/>
       <c r="AA214" s="2"/>
     </row>
-    <row r="215" spans="1:27" ht="247" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
@@ -10940,7 +10940,7 @@
         <v>86</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J215" s="2"/>
       <c r="K215" s="2"/>
@@ -10961,21 +10961,21 @@
       <c r="Z215" s="2"/>
       <c r="AA215" s="2"/>
     </row>
-    <row r="216" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
@@ -10983,7 +10983,7 @@
         <v>7</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J216" s="2"/>
       <c r="K216" s="2"/>
@@ -11004,21 +11004,21 @@
       <c r="Z216" s="2"/>
       <c r="AA216" s="2"/>
     </row>
-    <row r="217" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:27" ht="102" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
@@ -11026,7 +11026,7 @@
         <v>86</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J217" s="2"/>
       <c r="K217" s="2"/>
@@ -11049,19 +11049,19 @@
     </row>
     <row r="218" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
@@ -11088,19 +11088,19 @@
     </row>
     <row r="219" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
@@ -11125,21 +11125,21 @@
       <c r="Z219" s="2"/>
       <c r="AA219" s="2"/>
     </row>
-    <row r="220" spans="1:27" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B220" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E220" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -11147,7 +11147,7 @@
         <v>86</v>
       </c>
       <c r="I220" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J220" s="2"/>
       <c r="K220" s="2"/>
@@ -11168,21 +11168,21 @@
       <c r="Z220" s="2"/>
       <c r="AA220" s="2"/>
     </row>
-    <row r="221" spans="1:27" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -11190,7 +11190,7 @@
         <v>86</v>
       </c>
       <c r="I221" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J221" s="2"/>
       <c r="K221" s="2"/>
@@ -11211,21 +11211,21 @@
       <c r="Z221" s="2"/>
       <c r="AA221" s="2"/>
     </row>
-    <row r="222" spans="1:27" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -11233,7 +11233,7 @@
         <v>86</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J222" s="2"/>
       <c r="K222" s="2"/>
@@ -11256,19 +11256,19 @@
     </row>
     <row r="223" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -11293,21 +11293,21 @@
       <c r="Z223" s="2"/>
       <c r="AA223" s="2"/>
     </row>
-    <row r="224" spans="1:27" ht="203.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -11315,7 +11315,7 @@
         <v>86</v>
       </c>
       <c r="I224" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J224" s="2"/>
       <c r="K224" s="2"/>
@@ -11338,19 +11338,19 @@
     </row>
     <row r="225" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
@@ -11375,33 +11375,33 @@
       <c r="Z225" s="2"/>
       <c r="AA225" s="2"/>
     </row>
-    <row r="226" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H226" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I226" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J226" s="2"/>
       <c r="K226" s="2"/>
@@ -11422,33 +11422,33 @@
       <c r="Z226" s="2"/>
       <c r="AA226" s="2"/>
     </row>
-    <row r="227" spans="1:27" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J227" s="2"/>
       <c r="K227" s="2"/>
@@ -11469,18 +11469,18 @@
       <c r="Z227" s="2"/>
       <c r="AA227" s="2"/>
     </row>
-    <row r="228" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>92</v>
@@ -11488,10 +11488,10 @@
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J228" s="2"/>
       <c r="K228" s="2"/>
@@ -11512,18 +11512,18 @@
       <c r="Z228" s="2"/>
       <c r="AA228" s="2"/>
     </row>
-    <row r="229" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>92</v>
@@ -11532,13 +11532,13 @@
         <v>17</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>93</v>
+        <v>391</v>
       </c>
       <c r="H229" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J229" s="2"/>
       <c r="K229" s="2"/>
@@ -11561,16 +11561,16 @@
     </row>
     <row r="230" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>92</v>
@@ -11579,13 +11579,13 @@
         <v>7</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J230" s="2"/>
       <c r="K230" s="2"/>
@@ -11606,18 +11606,18 @@
       <c r="Z230" s="2"/>
       <c r="AA230" s="2"/>
     </row>
-    <row r="231" spans="1:27" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>92</v>
@@ -11626,13 +11626,13 @@
         <v>17</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I231" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J231" s="2"/>
       <c r="K231" s="2"/>
@@ -11653,18 +11653,18 @@
       <c r="Z231" s="2"/>
       <c r="AA231" s="2"/>
     </row>
-    <row r="232" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>92</v>
@@ -11673,13 +11673,13 @@
         <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J232" s="2"/>
       <c r="K232" s="2"/>
@@ -11700,29 +11700,29 @@
       <c r="Z232" s="2"/>
       <c r="AA232" s="2"/>
     </row>
-    <row r="233" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J233" s="2"/>
       <c r="K233" s="2"/>
@@ -11745,31 +11745,31 @@
     </row>
     <row r="234" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B234" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E234" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C234" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E234" s="3" t="s">
+      <c r="F234" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F234" s="3" t="s">
+      <c r="G234" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J234" s="2"/>
       <c r="K234" s="2"/>
@@ -11790,33 +11790,33 @@
       <c r="Z234" s="2"/>
       <c r="AA234" s="2"/>
     </row>
-    <row r="235" spans="1:27" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J235" s="2"/>
       <c r="K235" s="2"/>
@@ -11839,19 +11839,19 @@
     </row>
     <row r="236" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
@@ -11878,31 +11878,31 @@
     </row>
     <row r="237" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F237" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F237" s="3" t="s">
+      <c r="G237" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J237" s="2"/>
       <c r="K237" s="2"/>
@@ -11923,21 +11923,21 @@
       <c r="Z237" s="2"/>
       <c r="AA237" s="2"/>
     </row>
-    <row r="238" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
@@ -11945,7 +11945,7 @@
         <v>7</v>
       </c>
       <c r="I238" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J238" s="2"/>
       <c r="K238" s="2"/>
@@ -11966,29 +11966,29 @@
       <c r="Z238" s="2"/>
       <c r="AA238" s="2"/>
     </row>
-    <row r="239" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I239" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J239" s="2"/>
       <c r="K239" s="2"/>
@@ -12011,19 +12011,19 @@
     </row>
     <row r="240" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E240" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C240" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -12031,7 +12031,7 @@
         <v>7</v>
       </c>
       <c r="I240" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J240" s="2"/>
       <c r="K240" s="2"/>
@@ -12052,21 +12052,21 @@
       <c r="Z240" s="2"/>
       <c r="AA240" s="2"/>
     </row>
-    <row r="241" spans="1:27" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -12074,7 +12074,7 @@
         <v>7</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
@@ -12095,21 +12095,21 @@
       <c r="Z241" s="2"/>
       <c r="AA241" s="2"/>
     </row>
-    <row r="242" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -12117,7 +12117,7 @@
         <v>7</v>
       </c>
       <c r="I242" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J242" s="2"/>
       <c r="K242" s="2"/>
@@ -12140,19 +12140,19 @@
     </row>
     <row r="243" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -12179,19 +12179,19 @@
     </row>
     <row r="244" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -12218,19 +12218,19 @@
     </row>
     <row r="245" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -12238,7 +12238,7 @@
         <v>7</v>
       </c>
       <c r="I245" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J245" s="2"/>
       <c r="K245" s="2"/>
@@ -12261,19 +12261,19 @@
     </row>
     <row r="246" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -12298,33 +12298,33 @@
       <c r="Z246" s="2"/>
       <c r="AA246" s="2"/>
     </row>
-    <row r="247" spans="1:27" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B247" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E247" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C247" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E247" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H247" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I247" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="I247" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="J247" s="2"/>
       <c r="K247" s="2"/>
@@ -12345,33 +12345,33 @@
       <c r="Z247" s="2"/>
       <c r="AA247" s="2"/>
     </row>
-    <row r="248" spans="1:27" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:27" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H248" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="I248" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="I248" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="J248" s="2"/>
       <c r="K248" s="2"/>
@@ -33390,7 +33390,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I11" r:id="rId1" display="https://ofac.treasury.gov/specially-designated-nationals-list-data-formats-data-schemas" xr:uid="{3831C74C-DC9A-48D3-824A-E1DF02A0AF41}"/>
+    <hyperlink ref="I11" r:id="rId1" display="https://ofac.treasury.gov/specially-designated-nationals-list-data-formats-data-schemas" xr:uid="{8DEE140E-D4EC-4C09-9874-B2BEF6E47106}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TOSAN\mapping\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18DBBB4E-9727-4851-99E5-1B42B6504AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F2A43B-F9BD-4865-BCED-9833042410B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8C60D5FA-9BA1-4DC9-A2B8-A4B69C8D429C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3100" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3110" uniqueCount="733">
   <si>
     <t>Entity Category</t>
   </si>
@@ -985,9 +985,6 @@
     <t>citizenship[]</t>
   </si>
   <si>
-    <t>NATIONALITY[]</t>
-  </si>
-  <si>
     <t>Countries[].CountryType</t>
   </si>
   <si>
@@ -1290,9 +1287,6 @@
   </si>
   <si>
     <t>Aliases[].Phonetic_Key</t>
-  </si>
-  <si>
-    <t>Aliased[].Search_Tokens</t>
   </si>
   <si>
     <t>Aliases[].Note</t>
@@ -2375,6 +2369,15 @@
   </si>
   <si>
     <t>Comments, narratives, and supporting information</t>
+  </si>
+  <si>
+    <t>Aliases[].Search_Tokens</t>
+  </si>
+  <si>
+    <t>ISO2 code of the country name</t>
+  </si>
+  <si>
+    <t>NATIONALITY.VALUE[]</t>
   </si>
 </sst>
 </file>
@@ -6046,7 +6049,7 @@
         <v>116</v>
       </c>
       <c r="Y49" s="6" t="s">
-        <v>279</v>
+        <v>732</v>
       </c>
       <c r="Z49" s="6"/>
       <c r="AA49" s="6"/>
@@ -6064,10 +6067,10 @@
         <v>27</v>
       </c>
       <c r="B50" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>30</v>
@@ -6079,19 +6082,19 @@
         <v>45</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
@@ -6101,7 +6104,7 @@
         <v>45</v>
       </c>
       <c r="Q50" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
@@ -6111,19 +6114,19 @@
         <v>45</v>
       </c>
       <c r="W50" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="X50" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Y50" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z50" s="6" t="s">
         <v>45</v>
       </c>
       <c r="AA50" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AB50" s="5"/>
       <c r="AC50" s="5"/>
@@ -6135,13 +6138,21 @@
       <c r="AI50" s="5"/>
     </row>
     <row r="51" spans="1:35">
-      <c r="A51" s="6"/>
+      <c r="A51" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="B51" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
+        <v>285</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -6178,10 +6189,10 @@
         <v>27</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>30</v>
@@ -6193,19 +6204,19 @@
         <v>31</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
@@ -6231,13 +6242,13 @@
         <v>31</v>
       </c>
       <c r="Y52" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z52" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA52" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB52" s="5"/>
       <c r="AC52" s="5"/>
@@ -6253,10 +6264,10 @@
         <v>27</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>294</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>30</v>
@@ -6284,7 +6295,7 @@
         <v>31</v>
       </c>
       <c r="W53" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="X53" s="6"/>
       <c r="Y53" s="6"/>
@@ -6292,7 +6303,7 @@
         <v>31</v>
       </c>
       <c r="AA53" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AB53" s="5"/>
       <c r="AC53" s="5"/>
@@ -6308,40 +6319,40 @@
         <v>27</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="I54" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="I54" s="7" t="s">
-        <v>301</v>
-      </c>
       <c r="J54" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
       <c r="P54" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q54" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="Q54" s="6" t="s">
-        <v>303</v>
       </c>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
@@ -6350,10 +6361,10 @@
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
       <c r="X54" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y54" s="8" t="s">
         <v>304</v>
-      </c>
-      <c r="Y54" s="8" t="s">
-        <v>305</v>
       </c>
       <c r="Z54" s="6"/>
       <c r="AA54" s="6"/>
@@ -6371,74 +6382,74 @@
         <v>27</v>
       </c>
       <c r="B55" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G55" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="I55" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="J55" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L55" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="J55" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="K55" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="L55" s="6" t="s">
+      <c r="M55" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="M55" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="N55" s="6"/>
       <c r="O55" s="6"/>
       <c r="P55" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q55" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S55" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T55" s="6"/>
       <c r="U55" s="6"/>
       <c r="V55" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="W55" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="W55" s="30" t="s">
+      <c r="X55" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="X55" s="8" t="s">
+      <c r="Y55" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="Y55" s="31" t="s">
+      <c r="Z55" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="Z55" s="6" t="s">
+      <c r="AA55" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="AA55" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="AB55" s="5"/>
       <c r="AC55" s="5"/>
@@ -6454,16 +6465,16 @@
         <v>27</v>
       </c>
       <c r="B56" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>31</v>
@@ -6472,30 +6483,30 @@
         <v>32</v>
       </c>
       <c r="H56" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="J56" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="J56" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="L56" s="6" t="s">
+      <c r="M56" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
       <c r="P56" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q56" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="Q56" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>31</v>
@@ -6506,22 +6517,22 @@
       <c r="T56" s="6"/>
       <c r="U56" s="6"/>
       <c r="V56" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="W56" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="W56" s="30" t="s">
+      <c r="X56" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="X56" s="6" t="s">
+      <c r="Y56" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="Y56" s="8" t="s">
+      <c r="Z56" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA56" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="Z56" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="AA56" s="6" t="s">
-        <v>334</v>
       </c>
       <c r="AB56" s="5"/>
       <c r="AC56" s="5"/>
@@ -6537,7 +6548,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -6578,30 +6589,30 @@
         <v>27</v>
       </c>
       <c r="B58" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="I58" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="I58" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="J58" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="K58" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>339</v>
       </c>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
@@ -6616,10 +6627,10 @@
       <c r="V58" s="30"/>
       <c r="W58" s="30"/>
       <c r="X58" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y58" s="8" t="s">
         <v>340</v>
-      </c>
-      <c r="Y58" s="8" t="s">
-        <v>341</v>
       </c>
       <c r="Z58" s="6"/>
       <c r="AA58" s="6"/>
@@ -6637,30 +6648,30 @@
         <v>27</v>
       </c>
       <c r="B59" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
@@ -6675,10 +6686,10 @@
       <c r="V59" s="30"/>
       <c r="W59" s="30"/>
       <c r="X59" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y59" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Z59" s="6"/>
       <c r="AA59" s="6"/>
@@ -6696,30 +6707,30 @@
         <v>27</v>
       </c>
       <c r="B60" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>346</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>347</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
@@ -6731,17 +6742,17 @@
         <v>45</v>
       </c>
       <c r="S60" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T60" s="6"/>
       <c r="U60" s="6"/>
       <c r="V60" s="30"/>
       <c r="W60" s="30"/>
       <c r="X60" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Y60" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Z60" s="6"/>
       <c r="AA60" s="6"/>
@@ -6759,40 +6770,40 @@
         <v>27</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
       <c r="P61" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q61" s="6" t="s">
         <v>354</v>
-      </c>
-      <c r="Q61" s="6" t="s">
-        <v>355</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>45</v>
@@ -6801,16 +6812,16 @@
       <c r="T61" s="6"/>
       <c r="U61" s="6"/>
       <c r="V61" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="W61" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="X61" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="X61" s="8" t="s">
+      <c r="Y61" s="8" t="s">
         <v>357</v>
-      </c>
-      <c r="Y61" s="8" t="s">
-        <v>358</v>
       </c>
       <c r="Z61" s="6"/>
       <c r="AA61" s="6"/>
@@ -6828,7 +6839,7 @@
         <v>27</v>
       </c>
       <c r="B62" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -6869,7 +6880,7 @@
         <v>27</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -6910,7 +6921,7 @@
         <v>27</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -6951,7 +6962,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -6992,16 +7003,16 @@
         <v>27</v>
       </c>
       <c r="B66" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>363</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>364</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>116</v>
@@ -7029,7 +7040,7 @@
         <v>116</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
@@ -7041,7 +7052,7 @@
         <v>116</v>
       </c>
       <c r="Y66" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Z66" s="8"/>
       <c r="AA66" s="6"/>
@@ -7059,16 +7070,16 @@
         <v>27</v>
       </c>
       <c r="B67" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>49</v>
@@ -7080,19 +7091,19 @@
         <v>49</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L67" s="6" t="s">
         <v>45</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N67" s="6"/>
       <c r="O67" s="6"/>
@@ -7100,7 +7111,7 @@
         <v>49</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R67" s="6"/>
       <c r="S67" s="6"/>
@@ -7112,7 +7123,7 @@
         <v>45</v>
       </c>
       <c r="Y67" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Z67" s="21"/>
       <c r="AA67" s="21"/>
@@ -7130,16 +7141,16 @@
         <v>27</v>
       </c>
       <c r="B68" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>49</v>
@@ -7151,19 +7162,19 @@
         <v>49</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L68" s="6" t="s">
         <v>195</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
@@ -7171,7 +7182,7 @@
         <v>49</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R68" s="6"/>
       <c r="S68" s="6"/>
@@ -7183,7 +7194,7 @@
         <v>31</v>
       </c>
       <c r="Y68" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Z68" s="21"/>
       <c r="AA68" s="21"/>
@@ -7201,7 +7212,7 @@
         <v>27</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
@@ -7242,7 +7253,7 @@
         <v>27</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
@@ -7283,7 +7294,7 @@
         <v>27</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>381</v>
+        <v>730</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
@@ -7324,22 +7335,22 @@
         <v>27</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F72" s="32" t="s">
         <v>49</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H72" s="32" t="s">
         <v>172</v>
@@ -7361,7 +7372,7 @@
         <v>49</v>
       </c>
       <c r="Q72" s="32" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="R72" s="32"/>
       <c r="S72" s="32"/>
@@ -7373,7 +7384,7 @@
         <v>31</v>
       </c>
       <c r="Y72" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Z72" s="21"/>
       <c r="AA72" s="21"/>
@@ -7391,16 +7402,16 @@
         <v>27</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
@@ -7408,13 +7419,13 @@
         <v>116</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>116</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
@@ -7424,7 +7435,7 @@
         <v>116</v>
       </c>
       <c r="Q73" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R73" s="6"/>
       <c r="S73" s="6"/>
@@ -7450,40 +7461,40 @@
         <v>27</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>45</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L74" s="28" t="s">
         <v>45</v>
       </c>
       <c r="M74" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="N74" s="6"/>
       <c r="O74" s="6"/>
@@ -7491,7 +7502,7 @@
         <v>45</v>
       </c>
       <c r="Q74" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
@@ -7501,19 +7512,19 @@
         <v>45</v>
       </c>
       <c r="W74" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="X74" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Y74" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Z74" s="6" t="s">
         <v>45</v>
       </c>
       <c r="AA74" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AB74" s="5"/>
       <c r="AC74" s="5"/>
@@ -7529,40 +7540,40 @@
         <v>27</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N75" s="6"/>
       <c r="O75" s="6"/>
@@ -7570,7 +7581,7 @@
         <v>31</v>
       </c>
       <c r="Q75" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R75" s="6"/>
       <c r="S75" s="6"/>
@@ -7580,19 +7591,19 @@
         <v>31</v>
       </c>
       <c r="W75" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y75" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Z75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA75" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AB75" s="5"/>
       <c r="AC75" s="5"/>
@@ -7608,40 +7619,40 @@
         <v>27</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>45</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L76" s="6" t="s">
         <v>45</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N76" s="6"/>
       <c r="O76" s="6"/>
@@ -7649,7 +7660,7 @@
         <v>45</v>
       </c>
       <c r="Q76" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="R76" s="6"/>
       <c r="S76" s="6"/>
@@ -7659,19 +7670,19 @@
         <v>45</v>
       </c>
       <c r="W76" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="X76" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Y76" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Z76" s="8" t="s">
         <v>45</v>
       </c>
       <c r="AA76" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AB76" s="5"/>
       <c r="AC76" s="5"/>
@@ -7687,34 +7698,34 @@
         <v>27</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
@@ -7724,7 +7735,7 @@
         <v>31</v>
       </c>
       <c r="Q77" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R77" s="6"/>
       <c r="S77" s="6"/>
@@ -7734,7 +7745,7 @@
         <v>31</v>
       </c>
       <c r="W77" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="X77" s="6"/>
       <c r="Y77" s="6"/>
@@ -7742,7 +7753,7 @@
         <v>31</v>
       </c>
       <c r="AA77" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AB77" s="5"/>
       <c r="AC77" s="5"/>
@@ -7758,16 +7769,16 @@
         <v>27</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
@@ -7783,7 +7794,7 @@
         <v>116</v>
       </c>
       <c r="Q78" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R78" s="6"/>
       <c r="S78" s="6"/>
@@ -7795,7 +7806,7 @@
         <v>116</v>
       </c>
       <c r="Y78" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Z78" s="6"/>
       <c r="AA78" s="6"/>
@@ -7813,16 +7824,16 @@
         <v>27</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
@@ -7830,13 +7841,13 @@
         <v>31</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -7846,7 +7857,7 @@
         <v>31</v>
       </c>
       <c r="Q79" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R79" s="6"/>
       <c r="S79" s="6"/>
@@ -7856,19 +7867,19 @@
         <v>195</v>
       </c>
       <c r="W79" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="X79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y79" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Z79" s="6" t="s">
         <v>195</v>
       </c>
       <c r="AA79" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AB79" s="5"/>
       <c r="AC79" s="5"/>
@@ -7884,16 +7895,16 @@
         <v>27</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
@@ -7931,16 +7942,16 @@
         <v>27</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
@@ -7948,13 +7959,13 @@
         <v>116</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J81" s="6" t="s">
         <v>116</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
@@ -7964,7 +7975,7 @@
         <v>116</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R81" s="6"/>
       <c r="S81" s="6"/>
@@ -7976,13 +7987,13 @@
         <v>116</v>
       </c>
       <c r="Y81" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Z81" s="6" t="s">
         <v>116</v>
       </c>
       <c r="AA81" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AB81" s="5"/>
       <c r="AC81" s="5"/>
@@ -7998,40 +8009,40 @@
         <v>27</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J82" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L82" s="6" t="s">
         <v>195</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N82" s="6"/>
       <c r="O82" s="6"/>
@@ -8039,7 +8050,7 @@
         <v>172</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="R82" s="6"/>
       <c r="S82" s="6"/>
@@ -8049,19 +8060,19 @@
         <v>172</v>
       </c>
       <c r="W82" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="X82" s="6" t="s">
         <v>172</v>
       </c>
       <c r="Y82" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Z82" s="6" t="s">
         <v>172</v>
       </c>
       <c r="AA82" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AB82" s="5"/>
       <c r="AC82" s="5"/>
@@ -8077,16 +8088,16 @@
         <v>27</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
@@ -8094,13 +8105,13 @@
         <v>49</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J83" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
@@ -8110,7 +8121,7 @@
         <v>31</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="R83" s="6"/>
       <c r="S83" s="6"/>
@@ -8136,16 +8147,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
@@ -8153,13 +8164,13 @@
         <v>49</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J84" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
@@ -8169,7 +8180,7 @@
         <v>31</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="R84" s="6"/>
       <c r="S84" s="6"/>
@@ -8195,16 +8206,16 @@
         <v>27</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
@@ -8212,13 +8223,13 @@
         <v>49</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J85" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
@@ -8228,7 +8239,7 @@
         <v>31</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="R85" s="6"/>
       <c r="S85" s="6"/>
@@ -8254,16 +8265,16 @@
         <v>27</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
@@ -8271,13 +8282,13 @@
         <v>49</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
@@ -8293,19 +8304,19 @@
         <v>31</v>
       </c>
       <c r="W86" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="X86" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y86" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Z86" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA86" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AB86" s="5"/>
       <c r="AC86" s="5"/>
@@ -8321,16 +8332,16 @@
         <v>27</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
@@ -8338,13 +8349,13 @@
         <v>31</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J87" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
@@ -8354,7 +8365,7 @@
         <v>31</v>
       </c>
       <c r="Q87" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="R87" s="6"/>
       <c r="S87" s="6"/>
@@ -8364,19 +8375,19 @@
         <v>31</v>
       </c>
       <c r="W87" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="X87" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y87" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="Z87" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA87" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AB87" s="5"/>
       <c r="AC87" s="5"/>
@@ -8392,16 +8403,16 @@
         <v>27</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
@@ -8409,13 +8420,13 @@
         <v>49</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J88" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
@@ -8431,19 +8442,19 @@
         <v>31</v>
       </c>
       <c r="W88" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="X88" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y88" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Z88" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA88" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AB88" s="5"/>
       <c r="AC88" s="5"/>
@@ -8459,16 +8470,16 @@
         <v>27</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
@@ -8476,13 +8487,13 @@
         <v>49</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
@@ -8492,7 +8503,7 @@
         <v>31</v>
       </c>
       <c r="Q89" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="R89" s="6"/>
       <c r="S89" s="6"/>
@@ -8502,19 +8513,19 @@
         <v>31</v>
       </c>
       <c r="W89" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="X89" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y89" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Z89" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA89" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AB89" s="5"/>
       <c r="AC89" s="5"/>
@@ -8530,16 +8541,16 @@
         <v>27</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
@@ -8559,19 +8570,19 @@
       <c r="U90" s="6"/>
       <c r="V90" s="6"/>
       <c r="W90" s="8" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="X90" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Y90" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Z90" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA90" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AB90" s="5"/>
       <c r="AC90" s="5"/>
@@ -8587,16 +8598,16 @@
         <v>27</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
@@ -8604,13 +8615,13 @@
         <v>116</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J91" s="6" t="s">
         <v>116</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
@@ -8642,16 +8653,16 @@
         <v>27</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
@@ -8659,19 +8670,19 @@
         <v>31</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J92" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L92" s="6" t="s">
         <v>45</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="N92" s="6"/>
       <c r="O92" s="6"/>
@@ -8701,16 +8712,16 @@
         <v>27</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
@@ -8718,13 +8729,13 @@
         <v>31</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J93" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
@@ -8756,16 +8767,16 @@
         <v>27</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
@@ -8773,19 +8784,19 @@
         <v>31</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J94" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L94" s="6" t="s">
         <v>195</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="N94" s="6"/>
       <c r="O94" s="6"/>
@@ -8815,16 +8826,16 @@
         <v>27</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
@@ -8862,16 +8873,16 @@
         <v>27</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
@@ -8909,16 +8920,16 @@
         <v>27</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
@@ -8926,13 +8937,13 @@
         <v>31</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
@@ -8964,40 +8975,40 @@
         <v>27</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I98" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J98" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K98" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
       <c r="O98" s="6"/>
       <c r="P98" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q98" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>512</v>
       </c>
       <c r="R98" s="6"/>
       <c r="S98" s="6"/>
@@ -9023,48 +9034,48 @@
         <v>27</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G99" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="I99" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="H99" s="6" t="s">
+      <c r="J99" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="L99" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="I99" s="7" t="s">
+      <c r="M99" s="6" t="s">
         <v>517</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="K99" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>519</v>
       </c>
       <c r="N99" s="6"/>
       <c r="O99" s="6"/>
       <c r="P99" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q99" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="Q99" s="6" t="s">
-        <v>520</v>
       </c>
       <c r="R99" s="6"/>
       <c r="S99" s="6"/>
@@ -9074,19 +9085,19 @@
         <v>45</v>
       </c>
       <c r="W99" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="X99" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Y99" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="Z99" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AA99" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AB99" s="5"/>
       <c r="AC99" s="5"/>
@@ -9102,48 +9113,48 @@
         <v>27</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="I100" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="H100" s="6" t="s">
+      <c r="J100" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="L100" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="I100" s="7" t="s">
+      <c r="M100" s="6" t="s">
         <v>527</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="K100" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>529</v>
       </c>
       <c r="N100" s="6"/>
       <c r="O100" s="6"/>
       <c r="P100" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q100" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="R100" s="6"/>
       <c r="S100" s="6"/>
@@ -9153,7 +9164,7 @@
         <v>31</v>
       </c>
       <c r="W100" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="X100" s="6" t="s">
         <v>31</v>
@@ -9165,7 +9176,7 @@
         <v>31</v>
       </c>
       <c r="AA100" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AB100" s="5"/>
       <c r="AC100" s="5"/>
@@ -9181,30 +9192,30 @@
         <v>27</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
@@ -9236,34 +9247,34 @@
         <v>27</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
@@ -9273,7 +9284,7 @@
         <v>195</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="R102" s="6"/>
       <c r="S102" s="6"/>
@@ -9283,7 +9294,7 @@
         <v>45</v>
       </c>
       <c r="W102" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="X102" s="6"/>
       <c r="Y102" s="6"/>
@@ -9303,34 +9314,34 @@
         <v>27</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G103" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="I103" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="H103" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="I103" s="7" t="s">
-        <v>547</v>
-      </c>
       <c r="J103" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
@@ -9364,16 +9375,16 @@
         <v>27</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
@@ -9411,34 +9422,34 @@
         <v>27</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
@@ -9448,7 +9459,7 @@
         <v>45</v>
       </c>
       <c r="Q105" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="R105" s="6"/>
       <c r="S105" s="6"/>
@@ -9458,7 +9469,7 @@
         <v>45</v>
       </c>
       <c r="W105" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="X105" s="6"/>
       <c r="Y105" s="6"/>
@@ -9478,30 +9489,30 @@
         <v>27</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
@@ -9511,7 +9522,7 @@
         <v>31</v>
       </c>
       <c r="Q106" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="R106" s="6"/>
       <c r="S106" s="6"/>
@@ -9521,7 +9532,7 @@
         <v>31</v>
       </c>
       <c r="W106" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X106" s="6"/>
       <c r="Y106" s="6"/>
@@ -9538,7 +9549,7 @@
     </row>
     <row r="107" spans="1:35">
       <c r="A107" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>28</v>
@@ -9615,13 +9626,13 @@
     </row>
     <row r="108" spans="1:35">
       <c r="A108" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>30</v>
@@ -9657,7 +9668,7 @@
         <v>45</v>
       </c>
       <c r="Q108" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>31</v>
@@ -9673,13 +9684,13 @@
         <v>45</v>
       </c>
       <c r="Y108" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Z108" s="6" t="s">
         <v>45</v>
       </c>
       <c r="AA108" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AB108" s="5"/>
       <c r="AC108" s="5"/>
@@ -9692,7 +9703,7 @@
     </row>
     <row r="109" spans="1:35">
       <c r="A109" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>55</v>
@@ -9761,7 +9772,7 @@
     </row>
     <row r="110" spans="1:35">
       <c r="A110" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>62</v>
@@ -9818,7 +9829,7 @@
     </row>
     <row r="111" spans="1:35">
       <c r="A111" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>67</v>
@@ -9865,7 +9876,7 @@
     </row>
     <row r="112" spans="1:35">
       <c r="A112" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>71</v>
@@ -9944,7 +9955,7 @@
     </row>
     <row r="113" spans="1:35">
       <c r="A113" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>74</v>
@@ -9982,7 +9993,7 @@
         <v>45</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>45</v>
@@ -10023,7 +10034,7 @@
     </row>
     <row r="114" spans="1:35">
       <c r="A114" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>85</v>
@@ -10102,7 +10113,7 @@
     </row>
     <row r="115" spans="1:35">
       <c r="A115" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>93</v>
@@ -10126,7 +10137,7 @@
         <v>45</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J115" s="6" t="s">
         <v>45</v>
@@ -10140,19 +10151,19 @@
         <v>45</v>
       </c>
       <c r="O115" s="15" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="P115" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Q115" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S115" s="6" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="T115" s="6"/>
       <c r="U115" s="6"/>
@@ -10162,7 +10173,7 @@
         <v>45</v>
       </c>
       <c r="Y115" s="18" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="Z115" s="8" t="s">
         <v>45</v>
@@ -10181,7 +10192,7 @@
     </row>
     <row r="116" spans="1:35">
       <c r="A116" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>104</v>
@@ -10260,7 +10271,7 @@
     </row>
     <row r="117" spans="1:35">
       <c r="A117" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>106</v>
@@ -10304,7 +10315,7 @@
         <v>31</v>
       </c>
       <c r="S117" s="6" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="T117" s="6"/>
       <c r="U117" s="6"/>
@@ -10333,13 +10344,13 @@
     </row>
     <row r="118" spans="1:35">
       <c r="A118" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>113</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>69</v>
@@ -10400,13 +10411,13 @@
     </row>
     <row r="119" spans="1:35">
       <c r="A119" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>30</v>
@@ -10475,13 +10486,13 @@
     </row>
     <row r="120" spans="1:35">
       <c r="A120" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>30</v>
@@ -10513,7 +10524,7 @@
         <v>31</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>139</v>
@@ -10535,7 +10546,7 @@
         <v>143</v>
       </c>
       <c r="Y120" s="8" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="Z120" s="8" t="s">
         <v>31</v>
@@ -10554,7 +10565,7 @@
     </row>
     <row r="121" spans="1:35">
       <c r="A121" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B121" s="24" t="s">
         <v>162</v>
@@ -10595,7 +10606,7 @@
     </row>
     <row r="122" spans="1:35">
       <c r="A122" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B122" s="24" t="s">
         <v>163</v>
@@ -10636,7 +10647,7 @@
     </row>
     <row r="123" spans="1:35">
       <c r="A123" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B123" s="24" t="s">
         <v>164</v>
@@ -10677,7 +10688,7 @@
     </row>
     <row r="124" spans="1:35">
       <c r="A124" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>165</v>
@@ -10736,7 +10747,7 @@
     </row>
     <row r="125" spans="1:35">
       <c r="A125" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>170</v>
@@ -10754,7 +10765,7 @@
         <v>31</v>
       </c>
       <c r="G125" s="26" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H125" s="26" t="s">
         <v>172</v>
@@ -10799,7 +10810,7 @@
     </row>
     <row r="126" spans="1:35">
       <c r="A126" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>211</v>
@@ -10858,7 +10869,7 @@
     </row>
     <row r="127" spans="1:35">
       <c r="A127" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>217</v>
@@ -10905,7 +10916,7 @@
     </row>
     <row r="128" spans="1:35">
       <c r="A128" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>221</v>
@@ -10952,7 +10963,7 @@
     </row>
     <row r="129" spans="1:35">
       <c r="A129" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>224</v>
@@ -10999,7 +11010,7 @@
     </row>
     <row r="130" spans="1:35">
       <c r="A130" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>227</v>
@@ -11058,7 +11069,7 @@
     </row>
     <row r="131" spans="1:35">
       <c r="A131" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>234</v>
@@ -11094,7 +11105,7 @@
         <v>45</v>
       </c>
       <c r="Q131" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>45</v>
@@ -11121,7 +11132,7 @@
     </row>
     <row r="132" spans="1:35">
       <c r="A132" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>242</v>
@@ -11176,7 +11187,7 @@
     </row>
     <row r="133" spans="1:35">
       <c r="A133" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>235</v>
@@ -11235,13 +11246,13 @@
     </row>
     <row r="134" spans="1:35">
       <c r="A134" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>274</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>69</v>
@@ -11281,7 +11292,7 @@
         <v>45</v>
       </c>
       <c r="AA134" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AB134" s="5"/>
       <c r="AC134" s="5"/>
@@ -11294,13 +11305,13 @@
     </row>
     <row r="135" spans="1:35">
       <c r="A135" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>30</v>
@@ -11314,13 +11325,13 @@
         <v>49</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J135" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K135" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -11340,7 +11351,7 @@
         <v>31</v>
       </c>
       <c r="AA135" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB135" s="5"/>
       <c r="AC135" s="5"/>
@@ -11353,14 +11364,20 @@
     </row>
     <row r="136" spans="1:35">
       <c r="A136" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B136" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
+        <v>285</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
@@ -11394,13 +11411,13 @@
     </row>
     <row r="137" spans="1:35">
       <c r="A137" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B137" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>30</v>
@@ -11414,13 +11431,13 @@
         <v>49</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J137" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K137" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="L137" s="6"/>
       <c r="M137" s="6"/>
@@ -11440,7 +11457,7 @@
         <v>31</v>
       </c>
       <c r="AA137" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AB137" s="5"/>
       <c r="AC137" s="5"/>
@@ -11453,13 +11470,13 @@
     </row>
     <row r="138" spans="1:35">
       <c r="A138" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B138" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>294</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>30</v>
@@ -11489,13 +11506,13 @@
         <v>116</v>
       </c>
       <c r="Y138" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Z138" s="6" t="s">
         <v>116</v>
       </c>
       <c r="AA138" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AB138" s="5"/>
       <c r="AC138" s="5"/>
@@ -11508,19 +11525,19 @@
     </row>
     <row r="139" spans="1:35">
       <c r="A139" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
@@ -11528,13 +11545,13 @@
         <v>116</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J139" s="6" t="s">
         <v>116</v>
       </c>
       <c r="K139" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L139" s="6"/>
       <c r="M139" s="6"/>
@@ -11544,7 +11561,7 @@
         <v>116</v>
       </c>
       <c r="Q139" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R139" s="6"/>
       <c r="S139" s="6"/>
@@ -11556,13 +11573,13 @@
         <v>172</v>
       </c>
       <c r="Y139" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Z139" s="6" t="s">
         <v>172</v>
       </c>
       <c r="AA139" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AB139" s="5"/>
       <c r="AC139" s="5"/>
@@ -11575,37 +11592,37 @@
     </row>
     <row r="140" spans="1:35">
       <c r="A140" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J140" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K140" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L140" s="6"/>
       <c r="M140" s="6"/>
@@ -11615,7 +11632,7 @@
         <v>172</v>
       </c>
       <c r="Q140" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="R140" s="6"/>
       <c r="S140" s="6"/>
@@ -11638,19 +11655,19 @@
     </row>
     <row r="141" spans="1:35">
       <c r="A141" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
@@ -11658,13 +11675,13 @@
         <v>49</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J141" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K141" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L141" s="6"/>
       <c r="M141" s="6"/>
@@ -11674,7 +11691,7 @@
         <v>31</v>
       </c>
       <c r="Q141" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="R141" s="6"/>
       <c r="S141" s="6"/>
@@ -11697,19 +11714,19 @@
     </row>
     <row r="142" spans="1:35">
       <c r="A142" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
@@ -11717,13 +11734,13 @@
         <v>49</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J142" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K142" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L142" s="6"/>
       <c r="M142" s="6"/>
@@ -11733,7 +11750,7 @@
         <v>31</v>
       </c>
       <c r="Q142" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="R142" s="6"/>
       <c r="S142" s="6"/>
@@ -11756,19 +11773,19 @@
     </row>
     <row r="143" spans="1:35">
       <c r="A143" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
@@ -11776,13 +11793,13 @@
         <v>49</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J143" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L143" s="6"/>
       <c r="M143" s="6"/>
@@ -11792,7 +11809,7 @@
         <v>31</v>
       </c>
       <c r="Q143" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="R143" s="6"/>
       <c r="S143" s="6"/>
@@ -11804,13 +11821,13 @@
         <v>31</v>
       </c>
       <c r="Y143" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Z143" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA143" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AB143" s="5"/>
       <c r="AC143" s="5"/>
@@ -11823,19 +11840,19 @@
     </row>
     <row r="144" spans="1:35">
       <c r="A144" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
@@ -11843,13 +11860,13 @@
         <v>49</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J144" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K144" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L144" s="6"/>
       <c r="M144" s="6"/>
@@ -11867,13 +11884,13 @@
         <v>31</v>
       </c>
       <c r="Y144" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Z144" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA144" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AB144" s="5"/>
       <c r="AC144" s="5"/>
@@ -11886,19 +11903,19 @@
     </row>
     <row r="145" spans="1:35">
       <c r="A145" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
@@ -11906,13 +11923,13 @@
         <v>49</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J145" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
@@ -11930,13 +11947,13 @@
         <v>31</v>
       </c>
       <c r="Y145" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Z145" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA145" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AB145" s="5"/>
       <c r="AC145" s="5"/>
@@ -11949,19 +11966,19 @@
     </row>
     <row r="146" spans="1:35">
       <c r="A146" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
@@ -11969,13 +11986,13 @@
         <v>31</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J146" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K146" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L146" s="6"/>
       <c r="M146" s="6"/>
@@ -11985,7 +12002,7 @@
         <v>31</v>
       </c>
       <c r="Q146" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="R146" s="6"/>
       <c r="S146" s="6"/>
@@ -11997,13 +12014,13 @@
         <v>31</v>
       </c>
       <c r="Y146" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Z146" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA146" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AB146" s="5"/>
       <c r="AC146" s="5"/>
@@ -12016,19 +12033,19 @@
     </row>
     <row r="147" spans="1:35">
       <c r="A147" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
@@ -12036,13 +12053,13 @@
         <v>49</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J147" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L147" s="6"/>
       <c r="M147" s="6"/>
@@ -12052,7 +12069,7 @@
         <v>31</v>
       </c>
       <c r="Q147" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="R147" s="6"/>
       <c r="S147" s="6"/>
@@ -12064,13 +12081,13 @@
         <v>31</v>
       </c>
       <c r="Y147" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="Z147" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA147" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AB147" s="5"/>
       <c r="AC147" s="5"/>
@@ -12083,19 +12100,19 @@
     </row>
     <row r="148" spans="1:35">
       <c r="A148" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
@@ -12119,7 +12136,7 @@
         <v>116</v>
       </c>
       <c r="Y148" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="Z148" s="6"/>
       <c r="AA148" s="6"/>
@@ -12134,19 +12151,19 @@
     </row>
     <row r="149" spans="1:35">
       <c r="A149" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>116</v>
@@ -12174,7 +12191,7 @@
         <v>116</v>
       </c>
       <c r="Q149" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R149" s="6"/>
       <c r="S149" s="6"/>
@@ -12186,7 +12203,7 @@
         <v>45</v>
       </c>
       <c r="Y149" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Z149" s="21"/>
       <c r="AA149" s="21"/>
@@ -12201,19 +12218,19 @@
     </row>
     <row r="150" spans="1:35">
       <c r="A150" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B150" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>49</v>
@@ -12225,13 +12242,13 @@
         <v>49</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J150" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K150" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L150" s="6"/>
       <c r="M150" s="6"/>
@@ -12241,7 +12258,7 @@
         <v>49</v>
       </c>
       <c r="Q150" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R150" s="6"/>
       <c r="S150" s="6"/>
@@ -12253,7 +12270,7 @@
         <v>31</v>
       </c>
       <c r="Y150" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="Z150" s="21"/>
       <c r="AA150" s="21"/>
@@ -12268,19 +12285,19 @@
     </row>
     <row r="151" spans="1:35">
       <c r="A151" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B151" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C151" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>49</v>
@@ -12292,13 +12309,13 @@
         <v>49</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J151" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
@@ -12308,7 +12325,7 @@
         <v>49</v>
       </c>
       <c r="Q151" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R151" s="6"/>
       <c r="S151" s="6"/>
@@ -12320,7 +12337,7 @@
         <v>31</v>
       </c>
       <c r="Y151" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Z151" s="21"/>
       <c r="AA151" s="21"/>
@@ -12335,10 +12352,10 @@
     </row>
     <row r="152" spans="1:35">
       <c r="A152" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B152" s="24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
@@ -12376,10 +12393,10 @@
     </row>
     <row r="153" spans="1:35">
       <c r="A153" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B153" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C153" s="6"/>
       <c r="D153" s="6"/>
@@ -12417,10 +12434,10 @@
     </row>
     <row r="154" spans="1:35">
       <c r="A154" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B154" s="24" t="s">
-        <v>381</v>
+        <v>730</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="6"/>
@@ -12458,25 +12475,25 @@
     </row>
     <row r="155" spans="1:35">
       <c r="A155" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H155" s="26" t="s">
         <v>172</v>
@@ -12498,7 +12515,7 @@
         <v>116</v>
       </c>
       <c r="Q155" s="26" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R155" s="26"/>
       <c r="S155" s="26"/>
@@ -12521,19 +12538,19 @@
     </row>
     <row r="156" spans="1:35">
       <c r="A156" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
@@ -12541,13 +12558,13 @@
         <v>116</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J156" s="6" t="s">
         <v>116</v>
       </c>
       <c r="K156" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L156" s="6"/>
       <c r="M156" s="6"/>
@@ -12557,7 +12574,7 @@
         <v>116</v>
       </c>
       <c r="Q156" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R156" s="6"/>
       <c r="S156" s="6"/>
@@ -12569,13 +12586,13 @@
         <v>45</v>
       </c>
       <c r="Y156" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Z156" s="6" t="s">
         <v>45</v>
       </c>
       <c r="AA156" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AB156" s="5"/>
       <c r="AC156" s="5"/>
@@ -12588,37 +12605,37 @@
     </row>
     <row r="157" spans="1:35">
       <c r="A157" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J157" s="6" t="s">
         <v>45</v>
       </c>
       <c r="K157" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
@@ -12626,13 +12643,13 @@
         <v>45</v>
       </c>
       <c r="O157" s="28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="P157" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Q157" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="R157" s="6"/>
       <c r="S157" s="6"/>
@@ -12644,13 +12661,13 @@
         <v>31</v>
       </c>
       <c r="Y157" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Z157" s="6" t="s">
         <v>31</v>
       </c>
       <c r="AA157" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AB157" s="5"/>
       <c r="AC157" s="5"/>
@@ -12663,37 +12680,37 @@
     </row>
     <row r="158" spans="1:35">
       <c r="A158" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J158" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
@@ -12701,13 +12718,13 @@
         <v>31</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>31</v>
       </c>
       <c r="Q158" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R158" s="6"/>
       <c r="S158" s="6"/>
@@ -12719,13 +12736,13 @@
         <v>45</v>
       </c>
       <c r="Y158" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Z158" s="6" t="s">
         <v>45</v>
       </c>
       <c r="AA158" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AB158" s="5"/>
       <c r="AC158" s="5"/>
@@ -12738,37 +12755,37 @@
     </row>
     <row r="159" spans="1:35">
       <c r="A159" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H159" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J159" s="6" t="s">
         <v>45</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L159" s="6"/>
       <c r="M159" s="6"/>
@@ -12776,13 +12793,13 @@
         <v>45</v>
       </c>
       <c r="O159" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P159" s="6" t="s">
         <v>45</v>
       </c>
       <c r="Q159" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="R159" s="6"/>
       <c r="S159" s="6"/>
@@ -12796,7 +12813,7 @@
         <v>31</v>
       </c>
       <c r="AA159" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AB159" s="5"/>
       <c r="AC159" s="5"/>
@@ -12809,37 +12826,37 @@
     </row>
     <row r="160" spans="1:35">
       <c r="A160" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H160" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J160" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K160" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L160" s="6"/>
       <c r="M160" s="6"/>
@@ -12849,7 +12866,7 @@
         <v>31</v>
       </c>
       <c r="Q160" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R160" s="6"/>
       <c r="S160" s="6"/>
@@ -12872,19 +12889,19 @@
     </row>
     <row r="161" spans="1:35">
       <c r="A161" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
@@ -12892,23 +12909,23 @@
         <v>116</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J161" s="6" t="s">
         <v>116</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
       <c r="O161" s="6"/>
       <c r="P161" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Q161" s="6" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="R161" s="6"/>
       <c r="S161" s="6"/>
@@ -12931,19 +12948,19 @@
     </row>
     <row r="162" spans="1:35">
       <c r="A162" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
@@ -12951,23 +12968,23 @@
         <v>31</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J162" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K162" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L162" s="6"/>
       <c r="M162" s="6"/>
       <c r="N162" s="6"/>
       <c r="O162" s="6"/>
       <c r="P162" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q162" s="6" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="R162" s="6"/>
       <c r="S162" s="6"/>
@@ -12990,19 +13007,19 @@
     </row>
     <row r="163" spans="1:35">
       <c r="A163" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
@@ -13010,13 +13027,13 @@
         <v>31</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J163" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
@@ -13045,19 +13062,19 @@
     </row>
     <row r="164" spans="1:35">
       <c r="A164" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
@@ -13065,13 +13082,13 @@
         <v>31</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J164" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K164" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
@@ -13081,7 +13098,7 @@
         <v>31</v>
       </c>
       <c r="Q164" s="6" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="R164" s="6"/>
       <c r="S164" s="6"/>
@@ -13104,19 +13121,19 @@
     </row>
     <row r="165" spans="1:35">
       <c r="A165" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
@@ -13151,19 +13168,19 @@
     </row>
     <row r="166" spans="1:35">
       <c r="A166" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
@@ -13198,19 +13215,19 @@
     </row>
     <row r="167" spans="1:35">
       <c r="A167" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
@@ -13218,13 +13235,13 @@
         <v>31</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J167" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K167" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
@@ -13253,43 +13270,43 @@
     </row>
     <row r="168" spans="1:35">
       <c r="A168" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
       <c r="H168" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="I168" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="I168" s="7" t="s">
-        <v>301</v>
-      </c>
       <c r="J168" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="K168" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="K168" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
       <c r="N168" s="6"/>
       <c r="O168" s="6"/>
       <c r="P168" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q168" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="R168" s="6"/>
       <c r="S168" s="6"/>
@@ -13298,16 +13315,16 @@
       <c r="V168" s="6"/>
       <c r="W168" s="6"/>
       <c r="X168" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y168" s="8" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Z168" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AA168" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="AA168" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="AB168" s="5"/>
       <c r="AC168" s="5"/>
@@ -13320,73 +13337,73 @@
     </row>
     <row r="169" spans="1:35">
       <c r="A169" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G169" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="H169" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="H169" s="6" t="s">
+      <c r="I169" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="I169" s="7" t="s">
-        <v>310</v>
-      </c>
       <c r="J169" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="K169" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="K169" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
       <c r="N169" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="O169" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="O169" s="6" t="s">
-        <v>312</v>
-      </c>
       <c r="P169" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="Q169" s="6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="R169" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S169" s="6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="T169" s="6"/>
       <c r="U169" s="6"/>
       <c r="V169" s="6"/>
       <c r="W169" s="6"/>
       <c r="X169" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Y169" s="8" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="Z169" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AA169" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AB169" s="5"/>
       <c r="AC169" s="5"/>
@@ -13399,19 +13416,19 @@
     </row>
     <row r="170" spans="1:35">
       <c r="A170" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>31</v>
@@ -13420,30 +13437,30 @@
         <v>32</v>
       </c>
       <c r="H170" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I170" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="I170" s="7" t="s">
-        <v>325</v>
-      </c>
       <c r="J170" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K170" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="K170" s="7" t="s">
-        <v>325</v>
       </c>
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
       <c r="N170" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O170" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="O170" s="6" t="s">
-        <v>327</v>
-      </c>
       <c r="P170" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q170" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="R170" s="6" t="s">
         <v>31</v>
@@ -13470,10 +13487,10 @@
     </row>
     <row r="171" spans="1:35">
       <c r="A171" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B171" s="24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C171" s="6"/>
       <c r="D171" s="6"/>
@@ -13511,33 +13528,33 @@
     </row>
     <row r="172" spans="1:35">
       <c r="A172" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B172" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C172" s="6" t="s">
         <v>346</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>347</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="I172" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="I172" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="J172" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="K172" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="K172" s="7" t="s">
-        <v>339</v>
       </c>
       <c r="L172" s="6"/>
       <c r="M172" s="6"/>
@@ -13549,7 +13566,7 @@
         <v>45</v>
       </c>
       <c r="S172" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T172" s="6"/>
       <c r="U172" s="6"/>
@@ -13570,33 +13587,33 @@
     </row>
     <row r="173" spans="1:35">
       <c r="A173" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
@@ -13625,33 +13642,33 @@
     </row>
     <row r="174" spans="1:35">
       <c r="A174" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K174" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L174" s="6"/>
       <c r="M174" s="6"/>
@@ -13680,49 +13697,49 @@
     </row>
     <row r="175" spans="1:35">
       <c r="A175" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B175" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C175" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
       <c r="H175" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
       <c r="N175" s="6"/>
       <c r="O175" s="6"/>
       <c r="P175" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q175" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="R175" s="6" t="s">
         <v>45</v>
       </c>
       <c r="S175" s="6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="T175" s="6"/>
       <c r="U175" s="6"/>
@@ -13743,19 +13760,19 @@
     </row>
     <row r="176" spans="1:35">
       <c r="A176" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
@@ -13776,10 +13793,10 @@
       <c r="N176" s="6"/>
       <c r="O176" s="6"/>
       <c r="P176" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q176" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="R176" s="6"/>
       <c r="S176" s="6"/>
@@ -13802,19 +13819,19 @@
     </row>
     <row r="177" spans="1:35">
       <c r="A177" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
@@ -13822,23 +13839,23 @@
         <v>49</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J177" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="L177" s="6"/>
       <c r="M177" s="6"/>
       <c r="N177" s="6"/>
       <c r="O177" s="6"/>
       <c r="P177" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="Q177" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="R177" s="6"/>
       <c r="S177" s="6"/>
@@ -13861,19 +13878,19 @@
     </row>
     <row r="178" spans="1:35">
       <c r="A178" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
@@ -13881,13 +13898,13 @@
         <v>49</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="J178" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K178" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="L178" s="6"/>
       <c r="M178" s="6"/>
@@ -13897,7 +13914,7 @@
         <v>31</v>
       </c>
       <c r="Q178" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="R178" s="6"/>
       <c r="S178" s="6"/>
@@ -13920,19 +13937,19 @@
     </row>
     <row r="179" spans="1:35">
       <c r="A179" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
@@ -13967,19 +13984,19 @@
     </row>
     <row r="180" spans="1:35">
       <c r="A180" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
@@ -14003,7 +14020,7 @@
         <v>116</v>
       </c>
       <c r="Q180" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="R180" s="6"/>
       <c r="S180" s="6"/>
@@ -14026,19 +14043,19 @@
     </row>
     <row r="181" spans="1:35">
       <c r="A181" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
@@ -14046,13 +14063,13 @@
         <v>49</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J181" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="L181" s="6"/>
       <c r="M181" s="6"/>
@@ -14062,7 +14079,7 @@
         <v>45</v>
       </c>
       <c r="Q181" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="R181" s="6" t="s">
         <v>31</v>
@@ -14089,37 +14106,37 @@
     </row>
     <row r="182" spans="1:35">
       <c r="A182" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H182" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="J182" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K182" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -14150,19 +14167,19 @@
     </row>
     <row r="183" spans="1:35">
       <c r="A183" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
@@ -14180,7 +14197,7 @@
         <v>45</v>
       </c>
       <c r="S183" s="6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="T183" s="6"/>
       <c r="U183" s="6"/>
@@ -14201,33 +14218,33 @@
     </row>
     <row r="184" spans="1:35">
       <c r="A184" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
       <c r="H184" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K184" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -14256,37 +14273,37 @@
     </row>
     <row r="185" spans="1:35">
       <c r="A185" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J185" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K185" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -14296,7 +14313,7 @@
         <v>195</v>
       </c>
       <c r="Q185" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="R185" s="6"/>
       <c r="S185" s="6"/>
@@ -14319,37 +14336,37 @@
     </row>
     <row r="186" spans="1:35">
       <c r="A186" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="I186" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="H186" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="I186" s="7" t="s">
-        <v>547</v>
-      </c>
       <c r="J186" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K186" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -14380,19 +14397,19 @@
     </row>
     <row r="187" spans="1:35">
       <c r="A187" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
@@ -14427,37 +14444,37 @@
     </row>
     <row r="188" spans="1:35">
       <c r="A188" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K188" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="L188" s="6"/>
       <c r="M188" s="6"/>
@@ -14467,7 +14484,7 @@
         <v>45</v>
       </c>
       <c r="Q188" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="R188" s="6"/>
       <c r="S188" s="6"/>
@@ -14490,33 +14507,33 @@
     </row>
     <row r="189" spans="1:35">
       <c r="A189" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K189" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L189" s="6"/>
       <c r="M189" s="6"/>
@@ -14526,7 +14543,7 @@
         <v>31</v>
       </c>
       <c r="Q189" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="R189" s="6"/>
       <c r="S189" s="6"/>
@@ -14549,43 +14566,43 @@
     </row>
     <row r="190" spans="1:35">
       <c r="A190" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
       <c r="H190" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I190" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J190" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K190" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L190" s="6"/>
       <c r="M190" s="6"/>
       <c r="N190" s="6"/>
       <c r="O190" s="6"/>
       <c r="P190" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q190" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="Q190" s="6" t="s">
-        <v>512</v>
       </c>
       <c r="R190" s="6"/>
       <c r="S190" s="6"/>
@@ -14597,13 +14614,13 @@
         <v>45</v>
       </c>
       <c r="Y190" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="Z190" s="9" t="s">
         <v>45</v>
       </c>
       <c r="AA190" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AB190" s="5"/>
       <c r="AC190" s="5"/>
@@ -14616,47 +14633,47 @@
     </row>
     <row r="191" spans="1:35">
       <c r="A191" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G191" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="H191" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="I191" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="H191" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="I191" s="7" t="s">
-        <v>517</v>
-      </c>
       <c r="J191" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="L191" s="6"/>
       <c r="M191" s="6"/>
       <c r="N191" s="6"/>
       <c r="O191" s="6"/>
       <c r="P191" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q191" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="Q191" s="6" t="s">
-        <v>520</v>
       </c>
       <c r="R191" s="6"/>
       <c r="S191" s="6"/>
@@ -14674,7 +14691,7 @@
         <v>31</v>
       </c>
       <c r="AA191" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AB191" s="5"/>
       <c r="AC191" s="5"/>
@@ -14687,47 +14704,47 @@
     </row>
     <row r="192" spans="1:35">
       <c r="A192" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="I192" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="H192" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="I192" s="7" t="s">
-        <v>527</v>
-      </c>
       <c r="J192" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K192" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
       <c r="N192" s="6"/>
       <c r="O192" s="6"/>
       <c r="P192" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q192" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="R192" s="6"/>
       <c r="S192" s="6"/>
@@ -14750,7 +14767,7 @@
     </row>
     <row r="193" spans="1:35">
       <c r="A193" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>28</v>
@@ -14792,7 +14809,7 @@
         <v>31</v>
       </c>
       <c r="U193" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="V193" s="6"/>
       <c r="W193" s="6"/>
@@ -14811,13 +14828,13 @@
     </row>
     <row r="194" spans="1:35">
       <c r="A194" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>30</v>
@@ -14845,7 +14862,7 @@
         <v>45</v>
       </c>
       <c r="Q194" s="6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="R194" s="6"/>
       <c r="S194" s="6"/>
@@ -14853,7 +14870,7 @@
         <v>45</v>
       </c>
       <c r="U194" s="6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="V194" s="6"/>
       <c r="W194" s="6"/>
@@ -14872,13 +14889,13 @@
     </row>
     <row r="195" spans="1:35">
       <c r="A195" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D195" s="6" t="s">
         <v>30</v>
@@ -14910,7 +14927,7 @@
         <v>31</v>
       </c>
       <c r="U195" s="6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="V195" s="6"/>
       <c r="W195" s="6"/>
@@ -14929,7 +14946,7 @@
     </row>
     <row r="196" spans="1:35">
       <c r="A196" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>62</v>
@@ -14978,7 +14995,7 @@
     </row>
     <row r="197" spans="1:35">
       <c r="A197" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>67</v>
@@ -15025,7 +15042,7 @@
     </row>
     <row r="198" spans="1:35">
       <c r="A198" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>71</v>
@@ -15088,7 +15105,7 @@
     </row>
     <row r="199" spans="1:35">
       <c r="A199" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>74</v>
@@ -15132,7 +15149,7 @@
         <v>45</v>
       </c>
       <c r="U199" s="6" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="V199" s="6"/>
       <c r="W199" s="6"/>
@@ -15151,7 +15168,7 @@
     </row>
     <row r="200" spans="1:35">
       <c r="A200" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>85</v>
@@ -15214,7 +15231,7 @@
     </row>
     <row r="201" spans="1:35">
       <c r="A201" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>93</v>
@@ -15238,7 +15255,7 @@
         <v>45</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
@@ -15250,7 +15267,7 @@
         <v>45</v>
       </c>
       <c r="Q201" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="R201" s="6"/>
       <c r="S201" s="6"/>
@@ -15258,7 +15275,7 @@
         <v>31</v>
       </c>
       <c r="U201" s="35" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="V201" s="6"/>
       <c r="W201" s="6"/>
@@ -15277,7 +15294,7 @@
     </row>
     <row r="202" spans="1:35">
       <c r="A202" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>104</v>
@@ -15321,7 +15338,7 @@
         <v>31</v>
       </c>
       <c r="U202" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="V202" s="6"/>
       <c r="W202" s="6"/>
@@ -15340,7 +15357,7 @@
     </row>
     <row r="203" spans="1:35">
       <c r="A203" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>106</v>
@@ -15376,7 +15393,7 @@
         <v>31</v>
       </c>
       <c r="Q203" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R203" s="6"/>
       <c r="S203" s="6"/>
@@ -15399,13 +15416,13 @@
     </row>
     <row r="204" spans="1:35">
       <c r="A204" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>113</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>69</v>
@@ -15458,13 +15475,13 @@
     </row>
     <row r="205" spans="1:35">
       <c r="A205" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>30</v>
@@ -15502,7 +15519,7 @@
         <v>45</v>
       </c>
       <c r="U205" s="6" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="V205" s="6"/>
       <c r="W205" s="6"/>
@@ -15521,13 +15538,13 @@
     </row>
     <row r="206" spans="1:35">
       <c r="A206" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>30</v>
@@ -15565,7 +15582,7 @@
         <v>31</v>
       </c>
       <c r="U206" s="6" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="V206" s="6"/>
       <c r="W206" s="6"/>
@@ -15584,7 +15601,7 @@
     </row>
     <row r="207" spans="1:35">
       <c r="A207" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B207" s="24" t="s">
         <v>162</v>
@@ -15625,7 +15642,7 @@
     </row>
     <row r="208" spans="1:35">
       <c r="A208" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B208" s="24" t="s">
         <v>163</v>
@@ -15666,7 +15683,7 @@
     </row>
     <row r="209" spans="1:35">
       <c r="A209" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B209" s="24" t="s">
         <v>164</v>
@@ -15707,7 +15724,7 @@
     </row>
     <row r="210" spans="1:35">
       <c r="A210" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>165</v>
@@ -15758,7 +15775,7 @@
     </row>
     <row r="211" spans="1:35">
       <c r="A211" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>170</v>
@@ -15778,7 +15795,7 @@
         <v>49</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="J211" s="6"/>
       <c r="K211" s="6"/>
@@ -15809,19 +15826,19 @@
     </row>
     <row r="212" spans="1:35">
       <c r="A212" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>116</v>
@@ -15845,7 +15862,7 @@
         <v>116</v>
       </c>
       <c r="Q212" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R212" s="6"/>
       <c r="S212" s="6"/>
@@ -15868,19 +15885,19 @@
     </row>
     <row r="213" spans="1:35">
       <c r="A213" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B213" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C213" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="C213" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>49</v>
@@ -15892,7 +15909,7 @@
         <v>49</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
@@ -15904,7 +15921,7 @@
         <v>49</v>
       </c>
       <c r="Q213" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R213" s="6"/>
       <c r="S213" s="6"/>
@@ -15927,19 +15944,19 @@
     </row>
     <row r="214" spans="1:35">
       <c r="A214" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B214" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C214" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="C214" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>49</v>
@@ -15951,7 +15968,7 @@
         <v>49</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J214" s="6"/>
       <c r="K214" s="6"/>
@@ -15963,7 +15980,7 @@
         <v>49</v>
       </c>
       <c r="Q214" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R214" s="6"/>
       <c r="S214" s="6"/>
@@ -15986,10 +16003,10 @@
     </row>
     <row r="215" spans="1:35">
       <c r="A215" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B215" s="24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C215" s="6"/>
       <c r="D215" s="6"/>
@@ -16027,10 +16044,10 @@
     </row>
     <row r="216" spans="1:35">
       <c r="A216" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B216" s="24" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="6"/>
@@ -16068,10 +16085,10 @@
     </row>
     <row r="217" spans="1:35">
       <c r="A217" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B217" s="24" t="s">
-        <v>381</v>
+        <v>730</v>
       </c>
       <c r="C217" s="6"/>
       <c r="D217" s="6"/>
@@ -16109,31 +16126,31 @@
     </row>
     <row r="218" spans="1:35">
       <c r="A218" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H218" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="J218" s="6"/>
       <c r="K218" s="6"/>
@@ -16145,7 +16162,7 @@
         <v>49</v>
       </c>
       <c r="Q218" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="R218" s="6"/>
       <c r="S218" s="6"/>
@@ -16168,27 +16185,27 @@
     </row>
     <row r="219" spans="1:35">
       <c r="A219" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F219" s="6"/>
       <c r="G219" s="6"/>
       <c r="H219" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="I219" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="I219" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="J219" s="6"/>
       <c r="K219" s="6"/>
@@ -16197,10 +16214,10 @@
       <c r="N219" s="6"/>
       <c r="O219" s="6"/>
       <c r="P219" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="Q219" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="R219" s="6"/>
       <c r="S219" s="6"/>
@@ -16223,31 +16240,31 @@
     </row>
     <row r="220" spans="1:35">
       <c r="A220" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D220" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H220" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="I220" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="I220" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="J220" s="6"/>
       <c r="K220" s="6"/>
@@ -16256,10 +16273,10 @@
       <c r="N220" s="6"/>
       <c r="O220" s="6"/>
       <c r="P220" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="Q220" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="R220" s="6"/>
       <c r="S220" s="6"/>
@@ -16267,7 +16284,7 @@
         <v>45</v>
       </c>
       <c r="U220" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="V220" s="6"/>
       <c r="W220" s="6"/>
@@ -16286,31 +16303,31 @@
     </row>
     <row r="221" spans="1:35">
       <c r="A221" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G221" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H221" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J221" s="6"/>
       <c r="K221" s="6"/>
@@ -16319,10 +16336,10 @@
       <c r="N221" s="6"/>
       <c r="O221" s="6"/>
       <c r="P221" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="Q221" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="R221" s="6"/>
       <c r="S221" s="6"/>
@@ -16330,7 +16347,7 @@
         <v>31</v>
       </c>
       <c r="U221" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="V221" s="6"/>
       <c r="W221" s="6"/>
@@ -16349,10 +16366,10 @@
     </row>
     <row r="222" spans="1:35">
       <c r="A222" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B222" s="24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="6"/>
@@ -16390,27 +16407,27 @@
     </row>
     <row r="223" spans="1:35">
       <c r="A223" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D223" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F223" s="6"/>
       <c r="G223" s="6"/>
       <c r="H223" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="I223" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="I223" s="7" t="s">
-        <v>339</v>
       </c>
       <c r="J223" s="6"/>
       <c r="K223" s="6"/>
@@ -16441,27 +16458,27 @@
     </row>
     <row r="224" spans="1:35">
       <c r="A224" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D224" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F224" s="6"/>
       <c r="G224" s="6"/>
       <c r="H224" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I224" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J224" s="6"/>
       <c r="K224" s="6"/>
@@ -16492,27 +16509,27 @@
     </row>
     <row r="225" spans="1:35">
       <c r="A225" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D225" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F225" s="6"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J225" s="6"/>
       <c r="K225" s="6"/>
@@ -16543,27 +16560,27 @@
     </row>
     <row r="226" spans="1:35">
       <c r="A226" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B226" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C226" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="C226" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="D226" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F226" s="6"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I226" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J226" s="6"/>
       <c r="K226" s="6"/>
@@ -16572,10 +16589,10 @@
       <c r="N226" s="6"/>
       <c r="O226" s="6"/>
       <c r="P226" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="Q226" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="R226" s="6"/>
       <c r="S226" s="6"/>
@@ -16598,7 +16615,7 @@
     </row>
     <row r="227" spans="1:35">
       <c r="A227" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>211</v>
@@ -16632,7 +16649,7 @@
         <v>116</v>
       </c>
       <c r="Q227" s="6" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="R227" s="6"/>
       <c r="S227" s="6"/>
@@ -16655,7 +16672,7 @@
     </row>
     <row r="228" spans="1:35">
       <c r="A228" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>217</v>
@@ -16702,7 +16719,7 @@
     </row>
     <row r="229" spans="1:35">
       <c r="A229" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>221</v>
@@ -16749,7 +16766,7 @@
     </row>
     <row r="230" spans="1:35">
       <c r="A230" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>224</v>
@@ -16796,7 +16813,7 @@
     </row>
     <row r="231" spans="1:35">
       <c r="A231" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>227</v>
@@ -16816,7 +16833,7 @@
         <v>49</v>
       </c>
       <c r="I231" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="J231" s="6"/>
       <c r="K231" s="6"/>
@@ -16828,7 +16845,7 @@
         <v>31</v>
       </c>
       <c r="Q231" s="6" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="R231" s="6"/>
       <c r="S231" s="6"/>
@@ -16851,7 +16868,7 @@
     </row>
     <row r="232" spans="1:35">
       <c r="A232" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>234</v>
@@ -16871,7 +16888,7 @@
         <v>49</v>
       </c>
       <c r="I232" s="7" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J232" s="6"/>
       <c r="K232" s="6"/>
@@ -16883,7 +16900,7 @@
         <v>45</v>
       </c>
       <c r="Q232" s="6" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="R232" s="6"/>
       <c r="S232" s="6"/>
@@ -16906,7 +16923,7 @@
     </row>
     <row r="233" spans="1:35">
       <c r="A233" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>242</v>
@@ -16953,7 +16970,7 @@
     </row>
     <row r="234" spans="1:35">
       <c r="A234" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>235</v>
@@ -16973,7 +16990,7 @@
         <v>49</v>
       </c>
       <c r="I234" s="7" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J234" s="6"/>
       <c r="K234" s="6"/>
@@ -17004,13 +17021,13 @@
     </row>
     <row r="235" spans="1:35">
       <c r="A235" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>274</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D235" s="6" t="s">
         <v>69</v>
@@ -17032,7 +17049,7 @@
         <v>116</v>
       </c>
       <c r="Q235" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="R235" s="6"/>
       <c r="S235" s="6"/>
@@ -17055,13 +17072,13 @@
     </row>
     <row r="236" spans="1:35">
       <c r="A236" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D236" s="6" t="s">
         <v>30</v>
@@ -17083,7 +17100,7 @@
         <v>45</v>
       </c>
       <c r="Q236" s="6" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="R236" s="6"/>
       <c r="S236" s="6"/>
@@ -17106,14 +17123,20 @@
     </row>
     <row r="237" spans="1:35">
       <c r="A237" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B237" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="C237" s="6"/>
-      <c r="D237" s="6"/>
-      <c r="E237" s="6"/>
+        <v>285</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="F237" s="6"/>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -17147,13 +17170,13 @@
     </row>
     <row r="238" spans="1:35">
       <c r="A238" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B238" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C238" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="C238" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>30</v>
@@ -17175,7 +17198,7 @@
         <v>31</v>
       </c>
       <c r="Q238" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="R238" s="6"/>
       <c r="S238" s="6"/>
@@ -17198,13 +17221,13 @@
     </row>
     <row r="239" spans="1:35">
       <c r="A239" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B239" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C239" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="C239" s="6" t="s">
-        <v>294</v>
       </c>
       <c r="D239" s="6" t="s">
         <v>30</v>
@@ -17245,19 +17268,19 @@
     </row>
     <row r="240" spans="1:35">
       <c r="A240" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D240" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F240" s="6"/>
       <c r="G240" s="6"/>
@@ -17265,7 +17288,7 @@
         <v>116</v>
       </c>
       <c r="I240" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J240" s="6"/>
       <c r="K240" s="6"/>
@@ -17296,31 +17319,31 @@
     </row>
     <row r="241" spans="1:35">
       <c r="A241" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F241" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G241" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H241" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I241" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
@@ -17351,19 +17374,19 @@
     </row>
     <row r="242" spans="1:35">
       <c r="A242" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D242" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F242" s="6"/>
       <c r="G242" s="6"/>
@@ -17371,7 +17394,7 @@
         <v>49</v>
       </c>
       <c r="I242" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J242" s="6"/>
       <c r="K242" s="6"/>
@@ -17402,19 +17425,19 @@
     </row>
     <row r="243" spans="1:35">
       <c r="A243" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D243" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F243" s="6"/>
       <c r="G243" s="6"/>
@@ -17422,7 +17445,7 @@
         <v>49</v>
       </c>
       <c r="I243" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J243" s="6"/>
       <c r="K243" s="6"/>
@@ -17453,19 +17476,19 @@
     </row>
     <row r="244" spans="1:35">
       <c r="A244" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D244" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F244" s="6"/>
       <c r="G244" s="6"/>
@@ -17473,7 +17496,7 @@
         <v>49</v>
       </c>
       <c r="I244" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J244" s="6"/>
       <c r="K244" s="6"/>
@@ -17504,19 +17527,19 @@
     </row>
     <row r="245" spans="1:35">
       <c r="A245" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D245" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F245" s="6"/>
       <c r="G245" s="6"/>
@@ -17524,7 +17547,7 @@
         <v>49</v>
       </c>
       <c r="I245" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J245" s="6"/>
       <c r="K245" s="6"/>
@@ -17555,19 +17578,19 @@
     </row>
     <row r="246" spans="1:35">
       <c r="A246" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D246" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F246" s="6"/>
       <c r="G246" s="6"/>
@@ -17575,7 +17598,7 @@
         <v>49</v>
       </c>
       <c r="I246" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="6"/>
@@ -17606,19 +17629,19 @@
     </row>
     <row r="247" spans="1:35">
       <c r="A247" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D247" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F247" s="6"/>
       <c r="G247" s="6"/>
@@ -17626,7 +17649,7 @@
         <v>31</v>
       </c>
       <c r="I247" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J247" s="6"/>
       <c r="K247" s="6"/>
@@ -17657,19 +17680,19 @@
     </row>
     <row r="248" spans="1:35">
       <c r="A248" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D248" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F248" s="6"/>
       <c r="G248" s="6"/>
@@ -17677,7 +17700,7 @@
         <v>49</v>
       </c>
       <c r="I248" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="6"/>
@@ -17708,19 +17731,19 @@
     </row>
     <row r="249" spans="1:35">
       <c r="A249" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D249" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F249" s="6"/>
       <c r="G249" s="6"/>
@@ -17755,19 +17778,19 @@
     </row>
     <row r="250" spans="1:35">
       <c r="A250" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D250" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F250" s="6"/>
       <c r="G250" s="6"/>
@@ -17787,7 +17810,7 @@
         <v>116</v>
       </c>
       <c r="Q250" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="R250" s="6"/>
       <c r="S250" s="6"/>
@@ -17810,19 +17833,19 @@
     </row>
     <row r="251" spans="1:35">
       <c r="A251" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D251" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F251" s="6"/>
       <c r="G251" s="6"/>
@@ -17830,7 +17853,7 @@
         <v>49</v>
       </c>
       <c r="I251" s="7" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J251" s="6"/>
       <c r="K251" s="6"/>
@@ -17842,7 +17865,7 @@
         <v>31</v>
       </c>
       <c r="Q251" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="R251" s="6"/>
       <c r="S251" s="6"/>
@@ -17865,19 +17888,19 @@
     </row>
     <row r="252" spans="1:35">
       <c r="A252" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D252" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F252" s="6"/>
       <c r="G252" s="6"/>
@@ -17885,7 +17908,7 @@
         <v>49</v>
       </c>
       <c r="I252" s="7" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J252" s="6"/>
       <c r="K252" s="6"/>
@@ -17897,7 +17920,7 @@
         <v>31</v>
       </c>
       <c r="Q252" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R252" s="6"/>
       <c r="S252" s="6"/>
@@ -17920,19 +17943,19 @@
     </row>
     <row r="253" spans="1:35">
       <c r="A253" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D253" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F253" s="6"/>
       <c r="G253" s="6"/>
@@ -17940,7 +17963,7 @@
         <v>49</v>
       </c>
       <c r="I253" s="7" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J253" s="6"/>
       <c r="K253" s="6"/>
@@ -17952,7 +17975,7 @@
         <v>31</v>
       </c>
       <c r="Q253" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="R253" s="6"/>
       <c r="S253" s="6"/>
@@ -17975,19 +17998,19 @@
     </row>
     <row r="254" spans="1:35">
       <c r="A254" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D254" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F254" s="6"/>
       <c r="G254" s="6"/>
@@ -18022,19 +18045,19 @@
     </row>
     <row r="255" spans="1:35">
       <c r="A255" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D255" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F255" s="6"/>
       <c r="G255" s="6"/>
@@ -18042,7 +18065,7 @@
         <v>49</v>
       </c>
       <c r="I255" s="7" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="J255" s="6"/>
       <c r="K255" s="6"/>
@@ -18054,7 +18077,7 @@
         <v>31</v>
       </c>
       <c r="Q255" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="R255" s="6"/>
       <c r="S255" s="6"/>
@@ -18077,19 +18100,19 @@
     </row>
     <row r="256" spans="1:35">
       <c r="A256" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D256" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F256" s="6"/>
       <c r="G256" s="6"/>
@@ -18105,7 +18128,7 @@
         <v>31</v>
       </c>
       <c r="Q256" s="6" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="R256" s="6"/>
       <c r="S256" s="6"/>
@@ -18128,17 +18151,17 @@
     </row>
     <row r="257" spans="1:35">
       <c r="A257" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C257" s="6"/>
       <c r="D257" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F257" s="6"/>
       <c r="G257" s="20"/>
@@ -18146,7 +18169,7 @@
         <v>49</v>
       </c>
       <c r="I257" s="7" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="J257" s="6"/>
       <c r="K257" s="6"/>
@@ -18158,7 +18181,7 @@
         <v>31</v>
       </c>
       <c r="Q257" s="6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="R257" s="6"/>
       <c r="S257" s="6"/>
@@ -18181,17 +18204,17 @@
     </row>
     <row r="258" spans="1:35">
       <c r="A258" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C258" s="6"/>
       <c r="D258" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F258" s="6"/>
       <c r="G258" s="6"/>
@@ -18199,7 +18222,7 @@
         <v>49</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="J258" s="6"/>
       <c r="K258" s="6"/>
@@ -18230,31 +18253,31 @@
     </row>
     <row r="259" spans="1:35">
       <c r="A259" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D259" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F259" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G259" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H259" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J259" s="6"/>
       <c r="K259" s="6"/>
@@ -18285,25 +18308,25 @@
     </row>
     <row r="260" spans="1:35">
       <c r="A260" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G260" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H260" s="6"/>
       <c r="I260" s="7"/>
@@ -18336,17 +18359,17 @@
     </row>
     <row r="261" spans="1:35">
       <c r="A261" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C261" s="6"/>
       <c r="D261" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F261" s="6"/>
       <c r="G261" s="6"/>
@@ -18364,7 +18387,7 @@
       <c r="O261" s="6"/>
       <c r="P261" s="6"/>
       <c r="Q261" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="R261" s="6"/>
       <c r="S261" s="6"/>
@@ -18387,17 +18410,17 @@
     </row>
     <row r="262" spans="1:35">
       <c r="A262" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C262" s="6"/>
       <c r="D262" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F262" s="6"/>
       <c r="G262" s="6"/>
@@ -18405,7 +18428,7 @@
         <v>49</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J262" s="6"/>
       <c r="K262" s="6"/>
@@ -18414,10 +18437,10 @@
       <c r="N262" s="6"/>
       <c r="O262" s="6"/>
       <c r="P262" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q262" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="R262" s="6"/>
       <c r="S262" s="6"/>
@@ -18440,17 +18463,17 @@
     </row>
     <row r="263" spans="1:35">
       <c r="A263" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C263" s="6"/>
       <c r="D263" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E263" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F263" s="6"/>
       <c r="G263" s="6"/>
@@ -18458,7 +18481,7 @@
         <v>49</v>
       </c>
       <c r="I263" s="7" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J263" s="6"/>
       <c r="K263" s="6"/>
@@ -18467,10 +18490,10 @@
       <c r="N263" s="6"/>
       <c r="O263" s="6"/>
       <c r="P263" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q263" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="R263" s="6"/>
       <c r="S263" s="6"/>
@@ -18493,19 +18516,19 @@
     </row>
     <row r="264" spans="1:35">
       <c r="A264" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D264" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F264" s="6"/>
       <c r="G264" s="6"/>
@@ -18513,7 +18536,7 @@
         <v>116</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J264" s="6"/>
       <c r="K264" s="6"/>
@@ -18525,7 +18548,7 @@
         <v>116</v>
       </c>
       <c r="Q264" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R264" s="6"/>
       <c r="S264" s="6"/>
@@ -18548,31 +18571,31 @@
     </row>
     <row r="265" spans="1:35">
       <c r="A265" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D265" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F265" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G265" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H265" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J265" s="6"/>
       <c r="K265" s="6"/>
@@ -18584,7 +18607,7 @@
         <v>45</v>
       </c>
       <c r="Q265" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="R265" s="6"/>
       <c r="S265" s="6"/>
@@ -18607,31 +18630,31 @@
     </row>
     <row r="266" spans="1:35">
       <c r="A266" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D266" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H266" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J266" s="6"/>
       <c r="K266" s="6"/>
@@ -18643,7 +18666,7 @@
         <v>31</v>
       </c>
       <c r="Q266" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R266" s="6"/>
       <c r="S266" s="6"/>
@@ -18666,31 +18689,31 @@
     </row>
     <row r="267" spans="1:35">
       <c r="A267" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D267" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F267" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G267" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H267" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J267" s="6"/>
       <c r="K267" s="6"/>
@@ -18702,7 +18725,7 @@
         <v>45</v>
       </c>
       <c r="Q267" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="R267" s="6"/>
       <c r="S267" s="6"/>
@@ -18725,31 +18748,31 @@
     </row>
     <row r="268" spans="1:35">
       <c r="A268" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D268" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G268" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H268" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J268" s="6"/>
       <c r="K268" s="6"/>
@@ -18761,7 +18784,7 @@
         <v>31</v>
       </c>
       <c r="Q268" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R268" s="6"/>
       <c r="S268" s="6"/>
@@ -18784,27 +18807,27 @@
     </row>
     <row r="269" spans="1:35">
       <c r="A269" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D269" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F269" s="6"/>
       <c r="G269" s="6"/>
       <c r="H269" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I269" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J269" s="6"/>
       <c r="K269" s="6"/>
@@ -18835,31 +18858,31 @@
     </row>
     <row r="270" spans="1:35">
       <c r="A270" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D270" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F270" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H270" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I270" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J270" s="6"/>
       <c r="K270" s="6"/>
@@ -18871,7 +18894,7 @@
         <v>195</v>
       </c>
       <c r="Q270" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="R270" s="6"/>
       <c r="S270" s="6"/>
@@ -18879,7 +18902,7 @@
         <v>45</v>
       </c>
       <c r="U270" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="V270" s="6"/>
       <c r="W270" s="6"/>
@@ -18898,31 +18921,31 @@
     </row>
     <row r="271" spans="1:35">
       <c r="A271" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D271" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F271" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G271" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="H271" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="I271" s="7" t="s">
         <v>545</v>
-      </c>
-      <c r="H271" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="I271" s="7" t="s">
-        <v>547</v>
       </c>
       <c r="J271" s="6"/>
       <c r="K271" s="6"/>
@@ -18942,7 +18965,7 @@
         <v>31</v>
       </c>
       <c r="U271" s="6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="V271" s="6"/>
       <c r="W271" s="6"/>
@@ -18961,19 +18984,19 @@
     </row>
     <row r="272" spans="1:35">
       <c r="A272" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D272" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F272" s="6"/>
       <c r="G272" s="6"/>
@@ -19008,31 +19031,31 @@
     </row>
     <row r="273" spans="1:35">
       <c r="A273" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D273" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G273" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H273" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I273" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J273" s="6"/>
       <c r="K273" s="6"/>
@@ -19044,7 +19067,7 @@
         <v>45</v>
       </c>
       <c r="Q273" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="R273" s="6"/>
       <c r="S273" s="6"/>
@@ -19052,7 +19075,7 @@
         <v>45</v>
       </c>
       <c r="U273" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="V273" s="6"/>
       <c r="W273" s="6"/>
@@ -19071,27 +19094,27 @@
     </row>
     <row r="274" spans="1:35">
       <c r="A274" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D274" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F274" s="6"/>
       <c r="G274" s="6"/>
       <c r="H274" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I274" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J274" s="6"/>
       <c r="K274" s="6"/>
@@ -19103,7 +19126,7 @@
         <v>31</v>
       </c>
       <c r="Q274" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="R274" s="6"/>
       <c r="S274" s="6"/>
@@ -19126,19 +19149,19 @@
     </row>
     <row r="275" spans="1:35">
       <c r="A275" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D275" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F275" s="6"/>
       <c r="G275" s="6"/>
@@ -19146,7 +19169,7 @@
         <v>116</v>
       </c>
       <c r="I275" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J275" s="6"/>
       <c r="K275" s="6"/>
@@ -19155,10 +19178,10 @@
       <c r="N275" s="6"/>
       <c r="O275" s="6"/>
       <c r="P275" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Q275" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="R275" s="6"/>
       <c r="S275" s="6"/>
@@ -19181,19 +19204,19 @@
     </row>
     <row r="276" spans="1:35">
       <c r="A276" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F276" s="6"/>
       <c r="G276" s="6"/>
@@ -19201,7 +19224,7 @@
         <v>31</v>
       </c>
       <c r="I276" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J276" s="6"/>
       <c r="K276" s="6"/>
@@ -19210,10 +19233,10 @@
       <c r="N276" s="6"/>
       <c r="O276" s="6"/>
       <c r="P276" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q276" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="R276" s="6"/>
       <c r="S276" s="6"/>
@@ -19236,19 +19259,19 @@
     </row>
     <row r="277" spans="1:35">
       <c r="A277" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D277" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F277" s="6"/>
       <c r="G277" s="6"/>
@@ -19256,7 +19279,7 @@
         <v>31</v>
       </c>
       <c r="I277" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J277" s="6"/>
       <c r="K277" s="6"/>
@@ -19287,19 +19310,19 @@
     </row>
     <row r="278" spans="1:35">
       <c r="A278" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D278" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F278" s="6"/>
       <c r="G278" s="6"/>
@@ -19307,7 +19330,7 @@
         <v>31</v>
       </c>
       <c r="I278" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J278" s="6"/>
       <c r="K278" s="6"/>
@@ -19316,10 +19339,10 @@
       <c r="N278" s="6"/>
       <c r="O278" s="6"/>
       <c r="P278" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q278" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="R278" s="6"/>
       <c r="S278" s="6"/>
@@ -19342,19 +19365,19 @@
     </row>
     <row r="279" spans="1:35">
       <c r="A279" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D279" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F279" s="6"/>
       <c r="G279" s="6"/>
@@ -19389,19 +19412,19 @@
     </row>
     <row r="280" spans="1:35">
       <c r="A280" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D280" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F280" s="6"/>
       <c r="G280" s="6"/>
@@ -19436,19 +19459,19 @@
     </row>
     <row r="281" spans="1:35">
       <c r="A281" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D281" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F281" s="6"/>
       <c r="G281" s="6"/>
@@ -19456,7 +19479,7 @@
         <v>31</v>
       </c>
       <c r="I281" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J281" s="6"/>
       <c r="K281" s="6"/>
@@ -19487,27 +19510,27 @@
     </row>
     <row r="282" spans="1:35">
       <c r="A282" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D282" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F282" s="6"/>
       <c r="G282" s="6"/>
       <c r="H282" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I282" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J282" s="6"/>
       <c r="K282" s="6"/>
@@ -19516,10 +19539,10 @@
       <c r="N282" s="6"/>
       <c r="O282" s="6"/>
       <c r="P282" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="Q282" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="Q282" s="6" t="s">
-        <v>512</v>
       </c>
       <c r="R282" s="6"/>
       <c r="S282" s="6"/>
@@ -19542,31 +19565,31 @@
     </row>
     <row r="283" spans="1:35">
       <c r="A283" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D283" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E283" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F283" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G283" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="H283" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="I283" s="7" t="s">
         <v>515</v>
-      </c>
-      <c r="H283" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="I283" s="7" t="s">
-        <v>517</v>
       </c>
       <c r="J283" s="6"/>
       <c r="K283" s="6"/>
@@ -19575,10 +19598,10 @@
       <c r="N283" s="6"/>
       <c r="O283" s="6"/>
       <c r="P283" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q283" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="Q283" s="6" t="s">
-        <v>520</v>
       </c>
       <c r="R283" s="6"/>
       <c r="S283" s="6"/>
@@ -19601,31 +19624,31 @@
     </row>
     <row r="284" spans="1:35">
       <c r="A284" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D284" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>31</v>
       </c>
       <c r="G284" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="H284" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="I284" s="7" t="s">
         <v>525</v>
-      </c>
-      <c r="H284" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="I284" s="7" t="s">
-        <v>527</v>
       </c>
       <c r="J284" s="6"/>
       <c r="K284" s="6"/>
@@ -19634,10 +19657,10 @@
       <c r="N284" s="6"/>
       <c r="O284" s="6"/>
       <c r="P284" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q284" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="R284" s="6"/>
       <c r="S284" s="6"/>

--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B655D67B-D15C-45DB-8208-00EFD578B80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A342ED84-2F41-41BF-ABE5-21FB07856B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3418" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="762">
   <si>
     <t>Entity Category</t>
   </si>
@@ -1238,9 +1238,6 @@
     <t>Aliases[].Phonetic_Key</t>
   </si>
   <si>
-    <t>Aliased[].Search_Tokens</t>
-  </si>
-  <si>
     <t>Aliases[].Note</t>
   </si>
   <si>
@@ -2307,6 +2304,12 @@
   </si>
   <si>
     <t>INDIVIDUAL_DATE_OF_BIRTH.DATE|INDIVIDUAL_DATE_OF_BIRTH.YEAR|"From Year: "|INDIVIDUAL_DATE_OF_BIRTH.FROM_YEAR| "To Year: "|INDIVIDUAL_DATE_OF_BIRTH.TO_YEAR</t>
+  </si>
+  <si>
+    <t>"Crime" * "Sanctions"</t>
+  </si>
+  <si>
+    <t>Aliases[].Search_Tokens</t>
   </si>
 </sst>
 </file>
@@ -3601,11 +3604,11 @@
       <c r="K9" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>83</v>
+      <c r="L9" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>760</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
@@ -4664,18 +4667,6 @@
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>184</v>
-      </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -4717,14 +4708,26 @@
         <v>187</v>
       </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="H25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
@@ -5567,7 +5570,7 @@
         <v>52</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>33</v>
@@ -5601,13 +5604,13 @@
         <v>190</v>
       </c>
       <c r="Y41" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Z41" s="57" t="s">
         <v>190</v>
       </c>
       <c r="AA41" s="57" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AB41" s="40" t="s">
         <v>33</v>
@@ -5847,7 +5850,7 @@
         <v>52</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>48</v>
@@ -5997,7 +6000,7 @@
         <v>190</v>
       </c>
       <c r="Y48" s="11" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Z48" s="8" t="s">
         <v>33</v>
@@ -7653,7 +7656,7 @@
         <v>29</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>404</v>
+        <v>761</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8" t="s">
@@ -7698,10 +7701,10 @@
         <v>29</v>
       </c>
       <c r="B76" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>406</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>32</v>
@@ -7713,7 +7716,7 @@
         <v>52</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H76" s="20" t="s">
         <v>190</v>
@@ -7735,7 +7738,7 @@
         <v>52</v>
       </c>
       <c r="Q76" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="R76" s="20"/>
       <c r="S76" s="20"/>
@@ -7747,7 +7750,7 @@
         <v>190</v>
       </c>
       <c r="Y76" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="Z76" s="31"/>
       <c r="AA76" s="31"/>
@@ -7765,16 +7768,16 @@
         <v>29</v>
       </c>
       <c r="B77" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>409</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>410</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E77" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
@@ -7782,13 +7785,13 @@
         <v>131</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L77" s="8"/>
       <c r="M77" s="8"/>
@@ -7798,7 +7801,7 @@
         <v>131</v>
       </c>
       <c r="Q77" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R77" s="8"/>
       <c r="S77" s="8"/>
@@ -7824,16 +7827,16 @@
         <v>29</v>
       </c>
       <c r="B78" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>414</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E78" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>48</v>
@@ -7857,7 +7860,7 @@
         <v>48</v>
       </c>
       <c r="M78" s="43" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N78" s="8"/>
       <c r="O78" s="8"/>
@@ -7907,40 +7910,40 @@
         <v>29</v>
       </c>
       <c r="B79" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>418</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E79" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H79" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>33</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N79" s="8"/>
       <c r="O79" s="8"/>
@@ -7948,7 +7951,7 @@
         <v>33</v>
       </c>
       <c r="Q79" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R79" s="8"/>
       <c r="S79" s="8"/>
@@ -7958,25 +7961,25 @@
         <v>33</v>
       </c>
       <c r="W79" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="X79" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y79" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Z79" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA79" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AB79" s="40" t="s">
         <v>33</v>
       </c>
       <c r="AC79" s="41" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AD79" s="7"/>
       <c r="AE79" s="7"/>
@@ -7990,40 +7993,40 @@
         <v>29</v>
       </c>
       <c r="B80" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>427</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E80" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>48</v>
       </c>
       <c r="M80" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N80" s="8"/>
       <c r="O80" s="8"/>
@@ -8031,7 +8034,7 @@
         <v>48</v>
       </c>
       <c r="Q80" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R80" s="8"/>
       <c r="S80" s="8"/>
@@ -8041,25 +8044,25 @@
         <v>48</v>
       </c>
       <c r="W80" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X80" s="8" t="s">
         <v>48</v>
       </c>
       <c r="Y80" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Z80" s="11" t="s">
         <v>48</v>
       </c>
       <c r="AA80" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB80" s="40" t="s">
         <v>48</v>
       </c>
       <c r="AC80" s="41" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AD80" s="7"/>
       <c r="AE80" s="7"/>
@@ -8073,34 +8076,34 @@
         <v>29</v>
       </c>
       <c r="B81" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>435</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>436</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E81" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L81" s="8"/>
       <c r="M81" s="8"/>
@@ -8110,7 +8113,7 @@
         <v>33</v>
       </c>
       <c r="Q81" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R81" s="8"/>
       <c r="S81" s="8"/>
@@ -8120,7 +8123,7 @@
         <v>33</v>
       </c>
       <c r="W81" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="X81" s="8"/>
       <c r="Y81" s="8"/>
@@ -8128,13 +8131,13 @@
         <v>33</v>
       </c>
       <c r="AA81" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AB81" s="40" t="s">
         <v>33</v>
       </c>
       <c r="AC81" s="41" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AD81" s="7"/>
       <c r="AE81" s="7"/>
@@ -8148,16 +8151,16 @@
         <v>29</v>
       </c>
       <c r="B82" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="C82" s="8" t="s">
         <v>442</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
@@ -8173,7 +8176,7 @@
         <v>131</v>
       </c>
       <c r="Q82" s="11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="R82" s="8"/>
       <c r="S82" s="8"/>
@@ -8185,7 +8188,7 @@
         <v>131</v>
       </c>
       <c r="Y82" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
@@ -8203,16 +8206,16 @@
         <v>29</v>
       </c>
       <c r="B83" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>447</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>448</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
@@ -8220,13 +8223,13 @@
         <v>33</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
@@ -8236,7 +8239,7 @@
         <v>33</v>
       </c>
       <c r="Q83" s="11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="R83" s="8"/>
       <c r="S83" s="8"/>
@@ -8246,19 +8249,19 @@
         <v>213</v>
       </c>
       <c r="W83" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="X83" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y83" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Z83" s="8" t="s">
         <v>213</v>
       </c>
       <c r="AA83" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AB83" s="16"/>
       <c r="AC83" s="17"/>
@@ -8274,16 +8277,16 @@
         <v>29</v>
       </c>
       <c r="B84" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>452</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>453</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
@@ -8321,16 +8324,16 @@
         <v>29</v>
       </c>
       <c r="B85" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
@@ -8338,13 +8341,13 @@
         <v>131</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L85" s="8"/>
       <c r="M85" s="8"/>
@@ -8354,7 +8357,7 @@
         <v>131</v>
       </c>
       <c r="Q85" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R85" s="8"/>
       <c r="S85" s="8"/>
@@ -8366,13 +8369,13 @@
         <v>131</v>
       </c>
       <c r="Y85" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Z85" s="8" t="s">
         <v>131</v>
       </c>
       <c r="AA85" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AB85" s="16"/>
       <c r="AC85" s="17"/>
@@ -8388,40 +8391,40 @@
         <v>29</v>
       </c>
       <c r="B86" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>461</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>462</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J86" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>213</v>
       </c>
       <c r="M86" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N86" s="8"/>
       <c r="O86" s="8"/>
@@ -8429,7 +8432,7 @@
         <v>190</v>
       </c>
       <c r="Q86" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R86" s="8"/>
       <c r="S86" s="8"/>
@@ -8439,25 +8442,25 @@
         <v>190</v>
       </c>
       <c r="W86" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="X86" s="8" t="s">
         <v>190</v>
       </c>
       <c r="Y86" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Z86" s="8" t="s">
         <v>190</v>
       </c>
       <c r="AA86" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AB86" s="40" t="s">
         <v>33</v>
       </c>
       <c r="AC86" s="41" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AD86" s="7"/>
       <c r="AE86" s="7"/>
@@ -8471,16 +8474,16 @@
         <v>29</v>
       </c>
       <c r="B87" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>470</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>471</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
@@ -8488,13 +8491,13 @@
         <v>52</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L87" s="8"/>
       <c r="M87" s="8"/>
@@ -8504,7 +8507,7 @@
         <v>33</v>
       </c>
       <c r="Q87" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R87" s="8"/>
       <c r="S87" s="8"/>
@@ -8530,16 +8533,16 @@
         <v>29</v>
       </c>
       <c r="B88" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>474</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>475</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
@@ -8547,13 +8550,13 @@
         <v>52</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J88" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L88" s="8"/>
       <c r="M88" s="8"/>
@@ -8563,7 +8566,7 @@
         <v>33</v>
       </c>
       <c r="Q88" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R88" s="8"/>
       <c r="S88" s="8"/>
@@ -8589,16 +8592,16 @@
         <v>29</v>
       </c>
       <c r="B89" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C89" s="8" t="s">
         <v>478</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>479</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
@@ -8606,13 +8609,13 @@
         <v>52</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L89" s="8"/>
       <c r="M89" s="8"/>
@@ -8622,7 +8625,7 @@
         <v>33</v>
       </c>
       <c r="Q89" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R89" s="8"/>
       <c r="S89" s="8"/>
@@ -8648,16 +8651,16 @@
         <v>29</v>
       </c>
       <c r="B90" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>482</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>483</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
@@ -8665,13 +8668,13 @@
         <v>52</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L90" s="8"/>
       <c r="M90" s="8"/>
@@ -8687,19 +8690,19 @@
         <v>33</v>
       </c>
       <c r="W90" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="X90" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y90" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Z90" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA90" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AB90" s="16"/>
       <c r="AC90" s="17"/>
@@ -8715,16 +8718,16 @@
         <v>29</v>
       </c>
       <c r="B91" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>487</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>488</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
@@ -8732,13 +8735,13 @@
         <v>33</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L91" s="8"/>
       <c r="M91" s="8"/>
@@ -8748,7 +8751,7 @@
         <v>33</v>
       </c>
       <c r="Q91" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="R91" s="8"/>
       <c r="S91" s="8"/>
@@ -8758,19 +8761,19 @@
         <v>33</v>
       </c>
       <c r="W91" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="X91" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y91" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Z91" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA91" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AB91" s="16"/>
       <c r="AC91" s="17"/>
@@ -8786,16 +8789,16 @@
         <v>29</v>
       </c>
       <c r="B92" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>493</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>494</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
@@ -8803,13 +8806,13 @@
         <v>52</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J92" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L92" s="8"/>
       <c r="M92" s="8"/>
@@ -8825,19 +8828,19 @@
         <v>33</v>
       </c>
       <c r="W92" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X92" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y92" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Z92" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA92" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AB92" s="16"/>
       <c r="AC92" s="17"/>
@@ -8853,16 +8856,16 @@
         <v>29</v>
       </c>
       <c r="B93" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>498</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>499</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
@@ -8870,13 +8873,13 @@
         <v>52</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L93" s="8"/>
       <c r="M93" s="8"/>
@@ -8886,7 +8889,7 @@
         <v>33</v>
       </c>
       <c r="Q93" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="R93" s="8"/>
       <c r="S93" s="8"/>
@@ -8896,19 +8899,19 @@
         <v>33</v>
       </c>
       <c r="W93" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="X93" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y93" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Z93" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA93" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AB93" s="16"/>
       <c r="AC93" s="17"/>
@@ -8924,16 +8927,16 @@
         <v>29</v>
       </c>
       <c r="B94" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
@@ -8953,19 +8956,19 @@
       <c r="U94" s="8"/>
       <c r="V94" s="8"/>
       <c r="W94" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="X94" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Y94" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Z94" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA94" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AB94" s="16"/>
       <c r="AC94" s="17"/>
@@ -8981,16 +8984,16 @@
         <v>29</v>
       </c>
       <c r="B95" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>509</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>510</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
@@ -8998,13 +9001,13 @@
         <v>131</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L95" s="8"/>
       <c r="M95" s="8"/>
@@ -9036,16 +9039,16 @@
         <v>29</v>
       </c>
       <c r="B96" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>514</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
@@ -9053,19 +9056,19 @@
         <v>33</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J96" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>48</v>
       </c>
       <c r="M96" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N96" s="8"/>
       <c r="O96" s="8"/>
@@ -9095,16 +9098,16 @@
         <v>29</v>
       </c>
       <c r="B97" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="C97" s="8" t="s">
         <v>517</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>518</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
@@ -9112,13 +9115,13 @@
         <v>33</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L97" s="8"/>
       <c r="M97" s="8"/>
@@ -9150,16 +9153,16 @@
         <v>29</v>
       </c>
       <c r="B98" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="C98" s="8" t="s">
         <v>520</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>521</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
@@ -9167,19 +9170,19 @@
         <v>33</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J98" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>213</v>
       </c>
       <c r="M98" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N98" s="8"/>
       <c r="O98" s="8"/>
@@ -9209,16 +9212,16 @@
         <v>29</v>
       </c>
       <c r="B99" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="C99" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
@@ -9256,16 +9259,16 @@
         <v>29</v>
       </c>
       <c r="B100" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>527</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
@@ -9303,16 +9306,16 @@
         <v>29</v>
       </c>
       <c r="B101" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>528</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>529</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
@@ -9320,13 +9323,13 @@
         <v>33</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L101" s="8"/>
       <c r="M101" s="8"/>
@@ -9358,40 +9361,40 @@
         <v>29</v>
       </c>
       <c r="B102" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>531</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>532</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
       <c r="H102" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="I102" s="30" t="s">
         <v>534</v>
       </c>
-      <c r="I102" s="30" t="s">
-        <v>535</v>
-      </c>
       <c r="J102" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="K102" s="30" t="s">
         <v>534</v>
-      </c>
-      <c r="K102" s="30" t="s">
-        <v>535</v>
       </c>
       <c r="L102" s="8"/>
       <c r="M102" s="8"/>
       <c r="N102" s="8"/>
       <c r="O102" s="8"/>
       <c r="P102" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q102" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R102" s="8"/>
       <c r="S102" s="8"/>
@@ -9417,48 +9420,48 @@
         <v>29</v>
       </c>
       <c r="B103" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="C103" s="8" t="s">
         <v>537</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>538</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H103" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="H103" s="8" t="s">
+      <c r="I103" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="I103" s="10" t="s">
+      <c r="J103" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="K103" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="L103" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="J103" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="K103" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="L103" s="8" t="s">
+      <c r="M103" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="M103" s="8" t="s">
-        <v>543</v>
       </c>
       <c r="N103" s="8"/>
       <c r="O103" s="8"/>
       <c r="P103" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q103" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="R103" s="8"/>
       <c r="S103" s="8"/>
@@ -9468,25 +9471,25 @@
         <v>48</v>
       </c>
       <c r="W103" s="8" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="X103" s="8" t="s">
         <v>48</v>
       </c>
       <c r="Y103" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Z103" s="14" t="s">
         <v>48</v>
       </c>
       <c r="AA103" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AB103" s="40" t="s">
         <v>145</v>
       </c>
       <c r="AC103" s="41" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AD103" s="7"/>
       <c r="AE103" s="7"/>
@@ -9500,48 +9503,48 @@
         <v>29</v>
       </c>
       <c r="B104" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="C104" s="8" t="s">
         <v>548</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>549</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G104" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="H104" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="H104" s="8" t="s">
+      <c r="I104" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="I104" s="10" t="s">
+      <c r="J104" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="K104" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="L104" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="J104" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="K104" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="L104" s="8" t="s">
+      <c r="M104" s="8" t="s">
         <v>553</v>
-      </c>
-      <c r="M104" s="8" t="s">
-        <v>554</v>
       </c>
       <c r="N104" s="8"/>
       <c r="O104" s="8"/>
       <c r="P104" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q104" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="Q104" s="8" t="s">
-        <v>556</v>
       </c>
       <c r="R104" s="8"/>
       <c r="S104" s="8"/>
@@ -9551,7 +9554,7 @@
         <v>33</v>
       </c>
       <c r="W104" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X104" s="8" t="s">
         <v>33</v>
@@ -9563,13 +9566,13 @@
         <v>33</v>
       </c>
       <c r="AA104" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AB104" s="40" t="s">
         <v>161</v>
       </c>
       <c r="AC104" s="41" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AD104" s="7"/>
       <c r="AE104" s="7"/>
@@ -9583,30 +9586,30 @@
         <v>29</v>
       </c>
       <c r="B105" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="C105" s="8" t="s">
         <v>559</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>560</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
       <c r="H105" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L105" s="8"/>
       <c r="M105" s="8"/>
@@ -9638,34 +9641,34 @@
         <v>29</v>
       </c>
       <c r="B106" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="C106" s="8" t="s">
         <v>563</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>564</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>339</v>
       </c>
       <c r="G106" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="I106" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="H106" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="I106" s="10" t="s">
-        <v>566</v>
-      </c>
       <c r="J106" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L106" s="8"/>
       <c r="M106" s="8"/>
@@ -9675,7 +9678,7 @@
         <v>213</v>
       </c>
       <c r="Q106" s="8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R106" s="8"/>
       <c r="S106" s="8"/>
@@ -9685,7 +9688,7 @@
         <v>48</v>
       </c>
       <c r="W106" s="8" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="X106" s="8"/>
       <c r="Y106" s="8"/>
@@ -9705,34 +9708,34 @@
         <v>29</v>
       </c>
       <c r="B107" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>569</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>570</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G107" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="H107" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="H107" s="8" t="s">
+      <c r="I107" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="I107" s="10" t="s">
-        <v>573</v>
-      </c>
       <c r="J107" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="K107" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="K107" s="10" t="s">
-        <v>573</v>
       </c>
       <c r="L107" s="8"/>
       <c r="M107" s="8"/>
@@ -9766,16 +9769,16 @@
         <v>29</v>
       </c>
       <c r="B108" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="C108" s="8" t="s">
         <v>574</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
@@ -9813,34 +9816,34 @@
         <v>29</v>
       </c>
       <c r="B109" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>576</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>577</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>346</v>
       </c>
       <c r="G109" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="I109" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="H109" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="I109" s="10" t="s">
-        <v>579</v>
-      </c>
       <c r="J109" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K109" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L109" s="8"/>
       <c r="M109" s="8"/>
@@ -9850,7 +9853,7 @@
         <v>48</v>
       </c>
       <c r="Q109" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R109" s="8"/>
       <c r="S109" s="8"/>
@@ -9860,7 +9863,7 @@
         <v>48</v>
       </c>
       <c r="W109" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="X109" s="8"/>
       <c r="Y109" s="8"/>
@@ -9880,30 +9883,30 @@
         <v>29</v>
       </c>
       <c r="B110" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>581</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>582</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F110" s="9"/>
       <c r="G110" s="9"/>
       <c r="H110" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L110" s="8"/>
       <c r="M110" s="8"/>
@@ -9913,7 +9916,7 @@
         <v>33</v>
       </c>
       <c r="Q110" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R110" s="8"/>
       <c r="S110" s="8"/>
@@ -9923,7 +9926,7 @@
         <v>33</v>
       </c>
       <c r="W110" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="X110" s="8"/>
       <c r="Y110" s="8"/>
@@ -9940,7 +9943,7 @@
     </row>
     <row r="111" spans="1:35" ht="14.5" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>30</v>
@@ -10021,13 +10024,13 @@
     </row>
     <row r="112" spans="1:35" ht="14.5" customHeight="1">
       <c r="A112" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>32</v>
@@ -10063,7 +10066,7 @@
         <v>48</v>
       </c>
       <c r="Q112" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="R112" s="8" t="s">
         <v>33</v>
@@ -10079,19 +10082,19 @@
         <v>48</v>
       </c>
       <c r="Y112" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Z112" s="8" t="s">
         <v>48</v>
       </c>
       <c r="AA112" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AB112" s="49" t="s">
         <v>48</v>
       </c>
       <c r="AC112" s="50" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AD112" s="7"/>
       <c r="AE112" s="7"/>
@@ -10102,7 +10105,7 @@
     </row>
     <row r="113" spans="1:35" ht="14.5" customHeight="1">
       <c r="A113" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>59</v>
@@ -10175,7 +10178,7 @@
     </row>
     <row r="114" spans="1:35" ht="14.5" customHeight="1">
       <c r="A114" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>67</v>
@@ -10236,7 +10239,7 @@
     </row>
     <row r="115" spans="1:35" ht="14.5" customHeight="1">
       <c r="A115" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>73</v>
@@ -10283,7 +10286,7 @@
     </row>
     <row r="116" spans="1:35" ht="14.5" customHeight="1">
       <c r="A116" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>77</v>
@@ -10366,7 +10369,7 @@
     </row>
     <row r="117" spans="1:35" ht="14.5" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B117" s="18" t="s">
         <v>80</v>
@@ -10404,8 +10407,12 @@
       <c r="M117" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="N117" s="9"/>
-      <c r="O117" s="9"/>
+      <c r="N117" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O117" s="9" t="s">
+        <v>760</v>
+      </c>
       <c r="P117" s="9" t="s">
         <v>48</v>
       </c>
@@ -10453,7 +10460,7 @@
     </row>
     <row r="118" spans="1:35" ht="14.5" customHeight="1">
       <c r="A118" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>85</v>
@@ -10491,7 +10498,7 @@
         <v>48</v>
       </c>
       <c r="O118" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="P118" s="8" t="s">
         <v>48</v>
@@ -10536,7 +10543,7 @@
     </row>
     <row r="119" spans="1:35" ht="14.5" customHeight="1">
       <c r="A119" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>97</v>
@@ -10619,7 +10626,7 @@
     </row>
     <row r="120" spans="1:35" ht="101.5" customHeight="1">
       <c r="A120" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>106</v>
@@ -10657,13 +10664,13 @@
         <v>48</v>
       </c>
       <c r="O120" s="25" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P120" s="8" t="s">
         <v>48</v>
       </c>
       <c r="Q120" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="R120" s="8" t="s">
         <v>48</v>
@@ -10702,7 +10709,7 @@
     </row>
     <row r="121" spans="1:35" ht="14.5" customHeight="1">
       <c r="A121" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>118</v>
@@ -10785,7 +10792,7 @@
     </row>
     <row r="122" spans="1:35" ht="14.5" customHeight="1">
       <c r="A122" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>120</v>
@@ -10829,7 +10836,7 @@
         <v>33</v>
       </c>
       <c r="S122" s="8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T122" s="8"/>
       <c r="U122" s="8"/>
@@ -10858,13 +10865,13 @@
     </row>
     <row r="123" spans="1:35" ht="29" customHeight="1">
       <c r="A123" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>128</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>75</v>
@@ -10925,13 +10932,13 @@
     </row>
     <row r="124" spans="1:35" ht="43.5" customHeight="1">
       <c r="A124" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B124" s="8" t="s">
         <v>136</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>32</v>
@@ -11004,13 +11011,13 @@
     </row>
     <row r="125" spans="1:35" ht="43.5" customHeight="1">
       <c r="A125" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>148</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>32</v>
@@ -11042,7 +11049,7 @@
         <v>33</v>
       </c>
       <c r="O125" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="P125" s="8" t="s">
         <v>154</v>
@@ -11064,7 +11071,7 @@
         <v>158</v>
       </c>
       <c r="Y125" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Z125" s="11" t="s">
         <v>33</v>
@@ -11087,7 +11094,7 @@
     </row>
     <row r="126" spans="1:35" ht="14.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B126" s="31" t="s">
         <v>179</v>
@@ -11132,7 +11139,7 @@
     </row>
     <row r="127" spans="1:35" ht="14.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B127" s="31" t="s">
         <v>180</v>
@@ -11177,7 +11184,7 @@
     </row>
     <row r="128" spans="1:35" ht="14.5" customHeight="1">
       <c r="A128" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B128" s="31" t="s">
         <v>181</v>
@@ -11222,7 +11229,7 @@
     </row>
     <row r="129" spans="1:35" ht="14.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B129" s="8" t="s">
         <v>182</v>
@@ -11238,18 +11245,6 @@
       </c>
       <c r="F129" s="9"/>
       <c r="G129" s="9"/>
-      <c r="H129" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I129" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="J129" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K129" s="8" t="s">
-        <v>184</v>
-      </c>
       <c r="L129" s="8"/>
       <c r="M129" s="8"/>
       <c r="N129" s="8"/>
@@ -11281,20 +11276,32 @@
     </row>
     <row r="130" spans="1:35" ht="14.5" customHeight="1">
       <c r="A130" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B130" s="35" t="s">
         <v>187</v>
       </c>
       <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
+      <c r="D130" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="F130" s="9"/>
       <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="9"/>
-      <c r="J130" s="9"/>
-      <c r="K130" s="9"/>
+      <c r="H130" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J130" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K130" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="L130" s="9"/>
       <c r="M130" s="9"/>
       <c r="N130" s="9"/>
@@ -11322,7 +11329,7 @@
     </row>
     <row r="131" spans="1:35" ht="29" customHeight="1">
       <c r="A131" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>188</v>
@@ -11340,7 +11347,7 @@
         <v>33</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H131" s="9" t="s">
         <v>190</v>
@@ -11385,7 +11392,7 @@
     </row>
     <row r="132" spans="1:35" ht="14.5" customHeight="1">
       <c r="A132" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>229</v>
@@ -11444,7 +11451,7 @@
     </row>
     <row r="133" spans="1:35" ht="35.5" customHeight="1">
       <c r="A133" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B133" s="37" t="s">
         <v>235</v>
@@ -11511,7 +11518,7 @@
     </row>
     <row r="134" spans="1:35" ht="14.5" customHeight="1">
       <c r="A134" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>238</v>
@@ -11558,7 +11565,7 @@
     </row>
     <row r="135" spans="1:35" ht="14.5" customHeight="1">
       <c r="A135" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>240</v>
@@ -11605,7 +11612,7 @@
     </row>
     <row r="136" spans="1:35" ht="14.5" customHeight="1">
       <c r="A136" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>242</v>
@@ -11652,7 +11659,7 @@
     </row>
     <row r="137" spans="1:35" ht="14.5" customHeight="1">
       <c r="A137" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B137" s="8" t="s">
         <v>244</v>
@@ -11705,7 +11712,7 @@
     </row>
     <row r="138" spans="1:35" ht="29" customHeight="1">
       <c r="A138" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B138" s="8" t="s">
         <v>249</v>
@@ -11741,7 +11748,7 @@
         <v>48</v>
       </c>
       <c r="Q138" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="R138" s="8" t="s">
         <v>48</v>
@@ -11761,7 +11768,7 @@
         <v>48</v>
       </c>
       <c r="AC138" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AD138" s="7"/>
       <c r="AE138" s="7"/>
@@ -11772,7 +11779,7 @@
     </row>
     <row r="139" spans="1:35" ht="14.5" customHeight="1">
       <c r="A139" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B139" s="8" t="s">
         <v>257</v>
@@ -11827,7 +11834,7 @@
     </row>
     <row r="140" spans="1:35" ht="29" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B140" s="8" t="s">
         <v>250</v>
@@ -11869,13 +11876,13 @@
     </row>
     <row r="141" spans="1:35" ht="14.5" customHeight="1">
       <c r="A141" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B141" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D141" s="8" t="s">
         <v>75</v>
@@ -11922,13 +11929,13 @@
     </row>
     <row r="142" spans="1:35" ht="14.5" customHeight="1">
       <c r="A142" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B142" s="8" t="s">
         <v>297</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D142" s="8" t="s">
         <v>32</v>
@@ -11942,13 +11949,13 @@
         <v>52</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J142" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K142" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L142" s="8"/>
       <c r="M142" s="8"/>
@@ -11968,7 +11975,7 @@
         <v>48</v>
       </c>
       <c r="AA142" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AB142" s="16"/>
       <c r="AC142" s="17"/>
@@ -11981,7 +11988,7 @@
     </row>
     <row r="143" spans="1:35" ht="14.5" customHeight="1">
       <c r="A143" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B143" s="11" t="s">
         <v>303</v>
@@ -12032,7 +12039,7 @@
     </row>
     <row r="144" spans="1:35" ht="14.5" customHeight="1">
       <c r="A144" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B144" s="8" t="s">
         <v>305</v>
@@ -12052,13 +12059,13 @@
         <v>52</v>
       </c>
       <c r="I144" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J144" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K144" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L144" s="8"/>
       <c r="M144" s="8"/>
@@ -12087,7 +12094,7 @@
     </row>
     <row r="145" spans="1:35" ht="14.5" customHeight="1">
       <c r="A145" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B145" s="8" t="s">
         <v>312</v>
@@ -12136,19 +12143,19 @@
     </row>
     <row r="146" spans="1:35" ht="14.5" customHeight="1">
       <c r="A146" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D146" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F146" s="9"/>
       <c r="G146" s="9"/>
@@ -12156,13 +12163,13 @@
         <v>131</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J146" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K146" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L146" s="8"/>
       <c r="M146" s="8"/>
@@ -12172,7 +12179,7 @@
         <v>131</v>
       </c>
       <c r="Q146" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R146" s="8"/>
       <c r="S146" s="8"/>
@@ -12184,13 +12191,13 @@
         <v>131</v>
       </c>
       <c r="Y146" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Z146" s="8" t="s">
         <v>131</v>
       </c>
       <c r="AA146" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AB146" s="16"/>
       <c r="AC146" s="17"/>
@@ -12203,37 +12210,37 @@
     </row>
     <row r="147" spans="1:35" ht="58" customHeight="1">
       <c r="A147" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B147" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C147" s="8" t="s">
         <v>461</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>462</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H147" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J147" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K147" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L147" s="8"/>
       <c r="M147" s="8"/>
@@ -12243,7 +12250,7 @@
         <v>190</v>
       </c>
       <c r="Q147" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="R147" s="8"/>
       <c r="S147" s="8"/>
@@ -12255,19 +12262,19 @@
         <v>190</v>
       </c>
       <c r="Y147" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Z147" s="8" t="s">
         <v>190</v>
       </c>
       <c r="AA147" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AB147" s="49" t="s">
         <v>33</v>
       </c>
       <c r="AC147" s="50" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AD147" s="7"/>
       <c r="AE147" s="7"/>
@@ -12278,19 +12285,19 @@
     </row>
     <row r="148" spans="1:35" ht="29" customHeight="1">
       <c r="A148" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B148" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>470</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>471</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F148" s="9"/>
       <c r="G148" s="9"/>
@@ -12298,13 +12305,13 @@
         <v>52</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J148" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K148" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L148" s="8"/>
       <c r="M148" s="8"/>
@@ -12314,7 +12321,7 @@
         <v>33</v>
       </c>
       <c r="Q148" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R148" s="8"/>
       <c r="S148" s="8"/>
@@ -12337,19 +12344,19 @@
     </row>
     <row r="149" spans="1:35" ht="29" customHeight="1">
       <c r="A149" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B149" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C149" s="8" t="s">
         <v>474</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>475</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F149" s="9"/>
       <c r="G149" s="9"/>
@@ -12357,13 +12364,13 @@
         <v>52</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J149" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K149" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L149" s="8"/>
       <c r="M149" s="8"/>
@@ -12373,7 +12380,7 @@
         <v>33</v>
       </c>
       <c r="Q149" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R149" s="8"/>
       <c r="S149" s="8"/>
@@ -12395,19 +12402,19 @@
     </row>
     <row r="150" spans="1:35" ht="29" customHeight="1">
       <c r="A150" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B150" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="C150" s="8" t="s">
         <v>478</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>479</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F150" s="9"/>
       <c r="G150" s="9"/>
@@ -12415,13 +12422,13 @@
         <v>52</v>
       </c>
       <c r="I150" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J150" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K150" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L150" s="8"/>
       <c r="M150" s="8"/>
@@ -12431,7 +12438,7 @@
         <v>33</v>
       </c>
       <c r="Q150" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R150" s="8"/>
       <c r="S150" s="8"/>
@@ -12450,19 +12457,19 @@
     </row>
     <row r="151" spans="1:35" ht="29" customHeight="1">
       <c r="A151" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B151" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C151" s="8" t="s">
         <v>482</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>483</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F151" s="9"/>
       <c r="G151" s="9"/>
@@ -12470,13 +12477,13 @@
         <v>52</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J151" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K151" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L151" s="8"/>
       <c r="M151" s="8"/>
@@ -12494,13 +12501,13 @@
         <v>33</v>
       </c>
       <c r="Y151" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Z151" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA151" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AB151" s="16"/>
       <c r="AC151" s="17"/>
@@ -12513,19 +12520,19 @@
     </row>
     <row r="152" spans="1:35" ht="29" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B152" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C152" s="8" t="s">
         <v>493</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>494</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F152" s="9"/>
       <c r="G152" s="9"/>
@@ -12533,13 +12540,13 @@
         <v>52</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J152" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K152" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L152" s="8"/>
       <c r="M152" s="8"/>
@@ -12557,13 +12564,13 @@
         <v>33</v>
       </c>
       <c r="Y152" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="Z152" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA152" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AB152" s="16"/>
       <c r="AC152" s="17"/>
@@ -12576,19 +12583,19 @@
     </row>
     <row r="153" spans="1:35" ht="14.5" customHeight="1">
       <c r="A153" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B153" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C153" s="8" t="s">
         <v>487</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>488</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F153" s="9"/>
       <c r="G153" s="9"/>
@@ -12596,13 +12603,13 @@
         <v>33</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J153" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K153" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L153" s="8"/>
       <c r="M153" s="8"/>
@@ -12612,7 +12619,7 @@
         <v>33</v>
       </c>
       <c r="Q153" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="R153" s="8"/>
       <c r="S153" s="8"/>
@@ -12624,13 +12631,13 @@
         <v>33</v>
       </c>
       <c r="Y153" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Z153" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA153" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AB153" s="16"/>
       <c r="AC153" s="17"/>
@@ -12643,19 +12650,19 @@
     </row>
     <row r="154" spans="1:35" ht="29" customHeight="1">
       <c r="A154" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B154" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C154" s="8" t="s">
         <v>498</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>499</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F154" s="9"/>
       <c r="G154" s="9"/>
@@ -12663,13 +12670,13 @@
         <v>52</v>
       </c>
       <c r="I154" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J154" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K154" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L154" s="8"/>
       <c r="M154" s="8"/>
@@ -12679,7 +12686,7 @@
         <v>33</v>
       </c>
       <c r="Q154" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="R154" s="8"/>
       <c r="S154" s="8"/>
@@ -12691,13 +12698,13 @@
         <v>33</v>
       </c>
       <c r="Y154" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Z154" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA154" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AB154" s="16"/>
       <c r="AC154" s="17"/>
@@ -12710,19 +12717,19 @@
     </row>
     <row r="155" spans="1:35" ht="14.5" customHeight="1">
       <c r="A155" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B155" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="C155" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F155" s="9"/>
       <c r="G155" s="9"/>
@@ -12746,13 +12753,13 @@
         <v>33</v>
       </c>
       <c r="Y155" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="Z155" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA155" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AB155" s="16"/>
       <c r="AC155" s="17"/>
@@ -12765,13 +12772,13 @@
     </row>
     <row r="156" spans="1:35" ht="14.5" customHeight="1">
       <c r="A156" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B156" s="8" t="s">
         <v>385</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>75</v>
@@ -12817,7 +12824,7 @@
         <v>131</v>
       </c>
       <c r="Y156" s="8" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Z156" s="31"/>
       <c r="AA156" s="31"/>
@@ -12832,7 +12839,7 @@
     </row>
     <row r="157" spans="1:35" ht="14.5" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B157" s="8" t="s">
         <v>390</v>
@@ -12903,7 +12910,7 @@
     </row>
     <row r="158" spans="1:35" ht="14.5" customHeight="1">
       <c r="A158" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B158" s="8" t="s">
         <v>395</v>
@@ -12955,7 +12962,7 @@
         <v>33</v>
       </c>
       <c r="Y158" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Z158" s="31"/>
       <c r="AA158" s="31"/>
@@ -12974,7 +12981,7 @@
     </row>
     <row r="159" spans="1:35" ht="14.5" customHeight="1">
       <c r="A159" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B159" s="31" t="s">
         <v>402</v>
@@ -13017,7 +13024,7 @@
     </row>
     <row r="160" spans="1:35" ht="14.5" customHeight="1">
       <c r="A160" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B160" s="31" t="s">
         <v>403</v>
@@ -13062,10 +13069,10 @@
     </row>
     <row r="161" spans="1:35" ht="14.5" customHeight="1">
       <c r="A161" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B161" s="31" t="s">
-        <v>404</v>
+        <v>761</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="8" t="s">
@@ -13107,13 +13114,13 @@
     </row>
     <row r="162" spans="1:35" ht="14.5" customHeight="1">
       <c r="A162" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B162" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C162" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>406</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>32</v>
@@ -13125,7 +13132,7 @@
         <v>52</v>
       </c>
       <c r="G162" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H162" s="9" t="s">
         <v>190</v>
@@ -13147,7 +13154,7 @@
         <v>131</v>
       </c>
       <c r="Q162" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R162" s="9"/>
       <c r="S162" s="9"/>
@@ -13159,7 +13166,7 @@
         <v>190</v>
       </c>
       <c r="Y162" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="Z162" s="8"/>
       <c r="AA162" s="8"/>
@@ -13174,19 +13181,19 @@
     </row>
     <row r="163" spans="1:35" ht="14.5" customHeight="1">
       <c r="A163" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B163" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C163" s="8" t="s">
         <v>409</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>410</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F163" s="9"/>
       <c r="G163" s="9"/>
@@ -13194,13 +13201,13 @@
         <v>131</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J163" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L163" s="8"/>
       <c r="M163" s="8"/>
@@ -13210,7 +13217,7 @@
         <v>131</v>
       </c>
       <c r="Q163" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R163" s="8"/>
       <c r="S163" s="8"/>
@@ -13229,19 +13236,19 @@
     </row>
     <row r="164" spans="1:35" ht="14.5" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B164" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C164" s="8" t="s">
         <v>414</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>48</v>
@@ -13267,7 +13274,7 @@
         <v>48</v>
       </c>
       <c r="O164" s="43" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P164" s="8" t="s">
         <v>48</v>
@@ -13308,37 +13315,37 @@
     </row>
     <row r="165" spans="1:35" ht="14.5" customHeight="1">
       <c r="A165" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B165" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="C165" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>418</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H165" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I165" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J165" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K165" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L165" s="8"/>
       <c r="M165" s="8"/>
@@ -13346,13 +13353,13 @@
         <v>33</v>
       </c>
       <c r="O165" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P165" s="8" t="s">
         <v>33</v>
       </c>
       <c r="Q165" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R165" s="8"/>
       <c r="S165" s="8"/>
@@ -13364,19 +13371,19 @@
         <v>33</v>
       </c>
       <c r="Y165" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Z165" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AA165" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AB165" s="49" t="s">
         <v>33</v>
       </c>
       <c r="AC165" s="50" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AD165" s="7"/>
       <c r="AE165" s="7"/>
@@ -13387,37 +13394,37 @@
     </row>
     <row r="166" spans="1:35" ht="29" customHeight="1">
       <c r="A166" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B166" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="C166" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>427</v>
       </c>
       <c r="D166" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G166" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>48</v>
       </c>
       <c r="I166" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J166" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K166" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L166" s="8"/>
       <c r="M166" s="8"/>
@@ -13425,13 +13432,13 @@
         <v>48</v>
       </c>
       <c r="O166" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P166" s="8" t="s">
         <v>48</v>
       </c>
       <c r="Q166" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R166" s="8"/>
       <c r="S166" s="8"/>
@@ -13443,19 +13450,19 @@
         <v>48</v>
       </c>
       <c r="Y166" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Z166" s="8" t="s">
         <v>48</v>
       </c>
       <c r="AA166" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB166" s="49" t="s">
         <v>48</v>
       </c>
       <c r="AC166" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AD166" s="7"/>
       <c r="AE166" s="7"/>
@@ -13466,37 +13473,37 @@
     </row>
     <row r="167" spans="1:35" ht="14.5" customHeight="1">
       <c r="A167" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B167" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C167" s="8" t="s">
         <v>435</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>436</v>
       </c>
       <c r="D167" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H167" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I167" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J167" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K167" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L167" s="8"/>
       <c r="M167" s="8"/>
@@ -13506,7 +13513,7 @@
         <v>33</v>
       </c>
       <c r="Q167" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R167" s="8"/>
       <c r="S167" s="8"/>
@@ -13520,13 +13527,13 @@
         <v>33</v>
       </c>
       <c r="AA167" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AB167" s="49" t="s">
         <v>33</v>
       </c>
       <c r="AC167" s="50" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AD167" s="7"/>
       <c r="AE167" s="7"/>
@@ -13537,19 +13544,19 @@
     </row>
     <row r="168" spans="1:35" ht="29" customHeight="1">
       <c r="A168" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B168" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="C168" s="8" t="s">
         <v>509</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>510</v>
       </c>
       <c r="D168" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F168" s="9"/>
       <c r="G168" s="9"/>
@@ -13557,23 +13564,23 @@
         <v>131</v>
       </c>
       <c r="I168" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J168" s="8" t="s">
         <v>131</v>
       </c>
       <c r="K168" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L168" s="8"/>
       <c r="M168" s="8"/>
       <c r="N168" s="8"/>
       <c r="O168" s="8"/>
       <c r="P168" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q168" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="R168" s="8"/>
       <c r="S168" s="8"/>
@@ -13596,19 +13603,19 @@
     </row>
     <row r="169" spans="1:35" ht="14.5" customHeight="1">
       <c r="A169" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B169" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="C169" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>514</v>
       </c>
       <c r="D169" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F169" s="9"/>
       <c r="G169" s="9"/>
@@ -13616,23 +13623,23 @@
         <v>33</v>
       </c>
       <c r="I169" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J169" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K169" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L169" s="8"/>
       <c r="M169" s="8"/>
       <c r="N169" s="8"/>
       <c r="O169" s="8"/>
       <c r="P169" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q169" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R169" s="8"/>
       <c r="S169" s="8"/>
@@ -13655,19 +13662,19 @@
     </row>
     <row r="170" spans="1:35" ht="14.5" customHeight="1">
       <c r="A170" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B170" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="C170" s="8" t="s">
         <v>517</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>518</v>
       </c>
       <c r="D170" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F170" s="9"/>
       <c r="G170" s="9"/>
@@ -13675,13 +13682,13 @@
         <v>33</v>
       </c>
       <c r="I170" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J170" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K170" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L170" s="8"/>
       <c r="M170" s="8"/>
@@ -13710,19 +13717,19 @@
     </row>
     <row r="171" spans="1:35" ht="29" customHeight="1">
       <c r="A171" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B171" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C171" s="8" t="s">
         <v>520</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>521</v>
       </c>
       <c r="D171" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F171" s="9"/>
       <c r="G171" s="9"/>
@@ -13730,13 +13737,13 @@
         <v>33</v>
       </c>
       <c r="I171" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J171" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K171" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L171" s="8"/>
       <c r="M171" s="8"/>
@@ -13746,7 +13753,7 @@
         <v>33</v>
       </c>
       <c r="Q171" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="R171" s="8"/>
       <c r="S171" s="8"/>
@@ -13769,19 +13776,19 @@
     </row>
     <row r="172" spans="1:35" ht="14.5" customHeight="1">
       <c r="A172" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B172" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="C172" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="D172" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F172" s="9"/>
       <c r="G172" s="9"/>
@@ -13816,19 +13823,19 @@
     </row>
     <row r="173" spans="1:35" ht="14.5" customHeight="1">
       <c r="A173" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B173" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C173" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>527</v>
       </c>
       <c r="D173" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F173" s="9"/>
       <c r="G173" s="9"/>
@@ -13863,19 +13870,19 @@
     </row>
     <row r="174" spans="1:35" ht="14.5" customHeight="1">
       <c r="A174" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B174" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="C174" s="8" t="s">
         <v>528</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>529</v>
       </c>
       <c r="D174" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F174" s="9"/>
       <c r="G174" s="9"/>
@@ -13883,13 +13890,13 @@
         <v>33</v>
       </c>
       <c r="I174" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J174" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K174" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L174" s="8"/>
       <c r="M174" s="8"/>
@@ -13918,13 +13925,13 @@
     </row>
     <row r="175" spans="1:35" ht="14.5" customHeight="1">
       <c r="A175" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B175" s="8" t="s">
         <v>316</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D175" s="8" t="s">
         <v>75</v>
@@ -13951,10 +13958,10 @@
       <c r="N175" s="8"/>
       <c r="O175" s="8"/>
       <c r="P175" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q175" s="8" t="s">
         <v>622</v>
-      </c>
-      <c r="Q175" s="8" t="s">
-        <v>623</v>
       </c>
       <c r="R175" s="8"/>
       <c r="S175" s="8"/>
@@ -13973,13 +13980,13 @@
     </row>
     <row r="176" spans="1:35" ht="203" customHeight="1">
       <c r="A176" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>325</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D176" s="8" t="s">
         <v>32</v>
@@ -14014,26 +14021,26 @@
         <v>331</v>
       </c>
       <c r="P176" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="Q176" s="8" t="s">
         <v>625</v>
-      </c>
-      <c r="Q176" s="8" t="s">
-        <v>626</v>
       </c>
       <c r="R176" s="8" t="s">
         <v>48</v>
       </c>
       <c r="S176" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="T176" s="8"/>
       <c r="U176" s="8"/>
       <c r="V176" s="8"/>
       <c r="W176" s="8"/>
       <c r="X176" s="11" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Y176" s="11" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Z176" s="8" t="s">
         <v>339</v>
@@ -14056,13 +14063,13 @@
     </row>
     <row r="177" spans="1:35" ht="188.5" customHeight="1">
       <c r="A177" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B177" s="8" t="s">
         <v>342</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>32</v>
@@ -14097,10 +14104,10 @@
         <v>347</v>
       </c>
       <c r="P177" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q177" s="8" t="s">
         <v>622</v>
-      </c>
-      <c r="Q177" s="8" t="s">
-        <v>623</v>
       </c>
       <c r="R177" s="8" t="s">
         <v>33</v>
@@ -14116,7 +14123,7 @@
         <v>161</v>
       </c>
       <c r="Y177" s="11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Z177" s="8" t="s">
         <v>346</v>
@@ -14139,7 +14146,7 @@
     </row>
     <row r="178" spans="1:35" ht="14.5" customHeight="1">
       <c r="A178" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B178" s="31" t="s">
         <v>356</v>
@@ -14184,7 +14191,7 @@
     </row>
     <row r="179" spans="1:35" ht="14.5" customHeight="1">
       <c r="A179" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>367</v>
@@ -14243,13 +14250,13 @@
     </row>
     <row r="180" spans="1:35" ht="14.5" customHeight="1">
       <c r="A180" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B180" s="8" t="s">
         <v>363</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D180" s="8" t="s">
         <v>32</v>
@@ -14298,13 +14305,13 @@
     </row>
     <row r="181" spans="1:35" ht="14.5" customHeight="1">
       <c r="A181" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B181" s="8" t="s">
         <v>357</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D181" s="8" t="s">
         <v>32</v>
@@ -14353,7 +14360,7 @@
     </row>
     <row r="182" spans="1:35" ht="188.5" customHeight="1">
       <c r="A182" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>372</v>
@@ -14386,16 +14393,16 @@
       <c r="N182" s="8"/>
       <c r="O182" s="8"/>
       <c r="P182" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q182" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R182" s="8" t="s">
         <v>48</v>
       </c>
       <c r="S182" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="T182" s="8"/>
       <c r="U182" s="8"/>
@@ -14416,13 +14423,13 @@
     </row>
     <row r="183" spans="1:35" ht="29" customHeight="1">
       <c r="A183" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>380</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D183" s="8" t="s">
         <v>75</v>
@@ -14452,7 +14459,7 @@
         <v>319</v>
       </c>
       <c r="Q183" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="R183" s="8"/>
       <c r="S183" s="8"/>
@@ -14475,13 +14482,13 @@
     </row>
     <row r="184" spans="1:35" ht="14.5" customHeight="1">
       <c r="A184" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B184" s="8" t="s">
         <v>382</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D184" s="8" t="s">
         <v>32</v>
@@ -14495,23 +14502,23 @@
         <v>52</v>
       </c>
       <c r="I184" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J184" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K184" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L184" s="8"/>
       <c r="M184" s="8"/>
       <c r="N184" s="8"/>
       <c r="O184" s="8"/>
       <c r="P184" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="Q184" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R184" s="8"/>
       <c r="S184" s="8"/>
@@ -14534,13 +14541,13 @@
     </row>
     <row r="185" spans="1:35" ht="29" customHeight="1">
       <c r="A185" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B185" s="8" t="s">
         <v>383</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>32</v>
@@ -14554,13 +14561,13 @@
         <v>52</v>
       </c>
       <c r="I185" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J185" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K185" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="L185" s="8"/>
       <c r="M185" s="8"/>
@@ -14570,7 +14577,7 @@
         <v>33</v>
       </c>
       <c r="Q185" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="R185" s="8"/>
       <c r="S185" s="8"/>
@@ -14593,13 +14600,13 @@
     </row>
     <row r="186" spans="1:35" ht="14.5" customHeight="1">
       <c r="A186" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>384</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D186" s="8" t="s">
         <v>32</v>
@@ -14640,19 +14647,19 @@
     </row>
     <row r="187" spans="1:35" ht="14.5" customHeight="1">
       <c r="A187" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B187" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="C187" s="8" t="s">
         <v>644</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>645</v>
       </c>
       <c r="D187" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F187" s="9"/>
       <c r="G187" s="9"/>
@@ -14676,7 +14683,7 @@
         <v>131</v>
       </c>
       <c r="Q187" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="R187" s="8"/>
       <c r="S187" s="8"/>
@@ -14699,19 +14706,19 @@
     </row>
     <row r="188" spans="1:35" ht="14.5" customHeight="1">
       <c r="A188" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B188" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="C188" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>649</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F188" s="9"/>
       <c r="G188" s="9"/>
@@ -14719,13 +14726,13 @@
         <v>52</v>
       </c>
       <c r="I188" s="10" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J188" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K188" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L188" s="8"/>
       <c r="M188" s="8"/>
@@ -14735,7 +14742,7 @@
         <v>48</v>
       </c>
       <c r="Q188" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="R188" s="8" t="s">
         <v>33</v>
@@ -14762,37 +14769,37 @@
     </row>
     <row r="189" spans="1:35" ht="14.5" customHeight="1">
       <c r="A189" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B189" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="C189" s="8" t="s">
         <v>652</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>653</v>
       </c>
       <c r="D189" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H189" s="8" t="s">
         <v>52</v>
       </c>
       <c r="I189" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J189" s="8" t="s">
         <v>52</v>
       </c>
       <c r="K189" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L189" s="8"/>
       <c r="M189" s="8"/>
@@ -14823,19 +14830,19 @@
     </row>
     <row r="190" spans="1:35" ht="14.5" customHeight="1">
       <c r="A190" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B190" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="C190" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="C190" s="8" t="s">
-        <v>657</v>
       </c>
       <c r="D190" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F190" s="9"/>
       <c r="G190" s="9"/>
@@ -14853,7 +14860,7 @@
         <v>48</v>
       </c>
       <c r="S190" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="T190" s="8"/>
       <c r="U190" s="8"/>
@@ -14874,33 +14881,33 @@
     </row>
     <row r="191" spans="1:35" ht="14.5" customHeight="1">
       <c r="A191" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D191" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F191" s="9"/>
       <c r="G191" s="9"/>
       <c r="H191" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I191" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K191" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L191" s="8"/>
       <c r="M191" s="8"/>
@@ -14929,37 +14936,37 @@
     </row>
     <row r="192" spans="1:35" ht="29" customHeight="1">
       <c r="A192" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B192" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="C192" s="8" t="s">
         <v>563</v>
-      </c>
-      <c r="C192" s="8" t="s">
-        <v>564</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>339</v>
       </c>
       <c r="G192" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="H192" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="I192" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="H192" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="I192" s="10" t="s">
-        <v>566</v>
-      </c>
       <c r="J192" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K192" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L192" s="8"/>
       <c r="M192" s="8"/>
@@ -14969,7 +14976,7 @@
         <v>213</v>
       </c>
       <c r="Q192" s="8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R192" s="8"/>
       <c r="S192" s="8"/>
@@ -14992,37 +14999,37 @@
     </row>
     <row r="193" spans="1:35" ht="14.5" customHeight="1">
       <c r="A193" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B193" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="C193" s="8" t="s">
         <v>569</v>
-      </c>
-      <c r="C193" s="8" t="s">
-        <v>570</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G193" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="H193" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="H193" s="8" t="s">
+      <c r="I193" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="I193" s="10" t="s">
-        <v>573</v>
-      </c>
       <c r="J193" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="K193" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="K193" s="10" t="s">
-        <v>573</v>
       </c>
       <c r="L193" s="8"/>
       <c r="M193" s="8"/>
@@ -15053,19 +15060,19 @@
     </row>
     <row r="194" spans="1:35" ht="14.5" customHeight="1">
       <c r="A194" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B194" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="C194" s="8" t="s">
         <v>574</v>
-      </c>
-      <c r="C194" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F194" s="9"/>
       <c r="G194" s="9"/>
@@ -15100,37 +15107,37 @@
     </row>
     <row r="195" spans="1:35" ht="14.5" customHeight="1">
       <c r="A195" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>346</v>
       </c>
       <c r="G195" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="H195" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="I195" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="H195" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="I195" s="10" t="s">
-        <v>579</v>
-      </c>
       <c r="J195" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K195" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L195" s="8"/>
       <c r="M195" s="8"/>
@@ -15140,7 +15147,7 @@
         <v>48</v>
       </c>
       <c r="Q195" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R195" s="8"/>
       <c r="S195" s="8"/>
@@ -15163,33 +15170,33 @@
     </row>
     <row r="196" spans="1:35" ht="43.5" customHeight="1">
       <c r="A196" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B196" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="C196" s="8" t="s">
         <v>581</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>582</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F196" s="9"/>
       <c r="G196" s="9"/>
       <c r="H196" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I196" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J196" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K196" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L196" s="8"/>
       <c r="M196" s="8"/>
@@ -15199,7 +15206,7 @@
         <v>33</v>
       </c>
       <c r="Q196" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R196" s="8"/>
       <c r="S196" s="8"/>
@@ -15222,43 +15229,43 @@
     </row>
     <row r="197" spans="1:35" ht="14.5" customHeight="1">
       <c r="A197" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F197" s="9"/>
       <c r="G197" s="9"/>
       <c r="H197" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="I197" s="30" t="s">
         <v>534</v>
       </c>
-      <c r="I197" s="30" t="s">
-        <v>535</v>
-      </c>
       <c r="J197" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="K197" s="30" t="s">
         <v>534</v>
-      </c>
-      <c r="K197" s="30" t="s">
-        <v>535</v>
       </c>
       <c r="L197" s="8"/>
       <c r="M197" s="8"/>
       <c r="N197" s="8"/>
       <c r="O197" s="8"/>
       <c r="P197" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q197" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R197" s="8"/>
       <c r="S197" s="8"/>
@@ -15277,47 +15284,47 @@
     </row>
     <row r="198" spans="1:35" ht="87" customHeight="1">
       <c r="A198" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B198" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="C198" s="8" t="s">
         <v>537</v>
-      </c>
-      <c r="C198" s="8" t="s">
-        <v>538</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G198" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H198" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="H198" s="8" t="s">
+      <c r="I198" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="I198" s="10" t="s">
-        <v>541</v>
-      </c>
       <c r="J198" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="K198" s="10" t="s">
         <v>540</v>
-      </c>
-      <c r="K198" s="10" t="s">
-        <v>541</v>
       </c>
       <c r="L198" s="8"/>
       <c r="M198" s="8"/>
       <c r="N198" s="8"/>
       <c r="O198" s="8"/>
       <c r="P198" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q198" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="R198" s="8"/>
       <c r="S198" s="8"/>
@@ -15329,19 +15336,19 @@
         <v>48</v>
       </c>
       <c r="Y198" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Z198" s="14" t="s">
         <v>48</v>
       </c>
       <c r="AA198" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AB198" s="49" t="s">
         <v>145</v>
       </c>
       <c r="AC198" s="50" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AD198" s="7"/>
       <c r="AE198" s="7"/>
@@ -15352,47 +15359,47 @@
     </row>
     <row r="199" spans="1:35" ht="87" customHeight="1">
       <c r="A199" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B199" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="C199" s="8" t="s">
         <v>548</v>
-      </c>
-      <c r="C199" s="8" t="s">
-        <v>549</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G199" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="H199" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="H199" s="8" t="s">
+      <c r="I199" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="I199" s="10" t="s">
-        <v>552</v>
-      </c>
       <c r="J199" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="K199" s="10" t="s">
         <v>551</v>
-      </c>
-      <c r="K199" s="10" t="s">
-        <v>552</v>
       </c>
       <c r="L199" s="8"/>
       <c r="M199" s="8"/>
       <c r="N199" s="8"/>
       <c r="O199" s="8"/>
       <c r="P199" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q199" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="Q199" s="8" t="s">
-        <v>556</v>
       </c>
       <c r="R199" s="8"/>
       <c r="S199" s="8"/>
@@ -15410,13 +15417,13 @@
         <v>33</v>
       </c>
       <c r="AA199" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AB199" s="49" t="s">
         <v>161</v>
       </c>
       <c r="AC199" s="50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AD199" s="7"/>
       <c r="AE199" s="7"/>
@@ -15427,7 +15434,7 @@
     </row>
     <row r="200" spans="1:35" ht="14.5" customHeight="1">
       <c r="A200" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>30</v>
@@ -15469,7 +15476,7 @@
         <v>33</v>
       </c>
       <c r="U200" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="V200" s="8"/>
       <c r="W200" s="8"/>
@@ -15492,13 +15499,13 @@
     </row>
     <row r="201" spans="1:35" ht="14.5" customHeight="1">
       <c r="A201" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D201" s="8" t="s">
         <v>32</v>
@@ -15526,7 +15533,7 @@
         <v>48</v>
       </c>
       <c r="Q201" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="R201" s="8"/>
       <c r="S201" s="8"/>
@@ -15534,7 +15541,7 @@
         <v>48</v>
       </c>
       <c r="U201" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="V201" s="8"/>
       <c r="W201" s="8"/>
@@ -15546,7 +15553,7 @@
         <v>48</v>
       </c>
       <c r="AC201" s="50" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AD201" s="7"/>
       <c r="AE201" s="7"/>
@@ -15557,13 +15564,13 @@
     </row>
     <row r="202" spans="1:35" ht="14.5" customHeight="1">
       <c r="A202" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D202" s="8" t="s">
         <v>32</v>
@@ -15595,7 +15602,7 @@
         <v>33</v>
       </c>
       <c r="U202" s="8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="V202" s="8"/>
       <c r="W202" s="8"/>
@@ -15618,7 +15625,7 @@
     </row>
     <row r="203" spans="1:35" ht="14.5" customHeight="1">
       <c r="A203" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>67</v>
@@ -15671,7 +15678,7 @@
     </row>
     <row r="204" spans="1:35" ht="14.5" customHeight="1">
       <c r="A204" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>73</v>
@@ -15718,7 +15725,7 @@
     </row>
     <row r="205" spans="1:35" ht="14.5" customHeight="1">
       <c r="A205" s="11" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>77</v>
@@ -15785,7 +15792,7 @@
     </row>
     <row r="206" spans="1:35" ht="14.5" customHeight="1">
       <c r="A206" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>80</v>
@@ -15837,8 +15844,12 @@
       <c r="S206" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
+      <c r="T206" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="U206" s="9" t="s">
+        <v>82</v>
+      </c>
       <c r="V206" s="9" t="s">
         <v>48</v>
       </c>
@@ -15860,7 +15871,7 @@
     </row>
     <row r="207" spans="1:35" ht="14.5" customHeight="1">
       <c r="A207" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>85</v>
@@ -15904,7 +15915,7 @@
         <v>48</v>
       </c>
       <c r="U207" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="V207" s="8"/>
       <c r="W207" s="8"/>
@@ -15935,7 +15946,7 @@
     </row>
     <row r="208" spans="1:35" ht="14.5" customHeight="1">
       <c r="A208" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>97</v>
@@ -16002,7 +16013,7 @@
     </row>
     <row r="209" spans="1:35" ht="58" customHeight="1">
       <c r="A209" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>106</v>
@@ -16038,7 +16049,7 @@
         <v>48</v>
       </c>
       <c r="Q209" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="R209" s="8"/>
       <c r="S209" s="8"/>
@@ -16046,7 +16057,7 @@
         <v>33</v>
       </c>
       <c r="U209" s="54" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="V209" s="8"/>
       <c r="W209" s="8"/>
@@ -16069,7 +16080,7 @@
     </row>
     <row r="210" spans="1:35" ht="14.5" customHeight="1">
       <c r="A210" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B210" s="8" t="s">
         <v>118</v>
@@ -16113,7 +16124,7 @@
         <v>33</v>
       </c>
       <c r="U210" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="V210" s="8"/>
       <c r="W210" s="8"/>
@@ -16136,7 +16147,7 @@
     </row>
     <row r="211" spans="1:35" ht="14.5" customHeight="1">
       <c r="A211" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B211" s="8" t="s">
         <v>120</v>
@@ -16172,7 +16183,7 @@
         <v>33</v>
       </c>
       <c r="Q211" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R211" s="8"/>
       <c r="S211" s="8"/>
@@ -16195,13 +16206,13 @@
     </row>
     <row r="212" spans="1:35" ht="29" customHeight="1">
       <c r="A212" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B212" s="8" t="s">
         <v>128</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>75</v>
@@ -16254,13 +16265,13 @@
     </row>
     <row r="213" spans="1:35" ht="43.5" customHeight="1">
       <c r="A213" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B213" s="8" t="s">
         <v>136</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D213" s="8" t="s">
         <v>32</v>
@@ -16321,13 +16332,13 @@
     </row>
     <row r="214" spans="1:35" ht="43.5" customHeight="1">
       <c r="A214" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B214" s="8" t="s">
         <v>148</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D214" s="8" t="s">
         <v>32</v>
@@ -16365,7 +16376,7 @@
         <v>33</v>
       </c>
       <c r="U214" s="8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="V214" s="8"/>
       <c r="W214" s="8"/>
@@ -16377,7 +16388,7 @@
         <v>33</v>
       </c>
       <c r="AC214" s="50" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AD214" s="7"/>
       <c r="AE214" s="7"/>
@@ -16388,7 +16399,7 @@
     </row>
     <row r="215" spans="1:35" ht="14.5" customHeight="1">
       <c r="A215" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B215" s="31" t="s">
         <v>179</v>
@@ -16433,7 +16444,7 @@
     </row>
     <row r="216" spans="1:35" ht="14.5" customHeight="1">
       <c r="A216" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B216" s="31" t="s">
         <v>180</v>
@@ -16478,7 +16489,7 @@
     </row>
     <row r="217" spans="1:35" ht="14.5" customHeight="1">
       <c r="A217" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B217" s="31" t="s">
         <v>181</v>
@@ -16523,7 +16534,7 @@
     </row>
     <row r="218" spans="1:35" ht="14.5" customHeight="1">
       <c r="A218" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B218" s="8" t="s">
         <v>182</v>
@@ -16539,12 +16550,6 @@
       </c>
       <c r="F218" s="9"/>
       <c r="G218" s="9"/>
-      <c r="H218" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I218" s="10" t="s">
-        <v>184</v>
-      </c>
       <c r="J218" s="8"/>
       <c r="K218" s="8"/>
       <c r="L218" s="8"/>
@@ -16574,18 +16579,26 @@
     </row>
     <row r="219" spans="1:35" ht="14.5" customHeight="1">
       <c r="A219" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B219" s="35" t="s">
         <v>187</v>
       </c>
       <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
-      <c r="E219" s="8"/>
+      <c r="D219" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E219" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="F219" s="9"/>
       <c r="G219" s="9"/>
-      <c r="H219" s="9"/>
-      <c r="I219" s="9"/>
+      <c r="H219" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I219" s="10" t="s">
+        <v>184</v>
+      </c>
       <c r="J219" s="9"/>
       <c r="K219" s="9"/>
       <c r="L219" s="9"/>
@@ -16615,7 +16628,7 @@
     </row>
     <row r="220" spans="1:35" ht="14.5" customHeight="1">
       <c r="A220" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B220" s="8" t="s">
         <v>188</v>
@@ -16635,7 +16648,7 @@
         <v>52</v>
       </c>
       <c r="I220" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J220" s="8"/>
       <c r="K220" s="8"/>
@@ -16666,13 +16679,13 @@
     </row>
     <row r="221" spans="1:35" ht="14.5" customHeight="1">
       <c r="A221" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B221" s="8" t="s">
         <v>385</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D221" s="8" t="s">
         <v>75</v>
@@ -16725,7 +16738,7 @@
     </row>
     <row r="222" spans="1:35" ht="14.5" customHeight="1">
       <c r="A222" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B222" s="8" t="s">
         <v>390</v>
@@ -16788,7 +16801,7 @@
     </row>
     <row r="223" spans="1:35" ht="14.5" customHeight="1">
       <c r="A223" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B223" s="8" t="s">
         <v>395</v>
@@ -16851,7 +16864,7 @@
     </row>
     <row r="224" spans="1:35" ht="14.5" customHeight="1">
       <c r="A224" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B224" s="31" t="s">
         <v>402</v>
@@ -16896,7 +16909,7 @@
     </row>
     <row r="225" spans="1:35" ht="14.5" customHeight="1">
       <c r="A225" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>403</v>
@@ -16941,10 +16954,10 @@
     </row>
     <row r="226" spans="1:35" ht="14.5" customHeight="1">
       <c r="A226" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B226" s="31" t="s">
-        <v>404</v>
+        <v>761</v>
       </c>
       <c r="C226" s="8"/>
       <c r="D226" s="8" t="s">
@@ -16986,13 +16999,13 @@
     </row>
     <row r="227" spans="1:35" ht="14.5" customHeight="1">
       <c r="A227" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B227" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C227" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="C227" s="8" t="s">
-        <v>406</v>
       </c>
       <c r="D227" s="8" t="s">
         <v>32</v>
@@ -17004,13 +17017,13 @@
         <v>52</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H227" s="8" t="s">
         <v>52</v>
       </c>
       <c r="I227" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="J227" s="8"/>
       <c r="K227" s="8"/>
@@ -17022,7 +17035,7 @@
         <v>52</v>
       </c>
       <c r="Q227" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="R227" s="8"/>
       <c r="S227" s="8"/>
@@ -17045,13 +17058,13 @@
     </row>
     <row r="228" spans="1:35" ht="29" customHeight="1">
       <c r="A228" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B228" s="8" t="s">
         <v>316</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D228" s="8" t="s">
         <v>75</v>
@@ -17074,10 +17087,10 @@
       <c r="N228" s="8"/>
       <c r="O228" s="8"/>
       <c r="P228" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="Q228" s="8" t="s">
         <v>679</v>
-      </c>
-      <c r="Q228" s="8" t="s">
-        <v>680</v>
       </c>
       <c r="R228" s="8"/>
       <c r="S228" s="8"/>
@@ -17100,13 +17113,13 @@
     </row>
     <row r="229" spans="1:35" ht="174" customHeight="1">
       <c r="A229" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>325</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D229" s="8" t="s">
         <v>32</v>
@@ -17118,7 +17131,7 @@
         <v>339</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H229" s="8" t="s">
         <v>328</v>
@@ -17133,10 +17146,10 @@
       <c r="N229" s="8"/>
       <c r="O229" s="8"/>
       <c r="P229" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q229" s="8" t="s">
         <v>683</v>
-      </c>
-      <c r="Q229" s="8" t="s">
-        <v>684</v>
       </c>
       <c r="R229" s="8"/>
       <c r="S229" s="8"/>
@@ -17144,7 +17157,7 @@
         <v>48</v>
       </c>
       <c r="U229" s="8" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="V229" s="8"/>
       <c r="W229" s="8"/>
@@ -17156,7 +17169,7 @@
         <v>48</v>
       </c>
       <c r="AC229" s="50" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AD229" s="7"/>
       <c r="AE229" s="7"/>
@@ -17167,13 +17180,13 @@
     </row>
     <row r="230" spans="1:35" ht="130.5" customHeight="1">
       <c r="A230" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B230" s="8" t="s">
         <v>342</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D230" s="8" t="s">
         <v>32</v>
@@ -17185,13 +17198,13 @@
         <v>346</v>
       </c>
       <c r="G230" s="9" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H230" s="8" t="s">
         <v>344</v>
       </c>
       <c r="I230" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J230" s="8"/>
       <c r="K230" s="8"/>
@@ -17200,10 +17213,10 @@
       <c r="N230" s="8"/>
       <c r="O230" s="8"/>
       <c r="P230" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q230" s="8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="R230" s="8"/>
       <c r="S230" s="8"/>
@@ -17211,7 +17224,7 @@
         <v>33</v>
       </c>
       <c r="U230" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="V230" s="8"/>
       <c r="W230" s="8"/>
@@ -17223,7 +17236,7 @@
         <v>33</v>
       </c>
       <c r="AC230" s="55" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AD230" s="7"/>
       <c r="AE230" s="7"/>
@@ -17234,7 +17247,7 @@
     </row>
     <row r="231" spans="1:35" ht="14.5" customHeight="1">
       <c r="A231" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B231" s="31" t="s">
         <v>356</v>
@@ -17279,13 +17292,13 @@
     </row>
     <row r="232" spans="1:35" ht="14.5" customHeight="1">
       <c r="A232" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B232" s="8" t="s">
         <v>363</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D232" s="8" t="s">
         <v>32</v>
@@ -17330,13 +17343,13 @@
     </row>
     <row r="233" spans="1:35" ht="14.5" customHeight="1">
       <c r="A233" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B233" s="8" t="s">
         <v>357</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D233" s="8" t="s">
         <v>32</v>
@@ -17381,13 +17394,13 @@
     </row>
     <row r="234" spans="1:35" ht="14.5" customHeight="1">
       <c r="A234" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B234" s="8" t="s">
         <v>367</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D234" s="8" t="s">
         <v>32</v>
@@ -17432,7 +17445,7 @@
     </row>
     <row r="235" spans="1:35" ht="159.5" customHeight="1">
       <c r="A235" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B235" s="8" t="s">
         <v>372</v>
@@ -17461,10 +17474,10 @@
       <c r="N235" s="8"/>
       <c r="O235" s="8"/>
       <c r="P235" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q235" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="R235" s="8"/>
       <c r="S235" s="8"/>
@@ -17487,7 +17500,7 @@
     </row>
     <row r="236" spans="1:35" ht="14.5" customHeight="1">
       <c r="A236" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>229</v>
@@ -17521,7 +17534,7 @@
         <v>131</v>
       </c>
       <c r="Q236" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="R236" s="8"/>
       <c r="S236" s="8"/>
@@ -17544,7 +17557,7 @@
     </row>
     <row r="237" spans="1:35" ht="14.5" customHeight="1">
       <c r="A237" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B237" s="37" t="s">
         <v>235</v>
@@ -17564,7 +17577,7 @@
         <v>52</v>
       </c>
       <c r="I237" s="10" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="J237" s="37"/>
       <c r="K237" s="37"/>
@@ -17576,7 +17589,7 @@
         <v>33</v>
       </c>
       <c r="Q237" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="R237" s="37"/>
       <c r="S237" s="37"/>
@@ -17599,7 +17612,7 @@
     </row>
     <row r="238" spans="1:35" ht="14.5" customHeight="1">
       <c r="A238" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B238" s="8" t="s">
         <v>238</v>
@@ -17646,7 +17659,7 @@
     </row>
     <row r="239" spans="1:35" ht="14.5" customHeight="1">
       <c r="A239" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>240</v>
@@ -17693,7 +17706,7 @@
     </row>
     <row r="240" spans="1:35" ht="14.5" customHeight="1">
       <c r="A240" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B240" s="8" t="s">
         <v>242</v>
@@ -17740,7 +17753,7 @@
     </row>
     <row r="241" spans="1:35" ht="14.5" customHeight="1">
       <c r="A241" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B241" s="8" t="s">
         <v>244</v>
@@ -17760,7 +17773,7 @@
         <v>52</v>
       </c>
       <c r="I241" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J241" s="8"/>
       <c r="K241" s="8"/>
@@ -17789,7 +17802,7 @@
     </row>
     <row r="242" spans="1:35" ht="29" customHeight="1">
       <c r="A242" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B242" s="8" t="s">
         <v>249</v>
@@ -17809,7 +17822,7 @@
         <v>52</v>
       </c>
       <c r="I242" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="J242" s="8"/>
       <c r="K242" s="8"/>
@@ -17821,7 +17834,7 @@
         <v>48</v>
       </c>
       <c r="Q242" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="R242" s="8"/>
       <c r="S242" s="8"/>
@@ -17844,7 +17857,7 @@
     </row>
     <row r="243" spans="1:35" ht="14.5" customHeight="1">
       <c r="A243" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B243" s="8" t="s">
         <v>257</v>
@@ -17891,7 +17904,7 @@
     </row>
     <row r="244" spans="1:35" ht="29" customHeight="1">
       <c r="A244" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B244" s="8" t="s">
         <v>250</v>
@@ -17936,13 +17949,13 @@
     </row>
     <row r="245" spans="1:35" ht="29" customHeight="1">
       <c r="A245" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B245" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D245" s="8" t="s">
         <v>75</v>
@@ -17964,7 +17977,7 @@
         <v>131</v>
       </c>
       <c r="Q245" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="R245" s="8"/>
       <c r="S245" s="8"/>
@@ -17987,13 +18000,13 @@
     </row>
     <row r="246" spans="1:35" ht="14.5" customHeight="1">
       <c r="A246" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>297</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D246" s="8" t="s">
         <v>32</v>
@@ -18015,7 +18028,7 @@
         <v>48</v>
       </c>
       <c r="Q246" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="R246" s="8"/>
       <c r="S246" s="8"/>
@@ -18038,7 +18051,7 @@
     </row>
     <row r="247" spans="1:35" ht="14.5" customHeight="1">
       <c r="A247" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B247" s="11" t="s">
         <v>303</v>
@@ -18085,7 +18098,7 @@
     </row>
     <row r="248" spans="1:35" ht="29" customHeight="1">
       <c r="A248" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B248" s="8" t="s">
         <v>305</v>
@@ -18113,7 +18126,7 @@
         <v>33</v>
       </c>
       <c r="Q248" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="R248" s="8"/>
       <c r="S248" s="8"/>
@@ -18136,7 +18149,7 @@
     </row>
     <row r="249" spans="1:35" ht="14.5" customHeight="1">
       <c r="A249" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B249" s="8" t="s">
         <v>312</v>
@@ -18183,19 +18196,19 @@
     </row>
     <row r="250" spans="1:35" ht="14.5" customHeight="1">
       <c r="A250" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D250" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F250" s="9"/>
       <c r="G250" s="9"/>
@@ -18203,7 +18216,7 @@
         <v>131</v>
       </c>
       <c r="I250" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J250" s="8"/>
       <c r="K250" s="8"/>
@@ -18234,31 +18247,31 @@
     </row>
     <row r="251" spans="1:35" ht="14.5" customHeight="1">
       <c r="A251" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B251" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C251" s="8" t="s">
         <v>461</v>
-      </c>
-      <c r="C251" s="8" t="s">
-        <v>462</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G251" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I251" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J251" s="8"/>
       <c r="K251" s="8"/>
@@ -18289,19 +18302,19 @@
     </row>
     <row r="252" spans="1:35" ht="29" customHeight="1">
       <c r="A252" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B252" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C252" s="8" t="s">
         <v>470</v>
-      </c>
-      <c r="C252" s="8" t="s">
-        <v>471</v>
       </c>
       <c r="D252" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F252" s="9"/>
       <c r="G252" s="9"/>
@@ -18309,7 +18322,7 @@
         <v>52</v>
       </c>
       <c r="I252" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J252" s="8"/>
       <c r="K252" s="8"/>
@@ -18340,19 +18353,19 @@
     </row>
     <row r="253" spans="1:35" ht="29" customHeight="1">
       <c r="A253" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B253" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C253" s="8" t="s">
         <v>474</v>
-      </c>
-      <c r="C253" s="8" t="s">
-        <v>475</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F253" s="9"/>
       <c r="G253" s="9"/>
@@ -18360,7 +18373,7 @@
         <v>52</v>
       </c>
       <c r="I253" s="10" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J253" s="8"/>
       <c r="K253" s="8"/>
@@ -18391,19 +18404,19 @@
     </row>
     <row r="254" spans="1:35" ht="29" customHeight="1">
       <c r="A254" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B254" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="C254" s="8" t="s">
         <v>478</v>
-      </c>
-      <c r="C254" s="8" t="s">
-        <v>479</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E254" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F254" s="9"/>
       <c r="G254" s="9"/>
@@ -18411,7 +18424,7 @@
         <v>52</v>
       </c>
       <c r="I254" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J254" s="8"/>
       <c r="K254" s="8"/>
@@ -18442,19 +18455,19 @@
     </row>
     <row r="255" spans="1:35" ht="29" customHeight="1">
       <c r="A255" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B255" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C255" s="8" t="s">
         <v>482</v>
-      </c>
-      <c r="C255" s="8" t="s">
-        <v>483</v>
       </c>
       <c r="D255" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E255" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F255" s="9"/>
       <c r="G255" s="9"/>
@@ -18462,7 +18475,7 @@
         <v>52</v>
       </c>
       <c r="I255" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J255" s="8"/>
       <c r="K255" s="8"/>
@@ -18493,19 +18506,19 @@
     </row>
     <row r="256" spans="1:35" ht="29" customHeight="1">
       <c r="A256" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B256" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C256" s="8" t="s">
         <v>493</v>
-      </c>
-      <c r="C256" s="8" t="s">
-        <v>494</v>
       </c>
       <c r="D256" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F256" s="9"/>
       <c r="G256" s="9"/>
@@ -18513,7 +18526,7 @@
         <v>52</v>
       </c>
       <c r="I256" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J256" s="8"/>
       <c r="K256" s="8"/>
@@ -18544,19 +18557,19 @@
     </row>
     <row r="257" spans="1:35" ht="14.5" customHeight="1">
       <c r="A257" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B257" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C257" s="8" t="s">
         <v>487</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>488</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E257" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F257" s="9"/>
       <c r="G257" s="9"/>
@@ -18564,7 +18577,7 @@
         <v>33</v>
       </c>
       <c r="I257" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J257" s="8"/>
       <c r="K257" s="8"/>
@@ -18595,19 +18608,19 @@
     </row>
     <row r="258" spans="1:35" ht="29" customHeight="1">
       <c r="A258" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B258" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C258" s="8" t="s">
         <v>498</v>
-      </c>
-      <c r="C258" s="8" t="s">
-        <v>499</v>
       </c>
       <c r="D258" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E258" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F258" s="9"/>
       <c r="G258" s="9"/>
@@ -18615,7 +18628,7 @@
         <v>52</v>
       </c>
       <c r="I258" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J258" s="8"/>
       <c r="K258" s="8"/>
@@ -18646,19 +18659,19 @@
     </row>
     <row r="259" spans="1:35" ht="14.5" customHeight="1">
       <c r="A259" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B259" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="C259" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="C259" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E259" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F259" s="9"/>
       <c r="G259" s="9"/>
@@ -18693,19 +18706,19 @@
     </row>
     <row r="260" spans="1:35" ht="14.5" customHeight="1">
       <c r="A260" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B260" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="C260" s="8" t="s">
         <v>703</v>
-      </c>
-      <c r="C260" s="8" t="s">
-        <v>704</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F260" s="9"/>
       <c r="G260" s="9"/>
@@ -18725,7 +18738,7 @@
         <v>131</v>
       </c>
       <c r="Q260" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="R260" s="8"/>
       <c r="S260" s="8"/>
@@ -18748,19 +18761,19 @@
     </row>
     <row r="261" spans="1:35" ht="14.5" customHeight="1">
       <c r="A261" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B261" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="C261" s="8" t="s">
         <v>707</v>
-      </c>
-      <c r="C261" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="D261" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E261" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F261" s="9"/>
       <c r="G261" s="9"/>
@@ -18768,7 +18781,7 @@
         <v>52</v>
       </c>
       <c r="I261" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J261" s="8"/>
       <c r="K261" s="8"/>
@@ -18780,7 +18793,7 @@
         <v>33</v>
       </c>
       <c r="Q261" s="8" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="R261" s="8"/>
       <c r="S261" s="8"/>
@@ -18803,19 +18816,19 @@
     </row>
     <row r="262" spans="1:35" ht="14.5" customHeight="1">
       <c r="A262" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B262" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="C262" s="8" t="s">
         <v>711</v>
-      </c>
-      <c r="C262" s="8" t="s">
-        <v>712</v>
       </c>
       <c r="D262" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F262" s="9"/>
       <c r="G262" s="9"/>
@@ -18823,7 +18836,7 @@
         <v>52</v>
       </c>
       <c r="I262" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="J262" s="8"/>
       <c r="K262" s="8"/>
@@ -18835,7 +18848,7 @@
         <v>33</v>
       </c>
       <c r="Q262" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="R262" s="8"/>
       <c r="S262" s="8"/>
@@ -18858,19 +18871,19 @@
     </row>
     <row r="263" spans="1:35" ht="14.5" customHeight="1">
       <c r="A263" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B263" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C263" s="8" t="s">
         <v>715</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>716</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
@@ -18878,7 +18891,7 @@
         <v>52</v>
       </c>
       <c r="I263" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J263" s="8"/>
       <c r="K263" s="8"/>
@@ -18890,7 +18903,7 @@
         <v>33</v>
       </c>
       <c r="Q263" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="R263" s="8"/>
       <c r="S263" s="8"/>
@@ -18913,19 +18926,19 @@
     </row>
     <row r="264" spans="1:35" ht="14.5" customHeight="1">
       <c r="A264" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B264" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="C264" s="8" t="s">
         <v>719</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>720</v>
       </c>
       <c r="D264" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E264" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F264" s="9"/>
       <c r="G264" s="9"/>
@@ -18960,19 +18973,19 @@
     </row>
     <row r="265" spans="1:35" ht="14.5" customHeight="1">
       <c r="A265" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B265" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C265" s="8" t="s">
         <v>721</v>
-      </c>
-      <c r="C265" s="8" t="s">
-        <v>722</v>
       </c>
       <c r="D265" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
@@ -18980,7 +18993,7 @@
         <v>52</v>
       </c>
       <c r="I265" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="J265" s="8"/>
       <c r="K265" s="8"/>
@@ -18992,7 +19005,7 @@
         <v>33</v>
       </c>
       <c r="Q265" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="R265" s="8"/>
       <c r="S265" s="8"/>
@@ -19015,19 +19028,19 @@
     </row>
     <row r="266" spans="1:35" ht="14.5" customHeight="1">
       <c r="A266" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B266" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="C266" s="8" t="s">
         <v>725</v>
-      </c>
-      <c r="C266" s="8" t="s">
-        <v>726</v>
       </c>
       <c r="D266" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
@@ -19043,7 +19056,7 @@
         <v>33</v>
       </c>
       <c r="Q266" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R266" s="8"/>
       <c r="S266" s="8"/>
@@ -19066,17 +19079,17 @@
     </row>
     <row r="267" spans="1:35" ht="14.5" customHeight="1">
       <c r="A267" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C267" s="8"/>
       <c r="D267" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E267" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F267" s="9"/>
       <c r="G267" s="56"/>
@@ -19084,7 +19097,7 @@
         <v>52</v>
       </c>
       <c r="I267" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="J267" s="8"/>
       <c r="K267" s="8"/>
@@ -19096,7 +19109,7 @@
         <v>33</v>
       </c>
       <c r="Q267" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="R267" s="8"/>
       <c r="S267" s="8"/>
@@ -19119,17 +19132,17 @@
     </row>
     <row r="268" spans="1:35" ht="14.5" customHeight="1">
       <c r="A268" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C268" s="8"/>
       <c r="D268" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E268" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F268" s="9"/>
       <c r="G268" s="9"/>
@@ -19137,7 +19150,7 @@
         <v>52</v>
       </c>
       <c r="I268" s="10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J268" s="8"/>
       <c r="K268" s="8"/>
@@ -19168,31 +19181,31 @@
     </row>
     <row r="269" spans="1:35" ht="14.5" customHeight="1">
       <c r="A269" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B269" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="C269" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="C269" s="8" t="s">
-        <v>735</v>
       </c>
       <c r="D269" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G269" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H269" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I269" s="10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J269" s="8"/>
       <c r="K269" s="8"/>
@@ -19223,25 +19236,25 @@
     </row>
     <row r="270" spans="1:35" ht="14.5" customHeight="1">
       <c r="A270" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B270" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="C270" s="8" t="s">
         <v>738</v>
-      </c>
-      <c r="C270" s="8" t="s">
-        <v>739</v>
       </c>
       <c r="D270" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E270" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G270" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H270" s="8"/>
       <c r="I270" s="10"/>
@@ -19274,17 +19287,17 @@
     </row>
     <row r="271" spans="1:35" ht="14.5" customHeight="1">
       <c r="A271" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C271" s="8"/>
       <c r="D271" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E271" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F271" s="9"/>
       <c r="G271" s="9"/>
@@ -19302,7 +19315,7 @@
       <c r="O271" s="8"/>
       <c r="P271" s="8"/>
       <c r="Q271" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="R271" s="8"/>
       <c r="S271" s="8"/>
@@ -19325,17 +19338,17 @@
     </row>
     <row r="272" spans="1:35" ht="29" customHeight="1">
       <c r="A272" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C272" s="8"/>
       <c r="D272" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E272" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F272" s="9"/>
       <c r="G272" s="9"/>
@@ -19343,7 +19356,7 @@
         <v>52</v>
       </c>
       <c r="I272" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J272" s="8"/>
       <c r="K272" s="8"/>
@@ -19352,10 +19365,10 @@
       <c r="N272" s="8"/>
       <c r="O272" s="8"/>
       <c r="P272" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q272" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="R272" s="8"/>
       <c r="S272" s="8"/>
@@ -19378,17 +19391,17 @@
     </row>
     <row r="273" spans="1:35" ht="29" customHeight="1">
       <c r="A273" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C273" s="8"/>
       <c r="D273" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F273" s="9"/>
       <c r="G273" s="9"/>
@@ -19396,7 +19409,7 @@
         <v>52</v>
       </c>
       <c r="I273" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J273" s="8"/>
       <c r="K273" s="8"/>
@@ -19405,10 +19418,10 @@
       <c r="N273" s="8"/>
       <c r="O273" s="8"/>
       <c r="P273" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q273" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="R273" s="8"/>
       <c r="S273" s="8"/>
@@ -19431,19 +19444,19 @@
     </row>
     <row r="274" spans="1:35" ht="14.5" customHeight="1">
       <c r="A274" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B274" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C274" s="8" t="s">
         <v>409</v>
-      </c>
-      <c r="C274" s="8" t="s">
-        <v>410</v>
       </c>
       <c r="D274" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F274" s="9"/>
       <c r="G274" s="9"/>
@@ -19451,7 +19464,7 @@
         <v>131</v>
       </c>
       <c r="I274" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J274" s="8"/>
       <c r="K274" s="8"/>
@@ -19463,7 +19476,7 @@
         <v>131</v>
       </c>
       <c r="Q274" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R274" s="8"/>
       <c r="S274" s="8"/>
@@ -19486,19 +19499,19 @@
     </row>
     <row r="275" spans="1:35" ht="14.5" customHeight="1">
       <c r="A275" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B275" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C275" s="8" t="s">
         <v>414</v>
-      </c>
-      <c r="C275" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="D275" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>48</v>
@@ -19549,31 +19562,31 @@
     </row>
     <row r="276" spans="1:35" ht="14.5" customHeight="1">
       <c r="A276" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B276" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="C276" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="C276" s="8" t="s">
-        <v>418</v>
       </c>
       <c r="D276" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G276" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H276" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I276" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J276" s="8"/>
       <c r="K276" s="8"/>
@@ -19585,7 +19598,7 @@
         <v>33</v>
       </c>
       <c r="Q276" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R276" s="8"/>
       <c r="S276" s="8"/>
@@ -19601,7 +19614,7 @@
         <v>33</v>
       </c>
       <c r="AC276" s="50" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AD276" s="7"/>
       <c r="AE276" s="7"/>
@@ -19612,31 +19625,31 @@
     </row>
     <row r="277" spans="1:35" ht="29" customHeight="1">
       <c r="A277" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B277" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="C277" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="C277" s="8" t="s">
-        <v>427</v>
       </c>
       <c r="D277" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G277" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>48</v>
       </c>
       <c r="I277" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J277" s="8"/>
       <c r="K277" s="8"/>
@@ -19648,7 +19661,7 @@
         <v>48</v>
       </c>
       <c r="Q277" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R277" s="8"/>
       <c r="S277" s="8"/>
@@ -19664,7 +19677,7 @@
         <v>48</v>
       </c>
       <c r="AC277" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AD277" s="7"/>
       <c r="AE277" s="7"/>
@@ -19675,31 +19688,31 @@
     </row>
     <row r="278" spans="1:35" ht="14.5" customHeight="1">
       <c r="A278" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B278" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C278" s="8" t="s">
         <v>435</v>
-      </c>
-      <c r="C278" s="8" t="s">
-        <v>436</v>
       </c>
       <c r="D278" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G278" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H278" s="8" t="s">
         <v>33</v>
       </c>
       <c r="I278" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J278" s="8"/>
       <c r="K278" s="8"/>
@@ -19711,7 +19724,7 @@
         <v>33</v>
       </c>
       <c r="Q278" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R278" s="8"/>
       <c r="S278" s="8"/>
@@ -19727,7 +19740,7 @@
         <v>33</v>
       </c>
       <c r="AC278" s="50" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AD278" s="7"/>
       <c r="AE278" s="7"/>
@@ -19738,27 +19751,27 @@
     </row>
     <row r="279" spans="1:35" ht="14.5" customHeight="1">
       <c r="A279" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D279" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F279" s="9"/>
       <c r="G279" s="9"/>
       <c r="H279" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I279" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J279" s="8"/>
       <c r="K279" s="8"/>
@@ -19789,31 +19802,31 @@
     </row>
     <row r="280" spans="1:35" ht="29" customHeight="1">
       <c r="A280" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B280" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="C280" s="8" t="s">
         <v>563</v>
-      </c>
-      <c r="C280" s="8" t="s">
-        <v>564</v>
       </c>
       <c r="D280" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E280" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>339</v>
       </c>
       <c r="G280" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="H280" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="I280" s="10" t="s">
         <v>565</v>
-      </c>
-      <c r="H280" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="I280" s="10" t="s">
-        <v>566</v>
       </c>
       <c r="J280" s="8"/>
       <c r="K280" s="8"/>
@@ -19825,7 +19838,7 @@
         <v>213</v>
       </c>
       <c r="Q280" s="8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R280" s="8"/>
       <c r="S280" s="8"/>
@@ -19833,7 +19846,7 @@
         <v>48</v>
       </c>
       <c r="U280" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="V280" s="8"/>
       <c r="W280" s="8"/>
@@ -19852,31 +19865,31 @@
     </row>
     <row r="281" spans="1:35" ht="14.5" customHeight="1">
       <c r="A281" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B281" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="C281" s="8" t="s">
         <v>569</v>
-      </c>
-      <c r="C281" s="8" t="s">
-        <v>570</v>
       </c>
       <c r="D281" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E281" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G281" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="H281" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="H281" s="8" t="s">
+      <c r="I281" s="10" t="s">
         <v>572</v>
-      </c>
-      <c r="I281" s="10" t="s">
-        <v>573</v>
       </c>
       <c r="J281" s="8"/>
       <c r="K281" s="8"/>
@@ -19896,7 +19909,7 @@
         <v>33</v>
       </c>
       <c r="U281" s="8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="V281" s="8"/>
       <c r="W281" s="8"/>
@@ -19915,19 +19928,19 @@
     </row>
     <row r="282" spans="1:35" ht="14.5" customHeight="1">
       <c r="A282" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B282" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="C282" s="8" t="s">
         <v>574</v>
-      </c>
-      <c r="C282" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="D282" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E282" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F282" s="9"/>
       <c r="G282" s="9"/>
@@ -19962,31 +19975,31 @@
     </row>
     <row r="283" spans="1:35" ht="14.5" customHeight="1">
       <c r="A283" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D283" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>346</v>
       </c>
       <c r="G283" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="H283" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="I283" s="10" t="s">
         <v>578</v>
-      </c>
-      <c r="H283" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="I283" s="10" t="s">
-        <v>579</v>
       </c>
       <c r="J283" s="8"/>
       <c r="K283" s="8"/>
@@ -19998,7 +20011,7 @@
         <v>48</v>
       </c>
       <c r="Q283" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R283" s="8"/>
       <c r="S283" s="8"/>
@@ -20006,7 +20019,7 @@
         <v>48</v>
       </c>
       <c r="U283" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="V283" s="8"/>
       <c r="W283" s="8"/>
@@ -20025,27 +20038,27 @@
     </row>
     <row r="284" spans="1:35" ht="29" customHeight="1">
       <c r="A284" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B284" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="C284" s="8" t="s">
         <v>581</v>
-      </c>
-      <c r="C284" s="8" t="s">
-        <v>582</v>
       </c>
       <c r="D284" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E284" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F284" s="9"/>
       <c r="G284" s="9"/>
       <c r="H284" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I284" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J284" s="8"/>
       <c r="K284" s="8"/>
@@ -20057,7 +20070,7 @@
         <v>33</v>
       </c>
       <c r="Q284" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R284" s="8"/>
       <c r="S284" s="8"/>
@@ -20080,19 +20093,19 @@
     </row>
     <row r="285" spans="1:35" ht="43.5" customHeight="1">
       <c r="A285" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D285" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E285" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F285" s="9"/>
       <c r="G285" s="9"/>
@@ -20100,7 +20113,7 @@
         <v>131</v>
       </c>
       <c r="I285" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J285" s="8"/>
       <c r="K285" s="8"/>
@@ -20109,10 +20122,10 @@
       <c r="N285" s="8"/>
       <c r="O285" s="8"/>
       <c r="P285" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q285" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="R285" s="8"/>
       <c r="S285" s="8"/>
@@ -20135,19 +20148,19 @@
     </row>
     <row r="286" spans="1:35" ht="14.5" customHeight="1">
       <c r="A286" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D286" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E286" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F286" s="9"/>
       <c r="G286" s="9"/>
@@ -20155,7 +20168,7 @@
         <v>33</v>
       </c>
       <c r="I286" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J286" s="8"/>
       <c r="K286" s="8"/>
@@ -20164,10 +20177,10 @@
       <c r="N286" s="8"/>
       <c r="O286" s="8"/>
       <c r="P286" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q286" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="R286" s="8"/>
       <c r="S286" s="8"/>
@@ -20190,19 +20203,19 @@
     </row>
     <row r="287" spans="1:35" ht="14.5" customHeight="1">
       <c r="A287" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B287" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="C287" s="8" t="s">
         <v>517</v>
-      </c>
-      <c r="C287" s="8" t="s">
-        <v>518</v>
       </c>
       <c r="D287" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F287" s="9"/>
       <c r="G287" s="9"/>
@@ -20210,7 +20223,7 @@
         <v>33</v>
       </c>
       <c r="I287" s="10" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J287" s="8"/>
       <c r="K287" s="8"/>
@@ -20241,19 +20254,19 @@
     </row>
     <row r="288" spans="1:35" ht="43.5" customHeight="1">
       <c r="A288" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B288" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C288" s="8" t="s">
         <v>520</v>
-      </c>
-      <c r="C288" s="8" t="s">
-        <v>521</v>
       </c>
       <c r="D288" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E288" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F288" s="9"/>
       <c r="G288" s="9"/>
@@ -20261,7 +20274,7 @@
         <v>33</v>
       </c>
       <c r="I288" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J288" s="8"/>
       <c r="K288" s="8"/>
@@ -20270,10 +20283,10 @@
       <c r="N288" s="8"/>
       <c r="O288" s="8"/>
       <c r="P288" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q288" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="R288" s="8"/>
       <c r="S288" s="8"/>
@@ -20296,19 +20309,19 @@
     </row>
     <row r="289" spans="1:35" ht="14.5" customHeight="1">
       <c r="A289" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B289" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="C289" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="C289" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="D289" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F289" s="9"/>
       <c r="G289" s="9"/>
@@ -20343,19 +20356,19 @@
     </row>
     <row r="290" spans="1:35" ht="14.5" customHeight="1">
       <c r="A290" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B290" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C290" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="C290" s="8" t="s">
-        <v>527</v>
       </c>
       <c r="D290" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E290" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F290" s="9"/>
       <c r="G290" s="9"/>
@@ -20390,19 +20403,19 @@
     </row>
     <row r="291" spans="1:35" ht="14.5" customHeight="1">
       <c r="A291" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B291" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="C291" s="8" t="s">
         <v>528</v>
-      </c>
-      <c r="C291" s="8" t="s">
-        <v>529</v>
       </c>
       <c r="D291" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E291" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F291" s="9"/>
       <c r="G291" s="9"/>
@@ -20410,7 +20423,7 @@
         <v>33</v>
       </c>
       <c r="I291" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J291" s="8"/>
       <c r="K291" s="8"/>
@@ -20441,27 +20454,27 @@
     </row>
     <row r="292" spans="1:35" ht="14.5" customHeight="1">
       <c r="A292" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D292" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F292" s="9"/>
       <c r="G292" s="9"/>
       <c r="H292" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="I292" s="30" t="s">
         <v>534</v>
-      </c>
-      <c r="I292" s="30" t="s">
-        <v>535</v>
       </c>
       <c r="J292" s="8"/>
       <c r="K292" s="8"/>
@@ -20470,10 +20483,10 @@
       <c r="N292" s="8"/>
       <c r="O292" s="8"/>
       <c r="P292" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q292" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R292" s="8"/>
       <c r="S292" s="8"/>
@@ -20496,31 +20509,31 @@
     </row>
     <row r="293" spans="1:35" ht="72.5" customHeight="1">
       <c r="A293" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B293" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="C293" s="8" t="s">
         <v>537</v>
-      </c>
-      <c r="C293" s="8" t="s">
-        <v>538</v>
       </c>
       <c r="D293" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E293" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G293" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H293" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="H293" s="8" t="s">
+      <c r="I293" s="10" t="s">
         <v>540</v>
-      </c>
-      <c r="I293" s="10" t="s">
-        <v>541</v>
       </c>
       <c r="J293" s="8"/>
       <c r="K293" s="8"/>
@@ -20529,10 +20542,10 @@
       <c r="N293" s="8"/>
       <c r="O293" s="8"/>
       <c r="P293" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q293" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="R293" s="8"/>
       <c r="S293" s="8"/>
@@ -20548,7 +20561,7 @@
         <v>48</v>
       </c>
       <c r="AC293" s="50" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AD293" s="7"/>
       <c r="AE293" s="7"/>
@@ -20559,31 +20572,31 @@
     </row>
     <row r="294" spans="1:35" ht="72.5" customHeight="1">
       <c r="A294" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B294" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="C294" s="8" t="s">
         <v>548</v>
-      </c>
-      <c r="C294" s="8" t="s">
-        <v>549</v>
       </c>
       <c r="D294" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E294" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G294" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="H294" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="H294" s="8" t="s">
+      <c r="I294" s="10" t="s">
         <v>551</v>
-      </c>
-      <c r="I294" s="10" t="s">
-        <v>552</v>
       </c>
       <c r="J294" s="8"/>
       <c r="K294" s="8"/>
@@ -20592,10 +20605,10 @@
       <c r="N294" s="8"/>
       <c r="O294" s="8"/>
       <c r="P294" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q294" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="Q294" s="8" t="s">
-        <v>556</v>
       </c>
       <c r="R294" s="8"/>
       <c r="S294" s="8"/>
@@ -20611,7 +20624,7 @@
         <v>33</v>
       </c>
       <c r="AC294" s="50" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AD294" s="7"/>
       <c r="AE294" s="7"/>

--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D0E6D2-C1C4-4370-A313-49581D521CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F899D4-B510-48A0-830F-DDE2D11E34F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3791" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3788" uniqueCount="891">
   <si>
     <t>Entity Category</t>
   </si>
@@ -2168,9 +2168,6 @@
     <t>"CFTC RED List record"</t>
   </si>
   <si>
-    <t>"Category:" | category</t>
-  </si>
-  <si>
     <t>Names associated with the organization</t>
   </si>
   <si>
@@ -2219,9 +2216,6 @@
     <t>"Listing Date"</t>
   </si>
   <si>
-    <t>"Data as Of"</t>
-  </si>
-  <si>
     <t>type.text | Organization Established Date | valueDate.isApproximate</t>
   </si>
   <si>
@@ -2294,9 +2288,6 @@
     <t>ENTITY_ADDRESS.NOTE</t>
   </si>
   <si>
-    <t>"Municipality/District: " | municipality_province</t>
-  </si>
-  <si>
     <t>Alternate or former names of the organization</t>
   </si>
   <si>
@@ -2417,9 +2408,6 @@
     <t>detail.web_address</t>
   </si>
   <si>
-    <t>expand(contact_number, /) * expand(eMail, /)</t>
-  </si>
-  <si>
     <t>Additional notes regarding the contact information</t>
   </si>
   <si>
@@ -2502,9 +2490,6 @@
   </si>
   <si>
     <t>Current status of the measure</t>
-  </si>
-  <si>
-    <t>license_status</t>
   </si>
   <si>
     <t>"License Status:" | license_status</t>
@@ -2831,9 +2816,6 @@
 offenses * saction_imposed * project * category</t>
   </si>
   <si>
-    <t xml:space="preserve">concat_path </t>
-  </si>
-  <si>
     <t>"Managed By" * "Contractor Of"</t>
   </si>
   <si>
@@ -2844,6 +2826,18 @@
   </si>
   <si>
     <t>"Sanction Imposed:" | saction_imposed</t>
+  </si>
+  <si>
+    <t>explode * explode</t>
+  </si>
+  <si>
+    <t>contact_number::/ * eMail::/</t>
+  </si>
+  <si>
+    <t>"Municipality/District:" | municipality_province</t>
+  </si>
+  <si>
+    <t>is_valid</t>
   </si>
 </sst>
 </file>
@@ -3061,7 +3055,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3139,6 +3133,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3510,16 +3507,16 @@
         <v>34</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="AN1" s="9"/>
       <c r="AO1" s="9"/>
@@ -12067,8 +12064,12 @@
       <c r="AK120" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="AL120" s="8"/>
-      <c r="AM120" s="8"/>
+      <c r="AL120" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM120" s="9" t="s">
+        <v>680</v>
+      </c>
       <c r="AN120" s="9"/>
       <c r="AO120" s="9"/>
       <c r="AP120" s="9"/>
@@ -12825,12 +12826,8 @@
       </c>
       <c r="AJ128" s="8"/>
       <c r="AK128" s="8"/>
-      <c r="AL128" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AM128" s="8" t="s">
-        <v>670</v>
-      </c>
+      <c r="AL128" s="5"/>
+      <c r="AM128" s="8"/>
       <c r="AN128" s="9"/>
       <c r="AO128" s="9"/>
       <c r="AP128" s="9"/>
@@ -12843,7 +12840,7 @@
         <v>146</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>85</v>
@@ -12921,7 +12918,7 @@
         <v>156</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>38</v>
@@ -13019,7 +13016,7 @@
         <v>167</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>38</v>
@@ -13051,7 +13048,7 @@
         <v>39</v>
       </c>
       <c r="O131" s="5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P131" s="5" t="s">
         <v>173</v>
@@ -13073,7 +13070,7 @@
         <v>177</v>
       </c>
       <c r="Y131" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="Z131" s="5" t="s">
         <v>39</v>
@@ -13095,19 +13092,19 @@
         <v>39</v>
       </c>
       <c r="AI131" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AJ131" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AK131" s="8" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AL131" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM131" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AN131" s="9"/>
       <c r="AO131" s="9"/>
@@ -13411,7 +13408,7 @@
         <v>39</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>213</v>
@@ -13549,13 +13546,13 @@
         <v>59</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J139" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K139" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
@@ -13595,16 +13592,10 @@
         <v>39</v>
       </c>
       <c r="AI139" s="8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AJ139" s="8"/>
       <c r="AK139" s="8"/>
-      <c r="AL139" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM139" s="9" t="s">
-        <v>681</v>
-      </c>
       <c r="AO139" s="9"/>
       <c r="AP139" s="9"/>
     </row>
@@ -13789,13 +13780,13 @@
         <v>59</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="J143" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
@@ -13850,13 +13841,13 @@
         <v>59</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J144" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K144" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
@@ -13866,7 +13857,7 @@
         <v>55</v>
       </c>
       <c r="Q144" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="R144" s="5" t="s">
         <v>55</v>
@@ -13886,7 +13877,7 @@
         <v>55</v>
       </c>
       <c r="AC144" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AD144" s="5"/>
       <c r="AE144" s="5"/>
@@ -13896,16 +13887,12 @@
         <v>55</v>
       </c>
       <c r="AI144" s="8" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AJ144" s="5"/>
       <c r="AK144" s="5"/>
-      <c r="AL144" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="AM144" s="9" t="s">
-        <v>687</v>
-      </c>
+      <c r="AL144" s="5"/>
+      <c r="AM144" s="9"/>
       <c r="AO144" s="9"/>
       <c r="AP144" s="9"/>
     </row>
@@ -13931,13 +13918,13 @@
         <v>59</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J145" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
@@ -13965,7 +13952,7 @@
         <v>55</v>
       </c>
       <c r="AI145" s="8" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AJ145" s="5"/>
       <c r="AK145" s="5"/>
@@ -14036,7 +14023,7 @@
         <v>323</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>85</v>
@@ -14098,7 +14085,7 @@
         <v>329</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>38</v>
@@ -14112,13 +14099,13 @@
         <v>59</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K148" s="5" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
@@ -14138,7 +14125,7 @@
         <v>55</v>
       </c>
       <c r="AA148" s="5" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AB148" s="5"/>
       <c r="AC148" s="5"/>
@@ -14150,7 +14137,7 @@
         <v>55</v>
       </c>
       <c r="AI148" s="8" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="AJ148" s="5"/>
       <c r="AK148" s="5"/>
@@ -14240,13 +14227,13 @@
         <v>59</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K150" s="5" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
@@ -14274,7 +14261,7 @@
         <v>238</v>
       </c>
       <c r="AI150" s="19" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AJ150" s="5"/>
       <c r="AK150" s="5"/>
@@ -14336,7 +14323,7 @@
         <v>39</v>
       </c>
       <c r="AI151" s="8" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AJ151" s="8"/>
       <c r="AK151" s="8"/>
@@ -14354,7 +14341,7 @@
         <v>491</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>85</v>
@@ -14396,7 +14383,7 @@
         <v>149</v>
       </c>
       <c r="Y152" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="Z152" s="5" t="s">
         <v>149</v>
@@ -14420,7 +14407,7 @@
       <c r="AO152" s="9"/>
       <c r="AP152" s="9"/>
     </row>
-    <row r="153" spans="1:42" ht="72.5">
+    <row r="153" spans="1:42" ht="58">
       <c r="A153" s="5" t="s">
         <v>644</v>
       </c>
@@ -14462,7 +14449,7 @@
         <v>213</v>
       </c>
       <c r="Q153" s="5" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="R153" s="5"/>
       <c r="S153" s="5"/>
@@ -14474,7 +14461,7 @@
         <v>213</v>
       </c>
       <c r="Y153" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="Z153" s="5" t="s">
         <v>213</v>
@@ -14498,13 +14485,13 @@
         <v>39</v>
       </c>
       <c r="AK153" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AL153" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM153" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AN153" s="9"/>
       <c r="AO153" s="9"/>
@@ -14754,7 +14741,7 @@
         <v>39</v>
       </c>
       <c r="Y157" s="5" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="Z157" s="5" t="s">
         <v>39</v>
@@ -14776,7 +14763,7 @@
         <v>39</v>
       </c>
       <c r="AM157" s="8" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AN157" s="9"/>
       <c r="AO157" s="9"/>
@@ -14828,7 +14815,7 @@
         <v>39</v>
       </c>
       <c r="Y158" s="5" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="Z158" s="5" t="s">
         <v>39</v>
@@ -14902,7 +14889,7 @@
         <v>39</v>
       </c>
       <c r="Y159" s="5" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="Z159" s="5" t="s">
         <v>39</v>
@@ -14922,13 +14909,13 @@
         <v>55</v>
       </c>
       <c r="AK159" s="8" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AL159" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM159" s="8" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AN159" s="9"/>
       <c r="AO159" s="9"/>
@@ -14984,7 +14971,7 @@
         <v>39</v>
       </c>
       <c r="Y160" s="5" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="Z160" s="5" t="s">
         <v>39</v>
@@ -15046,7 +15033,7 @@
         <v>39</v>
       </c>
       <c r="Y161" s="5" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="Z161" s="5" t="s">
         <v>39</v>
@@ -15067,8 +15054,8 @@
       <c r="AL161" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="AM161" s="19" t="s">
-        <v>712</v>
+      <c r="AM161" s="27" t="s">
+        <v>889</v>
       </c>
       <c r="AN161" s="9"/>
       <c r="AO161" s="9"/>
@@ -15082,7 +15069,7 @@
         <v>420</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>85</v>
@@ -15128,7 +15115,7 @@
         <v>149</v>
       </c>
       <c r="Y162" s="5" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="Z162" s="5"/>
       <c r="AA162" s="5"/>
@@ -15280,7 +15267,7 @@
         <v>39</v>
       </c>
       <c r="Y164" s="5" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
@@ -15514,7 +15501,7 @@
         <v>213</v>
       </c>
       <c r="Y168" s="5" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="Z168" s="5"/>
       <c r="AA168" s="5"/>
@@ -15974,7 +15961,7 @@
         <v>571</v>
       </c>
       <c r="Q174" s="5" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="R174" s="5"/>
       <c r="S174" s="5"/>
@@ -16040,7 +16027,7 @@
         <v>579</v>
       </c>
       <c r="Q175" s="5" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="R175" s="5"/>
       <c r="S175" s="5"/>
@@ -16062,19 +16049,19 @@
         <v>55</v>
       </c>
       <c r="AI175" s="8" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AJ175" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AK175" s="8" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="AL175" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM175" s="9" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AO175" s="9"/>
       <c r="AP175" s="9"/>
@@ -16178,7 +16165,7 @@
         <v>39</v>
       </c>
       <c r="Q177" s="5" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="R177" s="5"/>
       <c r="S177" s="5"/>
@@ -16200,19 +16187,19 @@
         <v>39</v>
       </c>
       <c r="AI177" s="8" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="AJ177" s="8" t="s">
         <v>180</v>
       </c>
       <c r="AK177" s="8" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="AL177" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM177" s="9" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="AO177" s="9"/>
       <c r="AP177" s="9"/>
@@ -16381,7 +16368,7 @@
         <v>55</v>
       </c>
       <c r="AI180" s="8" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AJ180" s="8"/>
       <c r="AK180" s="8"/>
@@ -16399,7 +16386,7 @@
         <v>349</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>85</v>
@@ -16426,10 +16413,10 @@
       <c r="N181" s="5"/>
       <c r="O181" s="5"/>
       <c r="P181" s="5" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="Q181" s="5" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="R181" s="5"/>
       <c r="S181" s="5"/>
@@ -16465,7 +16452,7 @@
         <v>358</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>38</v>
@@ -16500,16 +16487,16 @@
         <v>364</v>
       </c>
       <c r="P182" s="5" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="Q182" s="5" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="R182" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S182" s="5" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="T182" s="5"/>
       <c r="U182" s="5"/>
@@ -16519,7 +16506,7 @@
         <v>579</v>
       </c>
       <c r="Y182" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="Z182" s="5" t="s">
         <v>372</v>
@@ -16543,7 +16530,7 @@
         <v>55</v>
       </c>
       <c r="AK182" s="8" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="AL182" s="8"/>
       <c r="AM182" s="8"/>
@@ -16559,7 +16546,7 @@
         <v>375</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>38</v>
@@ -16594,10 +16581,10 @@
         <v>380</v>
       </c>
       <c r="P183" s="5" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="Q183" s="5" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="R183" s="5" t="s">
         <v>39</v>
@@ -16613,7 +16600,7 @@
         <v>180</v>
       </c>
       <c r="Y183" s="5" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="Z183" s="5" t="s">
         <v>379</v>
@@ -16637,7 +16624,7 @@
         <v>39</v>
       </c>
       <c r="AK183" s="8" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="AL183" s="8"/>
       <c r="AM183" s="8"/>
@@ -16775,7 +16762,7 @@
         <v>397</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>38</v>
@@ -16837,7 +16824,7 @@
         <v>391</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>38</v>
@@ -16929,13 +16916,13 @@
         <v>579</v>
       </c>
       <c r="Q188" s="5" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="R188" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S188" s="5" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="T188" s="5"/>
       <c r="U188" s="5"/>
@@ -16957,7 +16944,7 @@
         <v>55</v>
       </c>
       <c r="AK188" s="8" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="AL188" s="8"/>
       <c r="AM188" s="8"/>
@@ -16973,7 +16960,7 @@
         <v>415</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>85</v>
@@ -17003,7 +16990,7 @@
         <v>352</v>
       </c>
       <c r="Q189" s="5" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="R189" s="5"/>
       <c r="S189" s="5"/>
@@ -17039,7 +17026,7 @@
         <v>417</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>38</v>
@@ -17053,23 +17040,23 @@
         <v>59</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="J190" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K190" s="5" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="L190" s="5"/>
       <c r="M190" s="5"/>
       <c r="N190" s="5"/>
       <c r="O190" s="5"/>
       <c r="P190" s="5" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="Q190" s="5" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="R190" s="5"/>
       <c r="S190" s="5"/>
@@ -17091,15 +17078,15 @@
         <v>55</v>
       </c>
       <c r="AI190" s="8" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="AJ190" s="8"/>
       <c r="AK190" s="8"/>
-      <c r="AL190" s="19" t="s">
+      <c r="AL190" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="AM190" s="19" t="s">
-        <v>748</v>
+      <c r="AM190" s="27" t="s">
+        <v>745</v>
       </c>
       <c r="AN190" s="9"/>
       <c r="AO190" s="9"/>
@@ -17113,7 +17100,7 @@
         <v>418</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>38</v>
@@ -17127,13 +17114,13 @@
         <v>59</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K191" s="5" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="L191" s="5"/>
       <c r="M191" s="5"/>
@@ -17143,7 +17130,7 @@
         <v>39</v>
       </c>
       <c r="Q191" s="5" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="R191" s="5"/>
       <c r="S191" s="5"/>
@@ -17165,13 +17152,15 @@
         <v>39</v>
       </c>
       <c r="AI191" s="8" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="AJ191" s="8"/>
       <c r="AK191" s="8"/>
-      <c r="AL191" s="19"/>
-      <c r="AM191" s="19" t="s">
-        <v>753</v>
+      <c r="AL191" s="26" t="s">
+        <v>887</v>
+      </c>
+      <c r="AM191" s="26" t="s">
+        <v>888</v>
       </c>
       <c r="AN191" s="9"/>
       <c r="AO191" s="9"/>
@@ -17185,7 +17174,7 @@
         <v>419</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>38</v>
@@ -17236,16 +17225,16 @@
         <v>644</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>85</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F193" s="5"/>
       <c r="G193" s="5"/>
@@ -17269,7 +17258,7 @@
         <v>149</v>
       </c>
       <c r="Q193" s="5" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="R193" s="5"/>
       <c r="S193" s="5"/>
@@ -17302,16 +17291,16 @@
         <v>644</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="5"/>
@@ -17319,13 +17308,13 @@
         <v>59</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K194" s="5" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="L194" s="5"/>
       <c r="M194" s="5"/>
@@ -17335,7 +17324,7 @@
         <v>55</v>
       </c>
       <c r="Q194" s="5" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="R194" s="5" t="s">
         <v>39</v>
@@ -17374,16 +17363,16 @@
         <v>644</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>140</v>
@@ -17395,13 +17384,13 @@
         <v>59</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K195" s="5" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="L195" s="5"/>
       <c r="M195" s="5"/>
@@ -17431,7 +17420,7 @@
         <v>39</v>
       </c>
       <c r="AI195" s="8" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="AJ195" s="8"/>
       <c r="AK195" s="8"/>
@@ -17439,7 +17428,7 @@
         <v>39</v>
       </c>
       <c r="AM195" s="8" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="AN195" s="9"/>
       <c r="AO195" s="9"/>
@@ -17450,16 +17439,16 @@
         <v>644</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F196" s="5"/>
       <c r="G196" s="5"/>
@@ -17477,7 +17466,7 @@
         <v>55</v>
       </c>
       <c r="S196" s="5" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="T196" s="5"/>
       <c r="U196" s="5"/>
@@ -17511,7 +17500,7 @@
         <v>599</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>85</v>
@@ -17629,19 +17618,19 @@
         <v>55</v>
       </c>
       <c r="AI198" s="8" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="AJ198" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AK198" s="8" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="AL198" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM198" s="8" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="AN198" s="9"/>
       <c r="AO198" s="9"/>
@@ -17707,19 +17696,19 @@
         <v>39</v>
       </c>
       <c r="AI199" s="8" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="AJ199" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AK199" s="8" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="AL199" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM199" s="8" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="AN199" s="9"/>
       <c r="AO199" s="9"/>
@@ -17775,13 +17764,13 @@
         <v>39</v>
       </c>
       <c r="AK200" s="8" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="AL200" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM200" s="8" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="AN200" s="9"/>
       <c r="AO200" s="9"/>
@@ -17795,7 +17784,7 @@
         <v>616</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>38</v>
@@ -17859,7 +17848,7 @@
         <v>39</v>
       </c>
       <c r="AM201" s="5" t="s">
-        <v>782</v>
+        <v>890</v>
       </c>
       <c r="AN201" s="9"/>
       <c r="AO201" s="9"/>
@@ -17927,13 +17916,13 @@
         <v>213</v>
       </c>
       <c r="AK202" s="8" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="AL202" s="25" t="s">
-        <v>888</v>
+        <v>213</v>
       </c>
       <c r="AM202" s="8" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="AN202" s="9"/>
       <c r="AO202" s="9"/>
@@ -17947,7 +17936,7 @@
         <v>568</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>85</v>
@@ -18266,10 +18255,10 @@
       <c r="AH207" s="8"/>
       <c r="AI207" s="8"/>
       <c r="AJ207" s="26" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="AK207" s="26" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="AL207" s="5"/>
       <c r="AM207" s="5"/>
@@ -18322,10 +18311,10 @@
       <c r="AH208" s="5"/>
       <c r="AI208" s="5"/>
       <c r="AJ208" s="26" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="AK208" s="26" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="AL208" s="5"/>
       <c r="AM208" s="5"/>
@@ -18381,7 +18370,7 @@
         <v>149</v>
       </c>
       <c r="AI209" s="8" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="AJ209" s="8"/>
       <c r="AK209" s="8"/>
@@ -18439,7 +18428,7 @@
         <v>39</v>
       </c>
       <c r="AI210" s="5" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="AJ210" s="5"/>
       <c r="AK210" s="5"/>
@@ -18509,7 +18498,7 @@
     </row>
     <row r="212" spans="1:42" ht="14.5">
       <c r="A212" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>36</v>
@@ -18551,7 +18540,7 @@
         <v>39</v>
       </c>
       <c r="U212" s="5" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="V212" s="5"/>
       <c r="W212" s="5"/>
@@ -18581,13 +18570,13 @@
     </row>
     <row r="213" spans="1:42" ht="14.5">
       <c r="A213" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>38</v>
@@ -18615,7 +18604,7 @@
         <v>55</v>
       </c>
       <c r="Q213" s="5" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="R213" s="5"/>
       <c r="S213" s="5"/>
@@ -18623,7 +18612,7 @@
         <v>55</v>
       </c>
       <c r="U213" s="5" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="V213" s="5"/>
       <c r="W213" s="5"/>
@@ -18635,7 +18624,7 @@
         <v>55</v>
       </c>
       <c r="AC213" s="7" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AD213" s="5"/>
       <c r="AE213" s="5"/>
@@ -18653,13 +18642,13 @@
     </row>
     <row r="214" spans="1:42" ht="14.5">
       <c r="A214" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>38</v>
@@ -18691,7 +18680,7 @@
         <v>39</v>
       </c>
       <c r="U214" s="5" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="V214" s="5"/>
       <c r="W214" s="5"/>
@@ -18721,7 +18710,7 @@
     </row>
     <row r="215" spans="1:42" ht="14.5">
       <c r="A215" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>76</v>
@@ -18781,7 +18770,7 @@
     </row>
     <row r="216" spans="1:42" ht="14.5">
       <c r="A216" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>83</v>
@@ -18835,7 +18824,7 @@
     </row>
     <row r="217" spans="1:42" ht="29">
       <c r="A217" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>87</v>
@@ -18909,7 +18898,7 @@
     </row>
     <row r="218" spans="1:42" ht="29">
       <c r="A218" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>90</v>
@@ -18999,7 +18988,7 @@
     </row>
     <row r="219" spans="1:42" ht="14.5">
       <c r="A219" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>97</v>
@@ -19043,7 +19032,7 @@
         <v>55</v>
       </c>
       <c r="U219" s="5" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="V219" s="5"/>
       <c r="W219" s="5"/>
@@ -19081,7 +19070,7 @@
     </row>
     <row r="220" spans="1:42" ht="14.5">
       <c r="A220" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>111</v>
@@ -19155,7 +19144,7 @@
     </row>
     <row r="221" spans="1:42" ht="58">
       <c r="A221" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>122</v>
@@ -19199,7 +19188,7 @@
         <v>39</v>
       </c>
       <c r="U221" s="21" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="V221" s="5"/>
       <c r="W221" s="5"/>
@@ -19211,7 +19200,7 @@
         <v>55</v>
       </c>
       <c r="AC221" s="13" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AD221" s="5"/>
       <c r="AE221" s="5"/>
@@ -19229,7 +19218,7 @@
     </row>
     <row r="222" spans="1:42" ht="14.5">
       <c r="A222" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>136</v>
@@ -19273,7 +19262,7 @@
         <v>39</v>
       </c>
       <c r="U222" s="5" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="V222" s="5"/>
       <c r="W222" s="5"/>
@@ -19303,7 +19292,7 @@
     </row>
     <row r="223" spans="1:42" ht="14.5">
       <c r="A223" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>138</v>
@@ -19369,13 +19358,13 @@
     </row>
     <row r="224" spans="1:42" ht="29">
       <c r="A224" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>146</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>85</v>
@@ -19435,13 +19424,13 @@
     </row>
     <row r="225" spans="1:42" ht="43.5">
       <c r="A225" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>156</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>38</v>
@@ -19509,13 +19498,13 @@
     </row>
     <row r="226" spans="1:42" ht="58">
       <c r="A226" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>167</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>38</v>
@@ -19553,7 +19542,7 @@
         <v>39</v>
       </c>
       <c r="U226" s="5" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="V226" s="5"/>
       <c r="W226" s="5"/>
@@ -19565,7 +19554,7 @@
         <v>39</v>
       </c>
       <c r="AC226" s="7" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="AD226" s="5"/>
       <c r="AE226" s="5"/>
@@ -19583,7 +19572,7 @@
     </row>
     <row r="227" spans="1:42" ht="14.5">
       <c r="A227" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>200</v>
@@ -19635,7 +19624,7 @@
     </row>
     <row r="228" spans="1:42" ht="14.5">
       <c r="A228" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>201</v>
@@ -19687,7 +19676,7 @@
     </row>
     <row r="229" spans="1:42" ht="14.5">
       <c r="A229" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>202</v>
@@ -19739,7 +19728,7 @@
     </row>
     <row r="230" spans="1:42" ht="14.5">
       <c r="A230" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>203</v>
@@ -19793,7 +19782,7 @@
     </row>
     <row r="231" spans="1:42" ht="14.5">
       <c r="A231" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>209</v>
@@ -19849,7 +19838,7 @@
     </row>
     <row r="232" spans="1:42" ht="14.5">
       <c r="A232" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>211</v>
@@ -19869,7 +19858,7 @@
         <v>59</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="J232" s="5"/>
       <c r="K232" s="5"/>
@@ -19907,13 +19896,13 @@
     </row>
     <row r="233" spans="1:42" ht="14.5">
       <c r="A233" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>420</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>85</v>
@@ -19973,7 +19962,7 @@
     </row>
     <row r="234" spans="1:42" ht="43.5">
       <c r="A234" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>425</v>
@@ -20043,7 +20032,7 @@
     </row>
     <row r="235" spans="1:42" ht="43.5">
       <c r="A235" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>430</v>
@@ -20113,7 +20102,7 @@
     </row>
     <row r="236" spans="1:42" ht="14.5">
       <c r="A236" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>437</v>
@@ -20165,7 +20154,7 @@
     </row>
     <row r="237" spans="1:42" ht="14.5">
       <c r="A237" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>438</v>
@@ -20217,7 +20206,7 @@
     </row>
     <row r="238" spans="1:42" ht="14.5">
       <c r="A238" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>439</v>
@@ -20269,7 +20258,7 @@
     </row>
     <row r="239" spans="1:42" ht="43.5">
       <c r="A239" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>440</v>
@@ -20293,7 +20282,7 @@
         <v>59</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="J239" s="5"/>
       <c r="K239" s="5"/>
@@ -20335,13 +20324,13 @@
     </row>
     <row r="240" spans="1:42" ht="29">
       <c r="A240" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>349</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>85</v>
@@ -20364,10 +20353,10 @@
       <c r="N240" s="5"/>
       <c r="O240" s="5"/>
       <c r="P240" s="5" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="Q240" s="5" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="R240" s="5"/>
       <c r="S240" s="5"/>
@@ -20397,13 +20386,13 @@
     </row>
     <row r="241" spans="1:42" ht="188.5">
       <c r="A241" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>358</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>38</v>
@@ -20415,7 +20404,7 @@
         <v>372</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>361</v>
@@ -20430,10 +20419,10 @@
       <c r="N241" s="5"/>
       <c r="O241" s="5"/>
       <c r="P241" s="5" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="Q241" s="5" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="R241" s="5"/>
       <c r="S241" s="5"/>
@@ -20441,7 +20430,7 @@
         <v>55</v>
       </c>
       <c r="U241" s="5" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="V241" s="5"/>
       <c r="W241" s="5"/>
@@ -20453,7 +20442,7 @@
         <v>93</v>
       </c>
       <c r="AC241" s="7" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AD241" s="5"/>
       <c r="AE241" s="5"/>
@@ -20471,13 +20460,13 @@
     </row>
     <row r="242" spans="1:42" ht="145">
       <c r="A242" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>375</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>38</v>
@@ -20489,13 +20478,13 @@
         <v>379</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>377</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="J242" s="5"/>
       <c r="K242" s="5"/>
@@ -20504,10 +20493,10 @@
       <c r="N242" s="5"/>
       <c r="O242" s="5"/>
       <c r="P242" s="5" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="Q242" s="5" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="R242" s="5"/>
       <c r="S242" s="5"/>
@@ -20515,7 +20504,7 @@
         <v>39</v>
       </c>
       <c r="U242" s="5" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="V242" s="5"/>
       <c r="W242" s="5"/>
@@ -20527,7 +20516,7 @@
         <v>180</v>
       </c>
       <c r="AC242" s="7" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="AD242" s="5"/>
       <c r="AE242" s="5"/>
@@ -20545,7 +20534,7 @@
     </row>
     <row r="243" spans="1:42" ht="29">
       <c r="A243" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>390</v>
@@ -20597,13 +20586,13 @@
     </row>
     <row r="244" spans="1:42" ht="14.5">
       <c r="A244" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>38</v>
@@ -20655,13 +20644,13 @@
     </row>
     <row r="245" spans="1:42" ht="14.5">
       <c r="A245" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>391</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>38</v>
@@ -20713,13 +20702,13 @@
     </row>
     <row r="246" spans="1:42" ht="14.5">
       <c r="A246" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>401</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>38</v>
@@ -20771,7 +20760,7 @@
     </row>
     <row r="247" spans="1:42" ht="174">
       <c r="A247" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>406</v>
@@ -20800,10 +20789,10 @@
       <c r="N247" s="5"/>
       <c r="O247" s="5"/>
       <c r="P247" s="5" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="Q247" s="5" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="R247" s="5"/>
       <c r="S247" s="5"/>
@@ -20833,7 +20822,7 @@
     </row>
     <row r="248" spans="1:42" ht="14.5">
       <c r="A248" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>258</v>
@@ -20867,7 +20856,7 @@
         <v>149</v>
       </c>
       <c r="Q248" s="5" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="R248" s="5"/>
       <c r="S248" s="5"/>
@@ -20897,7 +20886,7 @@
     </row>
     <row r="249" spans="1:42" ht="29">
       <c r="A249" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>264</v>
@@ -20917,7 +20906,7 @@
         <v>59</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="J249" s="5"/>
       <c r="K249" s="5"/>
@@ -20929,7 +20918,7 @@
         <v>39</v>
       </c>
       <c r="Q249" s="5" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="R249" s="5"/>
       <c r="S249" s="5"/>
@@ -20959,7 +20948,7 @@
     </row>
     <row r="250" spans="1:42" ht="14.5">
       <c r="A250" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>276</v>
@@ -21013,7 +21002,7 @@
     </row>
     <row r="251" spans="1:42" ht="14.5">
       <c r="A251" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>278</v>
@@ -21067,7 +21056,7 @@
     </row>
     <row r="252" spans="1:42" ht="14.5">
       <c r="A252" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>280</v>
@@ -21121,7 +21110,7 @@
     </row>
     <row r="253" spans="1:42" ht="14.5">
       <c r="A253" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>282</v>
@@ -21141,7 +21130,7 @@
         <v>59</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J253" s="5"/>
       <c r="K253" s="5"/>
@@ -21179,7 +21168,7 @@
     </row>
     <row r="254" spans="1:42" ht="29">
       <c r="A254" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>285</v>
@@ -21199,7 +21188,7 @@
         <v>59</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="J254" s="5"/>
       <c r="K254" s="5"/>
@@ -21211,7 +21200,7 @@
         <v>55</v>
       </c>
       <c r="Q254" s="5" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="R254" s="5"/>
       <c r="S254" s="5"/>
@@ -21241,7 +21230,7 @@
     </row>
     <row r="255" spans="1:42" ht="14.5">
       <c r="A255" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>293</v>
@@ -21295,7 +21284,7 @@
     </row>
     <row r="256" spans="1:42" ht="14.5">
       <c r="A256" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>286</v>
@@ -21349,13 +21338,13 @@
     </row>
     <row r="257" spans="1:42" ht="29">
       <c r="A257" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>323</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>85</v>
@@ -21377,7 +21366,7 @@
         <v>149</v>
       </c>
       <c r="Q257" s="5" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="R257" s="5"/>
       <c r="S257" s="5"/>
@@ -21407,13 +21396,13 @@
     </row>
     <row r="258" spans="1:42" ht="14.5">
       <c r="A258" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>329</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>38</v>
@@ -21435,7 +21424,7 @@
         <v>55</v>
       </c>
       <c r="Q258" s="5" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="R258" s="5"/>
       <c r="S258" s="5"/>
@@ -21465,7 +21454,7 @@
     </row>
     <row r="259" spans="1:42" ht="14.5">
       <c r="A259" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>335</v>
@@ -21519,7 +21508,7 @@
     </row>
     <row r="260" spans="1:42" ht="29">
       <c r="A260" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>337</v>
@@ -21547,7 +21536,7 @@
         <v>39</v>
       </c>
       <c r="Q260" s="5" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="R260" s="5"/>
       <c r="S260" s="5"/>
@@ -21577,7 +21566,7 @@
     </row>
     <row r="261" spans="1:42" ht="14.5">
       <c r="A261" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>345</v>
@@ -21631,13 +21620,13 @@
     </row>
     <row r="262" spans="1:42" ht="14.5">
       <c r="A262" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>491</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="D262" s="5" t="s">
         <v>85</v>
@@ -21689,7 +21678,7 @@
     </row>
     <row r="263" spans="1:42" ht="14.5">
       <c r="A263" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>498</v>
@@ -21751,7 +21740,7 @@
     </row>
     <row r="264" spans="1:42" ht="29">
       <c r="A264" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>507</v>
@@ -21809,7 +21798,7 @@
     </row>
     <row r="265" spans="1:42" ht="29">
       <c r="A265" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>511</v>
@@ -21867,7 +21856,7 @@
     </row>
     <row r="266" spans="1:42" ht="29">
       <c r="A266" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>515</v>
@@ -21925,7 +21914,7 @@
     </row>
     <row r="267" spans="1:42" ht="29">
       <c r="A267" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>519</v>
@@ -21983,7 +21972,7 @@
     </row>
     <row r="268" spans="1:42" ht="29">
       <c r="A268" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>530</v>
@@ -22041,7 +22030,7 @@
     </row>
     <row r="269" spans="1:42" ht="14.5">
       <c r="A269" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>524</v>
@@ -22099,7 +22088,7 @@
     </row>
     <row r="270" spans="1:42" ht="29">
       <c r="A270" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>535</v>
@@ -22157,7 +22146,7 @@
     </row>
     <row r="271" spans="1:42" ht="14.5">
       <c r="A271" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>541</v>
@@ -22211,19 +22200,19 @@
     </row>
     <row r="272" spans="1:42" ht="14.5">
       <c r="A272" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="D272" s="5" t="s">
         <v>85</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F272" s="5"/>
       <c r="G272" s="5"/>
@@ -22243,7 +22232,7 @@
         <v>149</v>
       </c>
       <c r="Q272" s="5" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="R272" s="5"/>
       <c r="S272" s="5"/>
@@ -22273,19 +22262,19 @@
     </row>
     <row r="273" spans="1:42" ht="14.5">
       <c r="A273" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5"/>
@@ -22293,7 +22282,7 @@
         <v>59</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="J273" s="5"/>
       <c r="K273" s="5"/>
@@ -22305,7 +22294,7 @@
         <v>39</v>
       </c>
       <c r="Q273" s="5" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="R273" s="5"/>
       <c r="S273" s="5"/>
@@ -22335,19 +22324,19 @@
     </row>
     <row r="274" spans="1:42" ht="14.5">
       <c r="A274" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="D274" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F274" s="5"/>
       <c r="G274" s="5"/>
@@ -22355,7 +22344,7 @@
         <v>59</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="J274" s="5"/>
       <c r="K274" s="5"/>
@@ -22367,7 +22356,7 @@
         <v>39</v>
       </c>
       <c r="Q274" s="5" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="R274" s="5"/>
       <c r="S274" s="5"/>
@@ -22397,19 +22386,19 @@
     </row>
     <row r="275" spans="1:42" ht="14.5">
       <c r="A275" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D275" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F275" s="5"/>
       <c r="G275" s="5"/>
@@ -22417,7 +22406,7 @@
         <v>59</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="J275" s="5"/>
       <c r="K275" s="5"/>
@@ -22429,7 +22418,7 @@
         <v>39</v>
       </c>
       <c r="Q275" s="5" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="R275" s="5"/>
       <c r="S275" s="5"/>
@@ -22459,19 +22448,19 @@
     </row>
     <row r="276" spans="1:42" ht="29">
       <c r="A276" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="D276" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F276" s="5"/>
       <c r="G276" s="5"/>
@@ -22513,19 +22502,19 @@
     </row>
     <row r="277" spans="1:42" ht="14.5">
       <c r="A277" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F277" s="5"/>
       <c r="G277" s="5"/>
@@ -22533,7 +22522,7 @@
         <v>59</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="J277" s="5"/>
       <c r="K277" s="5"/>
@@ -22545,7 +22534,7 @@
         <v>39</v>
       </c>
       <c r="Q277" s="5" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="R277" s="5"/>
       <c r="S277" s="5"/>
@@ -22575,19 +22564,19 @@
     </row>
     <row r="278" spans="1:42" ht="14.5">
       <c r="A278" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D278" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F278" s="5"/>
       <c r="G278" s="5"/>
@@ -22603,7 +22592,7 @@
         <v>39</v>
       </c>
       <c r="Q278" s="5" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="R278" s="5"/>
       <c r="S278" s="5"/>
@@ -22633,17 +22622,17 @@
     </row>
     <row r="279" spans="1:42" ht="14.5">
       <c r="A279" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C279" s="5"/>
       <c r="D279" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F279" s="5"/>
       <c r="G279" s="5"/>
@@ -22651,7 +22640,7 @@
         <v>59</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="J279" s="5"/>
       <c r="K279" s="5"/>
@@ -22663,7 +22652,7 @@
         <v>39</v>
       </c>
       <c r="Q279" s="5" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="R279" s="5"/>
       <c r="S279" s="5"/>
@@ -22693,17 +22682,17 @@
     </row>
     <row r="280" spans="1:42" ht="14.5">
       <c r="A280" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C280" s="5"/>
       <c r="D280" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F280" s="5"/>
       <c r="G280" s="5"/>
@@ -22711,7 +22700,7 @@
         <v>59</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="J280" s="5"/>
       <c r="K280" s="5"/>
@@ -22749,31 +22738,31 @@
     </row>
     <row r="281" spans="1:42" ht="14.5">
       <c r="A281" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="D281" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>39</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="H281" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="J281" s="5"/>
       <c r="K281" s="5"/>
@@ -22811,19 +22800,19 @@
     </row>
     <row r="282" spans="1:42" ht="14.5">
       <c r="A282" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="D282" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F282" s="5" t="s">
         <v>39</v>
@@ -22869,17 +22858,17 @@
     </row>
     <row r="283" spans="1:42" ht="14.5">
       <c r="A283" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="C283" s="5"/>
       <c r="D283" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="F283" s="5"/>
       <c r="G283" s="5"/>
@@ -22897,7 +22886,7 @@
       <c r="O283" s="5"/>
       <c r="P283" s="5"/>
       <c r="Q283" s="5" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="R283" s="5"/>
       <c r="S283" s="5"/>
@@ -22927,17 +22916,17 @@
     </row>
     <row r="284" spans="1:42" ht="43.5">
       <c r="A284" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C284" s="5"/>
       <c r="D284" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="F284" s="5"/>
       <c r="G284" s="5"/>
@@ -22945,7 +22934,7 @@
         <v>59</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="J284" s="5"/>
       <c r="K284" s="5"/>
@@ -22957,7 +22946,7 @@
         <v>579</v>
       </c>
       <c r="Q284" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="R284" s="5"/>
       <c r="S284" s="5"/>
@@ -22987,17 +22976,17 @@
     </row>
     <row r="285" spans="1:42" ht="43.5">
       <c r="A285" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="C285" s="5"/>
       <c r="D285" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="F285" s="5"/>
       <c r="G285" s="5"/>
@@ -23005,7 +22994,7 @@
         <v>59</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="J285" s="5"/>
       <c r="K285" s="5"/>
@@ -23017,7 +23006,7 @@
         <v>594</v>
       </c>
       <c r="Q285" s="5" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="R285" s="5"/>
       <c r="S285" s="5"/>
@@ -23047,7 +23036,7 @@
     </row>
     <row r="286" spans="1:42" ht="14.5">
       <c r="A286" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>445</v>
@@ -23109,7 +23098,7 @@
     </row>
     <row r="287" spans="1:42" ht="14.5">
       <c r="A287" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>450</v>
@@ -23179,7 +23168,7 @@
     </row>
     <row r="288" spans="1:42" ht="14.5">
       <c r="A288" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>453</v>
@@ -23249,7 +23238,7 @@
     </row>
     <row r="289" spans="1:42" ht="29">
       <c r="A289" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>463</v>
@@ -23319,7 +23308,7 @@
     </row>
     <row r="290" spans="1:42" ht="14.5">
       <c r="A290" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>472</v>
@@ -23389,13 +23378,13 @@
     </row>
     <row r="291" spans="1:42" ht="14.5">
       <c r="A291" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>599</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>85</v>
@@ -23447,7 +23436,7 @@
     </row>
     <row r="292" spans="1:42" ht="43.5">
       <c r="A292" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>603</v>
@@ -23491,7 +23480,7 @@
         <v>55</v>
       </c>
       <c r="U292" s="5" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="V292" s="5"/>
       <c r="W292" s="5"/>
@@ -23517,7 +23506,7 @@
     </row>
     <row r="293" spans="1:42" ht="14.5">
       <c r="A293" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>609</v>
@@ -23561,7 +23550,7 @@
         <v>39</v>
       </c>
       <c r="U293" s="5" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="V293" s="5"/>
       <c r="W293" s="5"/>
@@ -23587,7 +23576,7 @@
     </row>
     <row r="294" spans="1:42" ht="14.5">
       <c r="A294" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>614</v>
@@ -23641,13 +23630,13 @@
     </row>
     <row r="295" spans="1:42" ht="43.5">
       <c r="A295" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>616</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D295" s="5" t="s">
         <v>38</v>
@@ -23711,7 +23700,7 @@
     </row>
     <row r="296" spans="1:42" ht="29">
       <c r="A296" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>621</v>
@@ -23773,13 +23762,13 @@
     </row>
     <row r="297" spans="1:42" ht="43.5">
       <c r="A297" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>546</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="D297" s="5" t="s">
         <v>85</v>
@@ -23805,7 +23794,7 @@
         <v>571</v>
       </c>
       <c r="Q297" s="5" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="R297" s="5"/>
       <c r="S297" s="5"/>
@@ -23835,13 +23824,13 @@
     </row>
     <row r="298" spans="1:42" ht="14.5">
       <c r="A298" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>550</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="D298" s="5" t="s">
         <v>38</v>
@@ -23867,7 +23856,7 @@
         <v>579</v>
       </c>
       <c r="Q298" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="R298" s="5"/>
       <c r="S298" s="5"/>
@@ -23897,7 +23886,7 @@
     </row>
     <row r="299" spans="1:42" ht="29">
       <c r="A299" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>554</v>
@@ -23955,7 +23944,7 @@
     </row>
     <row r="300" spans="1:42" ht="43.5">
       <c r="A300" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>557</v>
@@ -23987,7 +23976,7 @@
         <v>594</v>
       </c>
       <c r="Q300" s="5" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="R300" s="5"/>
       <c r="S300" s="5"/>
@@ -24017,7 +24006,7 @@
     </row>
     <row r="301" spans="1:42" ht="14.5">
       <c r="A301" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>561</v>
@@ -24071,7 +24060,7 @@
     </row>
     <row r="302" spans="1:42" ht="14.5">
       <c r="A302" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>563</v>
@@ -24125,7 +24114,7 @@
     </row>
     <row r="303" spans="1:42" ht="14.5">
       <c r="A303" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>565</v>
@@ -24183,13 +24172,13 @@
     </row>
     <row r="304" spans="1:42" ht="29">
       <c r="A304" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>568</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="D304" s="5" t="s">
         <v>85</v>
@@ -24245,7 +24234,7 @@
     </row>
     <row r="305" spans="1:42" ht="87">
       <c r="A305" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>574</v>
@@ -24315,7 +24304,7 @@
     </row>
     <row r="306" spans="1:42" ht="87">
       <c r="A306" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>587</v>
@@ -24367,7 +24356,7 @@
         <v>39</v>
       </c>
       <c r="AC306" s="7" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="AD306" s="5"/>
       <c r="AE306" s="5"/>
@@ -24385,7 +24374,7 @@
     </row>
     <row r="307" spans="1:42" ht="14.5">
       <c r="A307" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>625</v>
@@ -24437,7 +24426,7 @@
     </row>
     <row r="308" spans="1:42" ht="14.5">
       <c r="A308" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>627</v>
@@ -24489,7 +24478,7 @@
     </row>
     <row r="309" spans="1:42" ht="14.5">
       <c r="A309" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>630</v>
@@ -24541,7 +24530,7 @@
     </row>
     <row r="310" spans="1:42" ht="14.5">
       <c r="A310" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>633</v>
@@ -24595,7 +24584,7 @@
     </row>
     <row r="311" spans="1:42" ht="14.5">
       <c r="A311" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>638</v>
@@ -24649,7 +24638,7 @@
     </row>
     <row r="312" spans="1:42" ht="14.5">
       <c r="A312" s="5" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>641</v>

--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F899D4-B510-48A0-830F-DDE2D11E34F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EB2F51-D770-4C24-AC80-8698E24D4AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3788" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3791" uniqueCount="892">
   <si>
     <t>Entity Category</t>
   </si>
@@ -2062,12 +2062,6 @@
   </si>
   <si>
     <t>"CFTC-RED-LIST"</t>
-  </si>
-  <si>
-    <t>"GPPB_BLACKLISTED_ENTITIES"</t>
-  </si>
-  <si>
-    <t>"DMW_RECRUITMENT_AGENCIES"</t>
   </si>
   <si>
     <t>"CFTC"</t>
@@ -2838,6 +2832,15 @@
   </si>
   <si>
     <t>is_valid</t>
+  </si>
+  <si>
+    <t>"GPPB-BLACKLISTED-ENTITIES"</t>
+  </si>
+  <si>
+    <t>"DMW-RECRUITMENT-AGENCIES"</t>
+  </si>
+  <si>
+    <t>"PEP (Politically Exposed Person)"</t>
   </si>
 </sst>
 </file>
@@ -3055,7 +3058,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3137,6 +3140,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3507,16 +3513,16 @@
         <v>34</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AN1" s="9"/>
       <c r="AO1" s="9"/>
@@ -4208,8 +4214,12 @@
       <c r="AE9" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="AF9" s="9"/>
-      <c r="AG9" s="9"/>
+      <c r="AF9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG9" s="28" t="s">
+        <v>891</v>
+      </c>
       <c r="AH9" s="8"/>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
@@ -4615,7 +4625,9 @@
       <c r="AF13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AG13" s="9"/>
+      <c r="AG13" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="8"/>
@@ -9634,7 +9646,7 @@
       <c r="AO85" s="9"/>
       <c r="AP85" s="9"/>
     </row>
-    <row r="86" spans="1:42" ht="58">
+    <row r="86" spans="1:42" ht="72.5">
       <c r="A86" s="5" t="s">
         <v>35</v>
       </c>
@@ -12068,7 +12080,7 @@
         <v>39</v>
       </c>
       <c r="AM120" s="9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AN120" s="9"/>
       <c r="AO120" s="9"/>
@@ -12430,13 +12442,13 @@
         <v>55</v>
       </c>
       <c r="AK124" s="8" t="s">
-        <v>654</v>
+        <v>889</v>
       </c>
       <c r="AL124" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM124" s="8" t="s">
-        <v>655</v>
+        <v>890</v>
       </c>
       <c r="AN124" s="9"/>
       <c r="AO124" s="9"/>
@@ -12526,19 +12538,19 @@
         <v>55</v>
       </c>
       <c r="AI125" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AJ125" s="9" t="s">
         <v>55</v>
       </c>
       <c r="AK125" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AL125" s="9" t="s">
         <v>55</v>
       </c>
       <c r="AM125" s="9" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AN125" s="9"/>
       <c r="AO125" s="9"/>
@@ -12570,7 +12582,7 @@
         <v>55</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>55</v>
@@ -12584,19 +12596,19 @@
         <v>55</v>
       </c>
       <c r="O126" s="11" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="P126" s="5" t="s">
         <v>55</v>
       </c>
       <c r="Q126" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="R126" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S126" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="T126" s="5"/>
       <c r="U126" s="5"/>
@@ -12606,19 +12618,19 @@
         <v>55</v>
       </c>
       <c r="Y126" s="11" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="Z126" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AA126" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AB126" s="5" t="s">
         <v>55</v>
       </c>
       <c r="AC126" s="13" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="AD126" s="5"/>
       <c r="AE126" s="5"/>
@@ -12634,13 +12646,13 @@
         <v>55</v>
       </c>
       <c r="AK126" s="18" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AL126" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM126" s="8" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AN126" s="9"/>
       <c r="AO126" s="9"/>
@@ -12794,7 +12806,7 @@
         <v>39</v>
       </c>
       <c r="S128" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="T128" s="5"/>
       <c r="U128" s="5"/>
@@ -12822,7 +12834,7 @@
         <v>55</v>
       </c>
       <c r="AI128" s="8" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AJ128" s="8"/>
       <c r="AK128" s="8"/>
@@ -12840,7 +12852,7 @@
         <v>146</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>85</v>
@@ -12918,7 +12930,7 @@
         <v>156</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>38</v>
@@ -13016,7 +13028,7 @@
         <v>167</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>38</v>
@@ -13048,7 +13060,7 @@
         <v>39</v>
       </c>
       <c r="O131" s="5" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="P131" s="5" t="s">
         <v>173</v>
@@ -13070,7 +13082,7 @@
         <v>177</v>
       </c>
       <c r="Y131" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="Z131" s="5" t="s">
         <v>39</v>
@@ -13092,19 +13104,19 @@
         <v>39</v>
       </c>
       <c r="AI131" s="8" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AJ131" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AK131" s="8" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AL131" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM131" s="8" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="AN131" s="9"/>
       <c r="AO131" s="9"/>
@@ -13408,7 +13420,7 @@
         <v>39</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>213</v>
@@ -13546,13 +13558,13 @@
         <v>59</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J139" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K139" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
@@ -13592,7 +13604,7 @@
         <v>39</v>
       </c>
       <c r="AI139" s="8" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AJ139" s="8"/>
       <c r="AK139" s="8"/>
@@ -13780,13 +13792,13 @@
         <v>59</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J143" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
@@ -13841,13 +13853,13 @@
         <v>59</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="J144" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K144" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
@@ -13857,7 +13869,7 @@
         <v>55</v>
       </c>
       <c r="Q144" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="R144" s="5" t="s">
         <v>55</v>
@@ -13877,7 +13889,7 @@
         <v>55</v>
       </c>
       <c r="AC144" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AD144" s="5"/>
       <c r="AE144" s="5"/>
@@ -13887,7 +13899,7 @@
         <v>55</v>
       </c>
       <c r="AI144" s="8" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AJ144" s="5"/>
       <c r="AK144" s="5"/>
@@ -13918,13 +13930,13 @@
         <v>59</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J145" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
@@ -13952,7 +13964,7 @@
         <v>55</v>
       </c>
       <c r="AI145" s="8" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="AJ145" s="5"/>
       <c r="AK145" s="5"/>
@@ -14023,7 +14035,7 @@
         <v>323</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>85</v>
@@ -14085,7 +14097,7 @@
         <v>329</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>38</v>
@@ -14099,13 +14111,13 @@
         <v>59</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K148" s="5" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
@@ -14125,7 +14137,7 @@
         <v>55</v>
       </c>
       <c r="AA148" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AB148" s="5"/>
       <c r="AC148" s="5"/>
@@ -14137,7 +14149,7 @@
         <v>55</v>
       </c>
       <c r="AI148" s="8" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AJ148" s="5"/>
       <c r="AK148" s="5"/>
@@ -14227,13 +14239,13 @@
         <v>59</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K150" s="5" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
@@ -14261,7 +14273,7 @@
         <v>238</v>
       </c>
       <c r="AI150" s="19" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="AJ150" s="5"/>
       <c r="AK150" s="5"/>
@@ -14323,7 +14335,7 @@
         <v>39</v>
       </c>
       <c r="AI151" s="8" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="AJ151" s="8"/>
       <c r="AK151" s="8"/>
@@ -14341,7 +14353,7 @@
         <v>491</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>85</v>
@@ -14383,7 +14395,7 @@
         <v>149</v>
       </c>
       <c r="Y152" s="5" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="Z152" s="5" t="s">
         <v>149</v>
@@ -14407,7 +14419,7 @@
       <c r="AO152" s="9"/>
       <c r="AP152" s="9"/>
     </row>
-    <row r="153" spans="1:42" ht="58">
+    <row r="153" spans="1:42" ht="72.5">
       <c r="A153" s="5" t="s">
         <v>644</v>
       </c>
@@ -14449,7 +14461,7 @@
         <v>213</v>
       </c>
       <c r="Q153" s="5" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="R153" s="5"/>
       <c r="S153" s="5"/>
@@ -14461,7 +14473,7 @@
         <v>213</v>
       </c>
       <c r="Y153" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="Z153" s="5" t="s">
         <v>213</v>
@@ -14485,13 +14497,13 @@
         <v>39</v>
       </c>
       <c r="AK153" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AL153" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM153" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AN153" s="9"/>
       <c r="AO153" s="9"/>
@@ -14741,7 +14753,7 @@
         <v>39</v>
       </c>
       <c r="Y157" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="Z157" s="5" t="s">
         <v>39</v>
@@ -14763,7 +14775,7 @@
         <v>39</v>
       </c>
       <c r="AM157" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AN157" s="9"/>
       <c r="AO157" s="9"/>
@@ -14815,7 +14827,7 @@
         <v>39</v>
       </c>
       <c r="Y158" s="5" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="Z158" s="5" t="s">
         <v>39</v>
@@ -14889,7 +14901,7 @@
         <v>39</v>
       </c>
       <c r="Y159" s="5" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="Z159" s="5" t="s">
         <v>39</v>
@@ -14909,13 +14921,13 @@
         <v>55</v>
       </c>
       <c r="AK159" s="8" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AL159" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM159" s="8" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AN159" s="9"/>
       <c r="AO159" s="9"/>
@@ -14971,7 +14983,7 @@
         <v>39</v>
       </c>
       <c r="Y160" s="5" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="Z160" s="5" t="s">
         <v>39</v>
@@ -15033,7 +15045,7 @@
         <v>39</v>
       </c>
       <c r="Y161" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="Z161" s="5" t="s">
         <v>39</v>
@@ -15055,7 +15067,7 @@
         <v>213</v>
       </c>
       <c r="AM161" s="27" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AN161" s="9"/>
       <c r="AO161" s="9"/>
@@ -15069,7 +15081,7 @@
         <v>420</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>85</v>
@@ -15115,7 +15127,7 @@
         <v>149</v>
       </c>
       <c r="Y162" s="5" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="Z162" s="5"/>
       <c r="AA162" s="5"/>
@@ -15267,7 +15279,7 @@
         <v>39</v>
       </c>
       <c r="Y164" s="5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
@@ -15501,7 +15513,7 @@
         <v>213</v>
       </c>
       <c r="Y168" s="5" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="Z168" s="5"/>
       <c r="AA168" s="5"/>
@@ -15961,7 +15973,7 @@
         <v>571</v>
       </c>
       <c r="Q174" s="5" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="R174" s="5"/>
       <c r="S174" s="5"/>
@@ -16027,7 +16039,7 @@
         <v>579</v>
       </c>
       <c r="Q175" s="5" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="R175" s="5"/>
       <c r="S175" s="5"/>
@@ -16049,19 +16061,19 @@
         <v>55</v>
       </c>
       <c r="AI175" s="8" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AJ175" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AK175" s="8" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="AL175" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM175" s="9" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="AO175" s="9"/>
       <c r="AP175" s="9"/>
@@ -16165,7 +16177,7 @@
         <v>39</v>
       </c>
       <c r="Q177" s="5" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="R177" s="5"/>
       <c r="S177" s="5"/>
@@ -16187,19 +16199,19 @@
         <v>39</v>
       </c>
       <c r="AI177" s="8" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AJ177" s="8" t="s">
         <v>180</v>
       </c>
       <c r="AK177" s="8" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AL177" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM177" s="9" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AO177" s="9"/>
       <c r="AP177" s="9"/>
@@ -16368,7 +16380,7 @@
         <v>55</v>
       </c>
       <c r="AI180" s="8" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AJ180" s="8"/>
       <c r="AK180" s="8"/>
@@ -16386,7 +16398,7 @@
         <v>349</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>85</v>
@@ -16413,10 +16425,10 @@
       <c r="N181" s="5"/>
       <c r="O181" s="5"/>
       <c r="P181" s="5" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="Q181" s="5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="R181" s="5"/>
       <c r="S181" s="5"/>
@@ -16452,7 +16464,7 @@
         <v>358</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>38</v>
@@ -16487,16 +16499,16 @@
         <v>364</v>
       </c>
       <c r="P182" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Q182" s="5" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="R182" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S182" s="5" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="T182" s="5"/>
       <c r="U182" s="5"/>
@@ -16506,7 +16518,7 @@
         <v>579</v>
       </c>
       <c r="Y182" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="Z182" s="5" t="s">
         <v>372</v>
@@ -16530,7 +16542,7 @@
         <v>55</v>
       </c>
       <c r="AK182" s="8" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="AL182" s="8"/>
       <c r="AM182" s="8"/>
@@ -16546,7 +16558,7 @@
         <v>375</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>38</v>
@@ -16581,10 +16593,10 @@
         <v>380</v>
       </c>
       <c r="P183" s="5" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="Q183" s="5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="R183" s="5" t="s">
         <v>39</v>
@@ -16600,7 +16612,7 @@
         <v>180</v>
       </c>
       <c r="Y183" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="Z183" s="5" t="s">
         <v>379</v>
@@ -16624,7 +16636,7 @@
         <v>39</v>
       </c>
       <c r="AK183" s="8" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AL183" s="8"/>
       <c r="AM183" s="8"/>
@@ -16762,7 +16774,7 @@
         <v>397</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>38</v>
@@ -16824,7 +16836,7 @@
         <v>391</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>38</v>
@@ -16916,13 +16928,13 @@
         <v>579</v>
       </c>
       <c r="Q188" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="R188" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S188" s="5" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="T188" s="5"/>
       <c r="U188" s="5"/>
@@ -16944,7 +16956,7 @@
         <v>55</v>
       </c>
       <c r="AK188" s="8" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="AL188" s="8"/>
       <c r="AM188" s="8"/>
@@ -16960,7 +16972,7 @@
         <v>415</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>85</v>
@@ -16990,7 +17002,7 @@
         <v>352</v>
       </c>
       <c r="Q189" s="5" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="R189" s="5"/>
       <c r="S189" s="5"/>
@@ -17026,7 +17038,7 @@
         <v>417</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>38</v>
@@ -17040,23 +17052,23 @@
         <v>59</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="J190" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K190" s="5" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="L190" s="5"/>
       <c r="M190" s="5"/>
       <c r="N190" s="5"/>
       <c r="O190" s="5"/>
       <c r="P190" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Q190" s="5" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="R190" s="5"/>
       <c r="S190" s="5"/>
@@ -17078,7 +17090,7 @@
         <v>55</v>
       </c>
       <c r="AI190" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="AJ190" s="8"/>
       <c r="AK190" s="8"/>
@@ -17086,7 +17098,7 @@
         <v>93</v>
       </c>
       <c r="AM190" s="27" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="AN190" s="9"/>
       <c r="AO190" s="9"/>
@@ -17100,7 +17112,7 @@
         <v>418</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>38</v>
@@ -17114,13 +17126,13 @@
         <v>59</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K191" s="5" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="L191" s="5"/>
       <c r="M191" s="5"/>
@@ -17130,7 +17142,7 @@
         <v>39</v>
       </c>
       <c r="Q191" s="5" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="R191" s="5"/>
       <c r="S191" s="5"/>
@@ -17152,15 +17164,15 @@
         <v>39</v>
       </c>
       <c r="AI191" s="8" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="AJ191" s="8"/>
       <c r="AK191" s="8"/>
       <c r="AL191" s="26" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="AM191" s="26" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AN191" s="9"/>
       <c r="AO191" s="9"/>
@@ -17174,7 +17186,7 @@
         <v>419</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>38</v>
@@ -17225,16 +17237,16 @@
         <v>644</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>85</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F193" s="5"/>
       <c r="G193" s="5"/>
@@ -17258,7 +17270,7 @@
         <v>149</v>
       </c>
       <c r="Q193" s="5" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="R193" s="5"/>
       <c r="S193" s="5"/>
@@ -17291,16 +17303,16 @@
         <v>644</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="5"/>
@@ -17308,13 +17320,13 @@
         <v>59</v>
       </c>
       <c r="I194" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K194" s="5" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="L194" s="5"/>
       <c r="M194" s="5"/>
@@ -17324,7 +17336,7 @@
         <v>55</v>
       </c>
       <c r="Q194" s="5" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="R194" s="5" t="s">
         <v>39</v>
@@ -17363,16 +17375,16 @@
         <v>644</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>140</v>
@@ -17384,13 +17396,13 @@
         <v>59</v>
       </c>
       <c r="I195" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>59</v>
       </c>
       <c r="K195" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L195" s="5"/>
       <c r="M195" s="5"/>
@@ -17420,7 +17432,7 @@
         <v>39</v>
       </c>
       <c r="AI195" s="8" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="AJ195" s="8"/>
       <c r="AK195" s="8"/>
@@ -17428,7 +17440,7 @@
         <v>39</v>
       </c>
       <c r="AM195" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="AN195" s="9"/>
       <c r="AO195" s="9"/>
@@ -17439,16 +17451,16 @@
         <v>644</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F196" s="5"/>
       <c r="G196" s="5"/>
@@ -17466,7 +17478,7 @@
         <v>55</v>
       </c>
       <c r="S196" s="5" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="T196" s="5"/>
       <c r="U196" s="5"/>
@@ -17500,7 +17512,7 @@
         <v>599</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>85</v>
@@ -17618,19 +17630,19 @@
         <v>55</v>
       </c>
       <c r="AI198" s="8" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AJ198" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AK198" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="AL198" s="8" t="s">
         <v>55</v>
       </c>
       <c r="AM198" s="8" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="AN198" s="9"/>
       <c r="AO198" s="9"/>
@@ -17696,19 +17708,19 @@
         <v>39</v>
       </c>
       <c r="AI199" s="8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AJ199" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AK199" s="8" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="AL199" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM199" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="AN199" s="9"/>
       <c r="AO199" s="9"/>
@@ -17764,13 +17776,13 @@
         <v>39</v>
       </c>
       <c r="AK200" s="8" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="AL200" s="8" t="s">
         <v>39</v>
       </c>
       <c r="AM200" s="8" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="AN200" s="9"/>
       <c r="AO200" s="9"/>
@@ -17784,7 +17796,7 @@
         <v>616</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>38</v>
@@ -17848,7 +17860,7 @@
         <v>39</v>
       </c>
       <c r="AM201" s="5" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="AN201" s="9"/>
       <c r="AO201" s="9"/>
@@ -17916,13 +17928,13 @@
         <v>213</v>
       </c>
       <c r="AK202" s="8" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="AL202" s="25" t="s">
         <v>213</v>
       </c>
       <c r="AM202" s="8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AN202" s="9"/>
       <c r="AO202" s="9"/>
@@ -17936,7 +17948,7 @@
         <v>568</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>85</v>
@@ -18255,10 +18267,10 @@
       <c r="AH207" s="8"/>
       <c r="AI207" s="8"/>
       <c r="AJ207" s="26" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="AK207" s="26" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="AL207" s="5"/>
       <c r="AM207" s="5"/>
@@ -18311,10 +18323,10 @@
       <c r="AH208" s="5"/>
       <c r="AI208" s="5"/>
       <c r="AJ208" s="26" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="AK208" s="26" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AL208" s="5"/>
       <c r="AM208" s="5"/>
@@ -18370,7 +18382,7 @@
         <v>149</v>
       </c>
       <c r="AI209" s="8" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AJ209" s="8"/>
       <c r="AK209" s="8"/>
@@ -18428,7 +18440,7 @@
         <v>39</v>
       </c>
       <c r="AI210" s="5" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AJ210" s="5"/>
       <c r="AK210" s="5"/>
@@ -18498,7 +18510,7 @@
     </row>
     <row r="212" spans="1:42" ht="14.5">
       <c r="A212" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>36</v>
@@ -18540,7 +18552,7 @@
         <v>39</v>
       </c>
       <c r="U212" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="V212" s="5"/>
       <c r="W212" s="5"/>
@@ -18570,13 +18582,13 @@
     </row>
     <row r="213" spans="1:42" ht="14.5">
       <c r="A213" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>38</v>
@@ -18604,7 +18616,7 @@
         <v>55</v>
       </c>
       <c r="Q213" s="5" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="R213" s="5"/>
       <c r="S213" s="5"/>
@@ -18612,7 +18624,7 @@
         <v>55</v>
       </c>
       <c r="U213" s="5" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="V213" s="5"/>
       <c r="W213" s="5"/>
@@ -18624,7 +18636,7 @@
         <v>55</v>
       </c>
       <c r="AC213" s="7" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AD213" s="5"/>
       <c r="AE213" s="5"/>
@@ -18642,13 +18654,13 @@
     </row>
     <row r="214" spans="1:42" ht="14.5">
       <c r="A214" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>38</v>
@@ -18680,7 +18692,7 @@
         <v>39</v>
       </c>
       <c r="U214" s="5" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="V214" s="5"/>
       <c r="W214" s="5"/>
@@ -18710,7 +18722,7 @@
     </row>
     <row r="215" spans="1:42" ht="14.5">
       <c r="A215" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>76</v>
@@ -18770,7 +18782,7 @@
     </row>
     <row r="216" spans="1:42" ht="14.5">
       <c r="A216" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>83</v>
@@ -18824,7 +18836,7 @@
     </row>
     <row r="217" spans="1:42" ht="29">
       <c r="A217" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>87</v>
@@ -18898,7 +18910,7 @@
     </row>
     <row r="218" spans="1:42" ht="29">
       <c r="A218" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>90</v>
@@ -18988,7 +19000,7 @@
     </row>
     <row r="219" spans="1:42" ht="14.5">
       <c r="A219" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>97</v>
@@ -19032,7 +19044,7 @@
         <v>55</v>
       </c>
       <c r="U219" s="5" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="V219" s="5"/>
       <c r="W219" s="5"/>
@@ -19070,7 +19082,7 @@
     </row>
     <row r="220" spans="1:42" ht="14.5">
       <c r="A220" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>111</v>
@@ -19144,7 +19156,7 @@
     </row>
     <row r="221" spans="1:42" ht="58">
       <c r="A221" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>122</v>
@@ -19168,7 +19180,7 @@
         <v>55</v>
       </c>
       <c r="I221" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
@@ -19180,7 +19192,7 @@
         <v>55</v>
       </c>
       <c r="Q221" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="R221" s="5"/>
       <c r="S221" s="5"/>
@@ -19188,7 +19200,7 @@
         <v>39</v>
       </c>
       <c r="U221" s="21" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="V221" s="5"/>
       <c r="W221" s="5"/>
@@ -19200,7 +19212,7 @@
         <v>55</v>
       </c>
       <c r="AC221" s="13" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AD221" s="5"/>
       <c r="AE221" s="5"/>
@@ -19218,7 +19230,7 @@
     </row>
     <row r="222" spans="1:42" ht="14.5">
       <c r="A222" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>136</v>
@@ -19262,7 +19274,7 @@
         <v>39</v>
       </c>
       <c r="U222" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="V222" s="5"/>
       <c r="W222" s="5"/>
@@ -19292,7 +19304,7 @@
     </row>
     <row r="223" spans="1:42" ht="14.5">
       <c r="A223" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>138</v>
@@ -19358,13 +19370,13 @@
     </row>
     <row r="224" spans="1:42" ht="29">
       <c r="A224" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>146</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>85</v>
@@ -19424,13 +19436,13 @@
     </row>
     <row r="225" spans="1:42" ht="43.5">
       <c r="A225" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>156</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>38</v>
@@ -19498,13 +19510,13 @@
     </row>
     <row r="226" spans="1:42" ht="58">
       <c r="A226" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>167</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>38</v>
@@ -19542,7 +19554,7 @@
         <v>39</v>
       </c>
       <c r="U226" s="5" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="V226" s="5"/>
       <c r="W226" s="5"/>
@@ -19554,7 +19566,7 @@
         <v>39</v>
       </c>
       <c r="AC226" s="7" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="AD226" s="5"/>
       <c r="AE226" s="5"/>
@@ -19572,7 +19584,7 @@
     </row>
     <row r="227" spans="1:42" ht="14.5">
       <c r="A227" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>200</v>
@@ -19624,7 +19636,7 @@
     </row>
     <row r="228" spans="1:42" ht="14.5">
       <c r="A228" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>201</v>
@@ -19676,7 +19688,7 @@
     </row>
     <row r="229" spans="1:42" ht="14.5">
       <c r="A229" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>202</v>
@@ -19728,7 +19740,7 @@
     </row>
     <row r="230" spans="1:42" ht="14.5">
       <c r="A230" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>203</v>
@@ -19782,7 +19794,7 @@
     </row>
     <row r="231" spans="1:42" ht="14.5">
       <c r="A231" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>209</v>
@@ -19838,7 +19850,7 @@
     </row>
     <row r="232" spans="1:42" ht="14.5">
       <c r="A232" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>211</v>
@@ -19858,7 +19870,7 @@
         <v>59</v>
       </c>
       <c r="I232" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="J232" s="5"/>
       <c r="K232" s="5"/>
@@ -19896,13 +19908,13 @@
     </row>
     <row r="233" spans="1:42" ht="14.5">
       <c r="A233" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>420</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>85</v>
@@ -19962,7 +19974,7 @@
     </row>
     <row r="234" spans="1:42" ht="43.5">
       <c r="A234" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>425</v>
@@ -20032,7 +20044,7 @@
     </row>
     <row r="235" spans="1:42" ht="43.5">
       <c r="A235" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>430</v>
@@ -20102,7 +20114,7 @@
     </row>
     <row r="236" spans="1:42" ht="14.5">
       <c r="A236" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>437</v>
@@ -20154,7 +20166,7 @@
     </row>
     <row r="237" spans="1:42" ht="14.5">
       <c r="A237" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>438</v>
@@ -20206,7 +20218,7 @@
     </row>
     <row r="238" spans="1:42" ht="14.5">
       <c r="A238" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>439</v>
@@ -20258,7 +20270,7 @@
     </row>
     <row r="239" spans="1:42" ht="43.5">
       <c r="A239" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>440</v>
@@ -20282,7 +20294,7 @@
         <v>59</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="J239" s="5"/>
       <c r="K239" s="5"/>
@@ -20324,13 +20336,13 @@
     </row>
     <row r="240" spans="1:42" ht="29">
       <c r="A240" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>349</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>85</v>
@@ -20353,10 +20365,10 @@
       <c r="N240" s="5"/>
       <c r="O240" s="5"/>
       <c r="P240" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="Q240" s="5" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="R240" s="5"/>
       <c r="S240" s="5"/>
@@ -20386,13 +20398,13 @@
     </row>
     <row r="241" spans="1:42" ht="188.5">
       <c r="A241" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>358</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>38</v>
@@ -20404,7 +20416,7 @@
         <v>372</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>361</v>
@@ -20419,10 +20431,10 @@
       <c r="N241" s="5"/>
       <c r="O241" s="5"/>
       <c r="P241" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="Q241" s="5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="R241" s="5"/>
       <c r="S241" s="5"/>
@@ -20430,7 +20442,7 @@
         <v>55</v>
       </c>
       <c r="U241" s="5" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="V241" s="5"/>
       <c r="W241" s="5"/>
@@ -20442,7 +20454,7 @@
         <v>93</v>
       </c>
       <c r="AC241" s="7" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="AD241" s="5"/>
       <c r="AE241" s="5"/>
@@ -20460,13 +20472,13 @@
     </row>
     <row r="242" spans="1:42" ht="145">
       <c r="A242" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>375</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>38</v>
@@ -20478,13 +20490,13 @@
         <v>379</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>377</v>
       </c>
       <c r="I242" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="J242" s="5"/>
       <c r="K242" s="5"/>
@@ -20493,10 +20505,10 @@
       <c r="N242" s="5"/>
       <c r="O242" s="5"/>
       <c r="P242" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="Q242" s="5" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="R242" s="5"/>
       <c r="S242" s="5"/>
@@ -20504,7 +20516,7 @@
         <v>39</v>
       </c>
       <c r="U242" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="V242" s="5"/>
       <c r="W242" s="5"/>
@@ -20516,7 +20528,7 @@
         <v>180</v>
       </c>
       <c r="AC242" s="7" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="AD242" s="5"/>
       <c r="AE242" s="5"/>
@@ -20534,7 +20546,7 @@
     </row>
     <row r="243" spans="1:42" ht="29">
       <c r="A243" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>390</v>
@@ -20586,13 +20598,13 @@
     </row>
     <row r="244" spans="1:42" ht="14.5">
       <c r="A244" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>38</v>
@@ -20644,13 +20656,13 @@
     </row>
     <row r="245" spans="1:42" ht="14.5">
       <c r="A245" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>391</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>38</v>
@@ -20702,13 +20714,13 @@
     </row>
     <row r="246" spans="1:42" ht="14.5">
       <c r="A246" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>401</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>38</v>
@@ -20760,7 +20772,7 @@
     </row>
     <row r="247" spans="1:42" ht="174">
       <c r="A247" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>406</v>
@@ -20789,10 +20801,10 @@
       <c r="N247" s="5"/>
       <c r="O247" s="5"/>
       <c r="P247" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="Q247" s="5" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="R247" s="5"/>
       <c r="S247" s="5"/>
@@ -20822,7 +20834,7 @@
     </row>
     <row r="248" spans="1:42" ht="14.5">
       <c r="A248" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>258</v>
@@ -20856,7 +20868,7 @@
         <v>149</v>
       </c>
       <c r="Q248" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="R248" s="5"/>
       <c r="S248" s="5"/>
@@ -20886,7 +20898,7 @@
     </row>
     <row r="249" spans="1:42" ht="29">
       <c r="A249" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>264</v>
@@ -20906,7 +20918,7 @@
         <v>59</v>
       </c>
       <c r="I249" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J249" s="5"/>
       <c r="K249" s="5"/>
@@ -20918,7 +20930,7 @@
         <v>39</v>
       </c>
       <c r="Q249" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="R249" s="5"/>
       <c r="S249" s="5"/>
@@ -20948,7 +20960,7 @@
     </row>
     <row r="250" spans="1:42" ht="14.5">
       <c r="A250" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>276</v>
@@ -21002,7 +21014,7 @@
     </row>
     <row r="251" spans="1:42" ht="14.5">
       <c r="A251" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>278</v>
@@ -21056,7 +21068,7 @@
     </row>
     <row r="252" spans="1:42" ht="14.5">
       <c r="A252" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>280</v>
@@ -21110,7 +21122,7 @@
     </row>
     <row r="253" spans="1:42" ht="14.5">
       <c r="A253" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>282</v>
@@ -21130,7 +21142,7 @@
         <v>59</v>
       </c>
       <c r="I253" s="6" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="J253" s="5"/>
       <c r="K253" s="5"/>
@@ -21168,7 +21180,7 @@
     </row>
     <row r="254" spans="1:42" ht="29">
       <c r="A254" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>285</v>
@@ -21188,7 +21200,7 @@
         <v>59</v>
       </c>
       <c r="I254" s="6" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="J254" s="5"/>
       <c r="K254" s="5"/>
@@ -21200,7 +21212,7 @@
         <v>55</v>
       </c>
       <c r="Q254" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="R254" s="5"/>
       <c r="S254" s="5"/>
@@ -21230,7 +21242,7 @@
     </row>
     <row r="255" spans="1:42" ht="14.5">
       <c r="A255" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>293</v>
@@ -21284,7 +21296,7 @@
     </row>
     <row r="256" spans="1:42" ht="14.5">
       <c r="A256" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>286</v>
@@ -21338,13 +21350,13 @@
     </row>
     <row r="257" spans="1:42" ht="29">
       <c r="A257" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>323</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>85</v>
@@ -21366,7 +21378,7 @@
         <v>149</v>
       </c>
       <c r="Q257" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="R257" s="5"/>
       <c r="S257" s="5"/>
@@ -21396,13 +21408,13 @@
     </row>
     <row r="258" spans="1:42" ht="14.5">
       <c r="A258" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>329</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>38</v>
@@ -21424,7 +21436,7 @@
         <v>55</v>
       </c>
       <c r="Q258" s="5" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="R258" s="5"/>
       <c r="S258" s="5"/>
@@ -21454,7 +21466,7 @@
     </row>
     <row r="259" spans="1:42" ht="14.5">
       <c r="A259" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>335</v>
@@ -21508,7 +21520,7 @@
     </row>
     <row r="260" spans="1:42" ht="29">
       <c r="A260" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>337</v>
@@ -21536,7 +21548,7 @@
         <v>39</v>
       </c>
       <c r="Q260" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="R260" s="5"/>
       <c r="S260" s="5"/>
@@ -21566,7 +21578,7 @@
     </row>
     <row r="261" spans="1:42" ht="14.5">
       <c r="A261" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>345</v>
@@ -21620,13 +21632,13 @@
     </row>
     <row r="262" spans="1:42" ht="14.5">
       <c r="A262" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>491</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D262" s="5" t="s">
         <v>85</v>
@@ -21678,7 +21690,7 @@
     </row>
     <row r="263" spans="1:42" ht="14.5">
       <c r="A263" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>498</v>
@@ -21740,7 +21752,7 @@
     </row>
     <row r="264" spans="1:42" ht="29">
       <c r="A264" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>507</v>
@@ -21798,7 +21810,7 @@
     </row>
     <row r="265" spans="1:42" ht="29">
       <c r="A265" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>511</v>
@@ -21856,7 +21868,7 @@
     </row>
     <row r="266" spans="1:42" ht="29">
       <c r="A266" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>515</v>
@@ -21914,7 +21926,7 @@
     </row>
     <row r="267" spans="1:42" ht="29">
       <c r="A267" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>519</v>
@@ -21972,7 +21984,7 @@
     </row>
     <row r="268" spans="1:42" ht="29">
       <c r="A268" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>530</v>
@@ -22030,7 +22042,7 @@
     </row>
     <row r="269" spans="1:42" ht="14.5">
       <c r="A269" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>524</v>
@@ -22088,7 +22100,7 @@
     </row>
     <row r="270" spans="1:42" ht="29">
       <c r="A270" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>535</v>
@@ -22146,7 +22158,7 @@
     </row>
     <row r="271" spans="1:42" ht="14.5">
       <c r="A271" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>541</v>
@@ -22200,19 +22212,19 @@
     </row>
     <row r="272" spans="1:42" ht="14.5">
       <c r="A272" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D272" s="5" t="s">
         <v>85</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F272" s="5"/>
       <c r="G272" s="5"/>
@@ -22232,7 +22244,7 @@
         <v>149</v>
       </c>
       <c r="Q272" s="5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="R272" s="5"/>
       <c r="S272" s="5"/>
@@ -22262,19 +22274,19 @@
     </row>
     <row r="273" spans="1:42" ht="14.5">
       <c r="A273" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5"/>
@@ -22282,7 +22294,7 @@
         <v>59</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J273" s="5"/>
       <c r="K273" s="5"/>
@@ -22294,7 +22306,7 @@
         <v>39</v>
       </c>
       <c r="Q273" s="5" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="R273" s="5"/>
       <c r="S273" s="5"/>
@@ -22324,19 +22336,19 @@
     </row>
     <row r="274" spans="1:42" ht="14.5">
       <c r="A274" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D274" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F274" s="5"/>
       <c r="G274" s="5"/>
@@ -22344,7 +22356,7 @@
         <v>59</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="J274" s="5"/>
       <c r="K274" s="5"/>
@@ -22356,7 +22368,7 @@
         <v>39</v>
       </c>
       <c r="Q274" s="5" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="R274" s="5"/>
       <c r="S274" s="5"/>
@@ -22386,19 +22398,19 @@
     </row>
     <row r="275" spans="1:42" ht="14.5">
       <c r="A275" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D275" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F275" s="5"/>
       <c r="G275" s="5"/>
@@ -22406,7 +22418,7 @@
         <v>59</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="J275" s="5"/>
       <c r="K275" s="5"/>
@@ -22418,7 +22430,7 @@
         <v>39</v>
       </c>
       <c r="Q275" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="R275" s="5"/>
       <c r="S275" s="5"/>
@@ -22448,19 +22460,19 @@
     </row>
     <row r="276" spans="1:42" ht="29">
       <c r="A276" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D276" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F276" s="5"/>
       <c r="G276" s="5"/>
@@ -22502,19 +22514,19 @@
     </row>
     <row r="277" spans="1:42" ht="14.5">
       <c r="A277" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F277" s="5"/>
       <c r="G277" s="5"/>
@@ -22522,7 +22534,7 @@
         <v>59</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="J277" s="5"/>
       <c r="K277" s="5"/>
@@ -22534,7 +22546,7 @@
         <v>39</v>
       </c>
       <c r="Q277" s="5" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="R277" s="5"/>
       <c r="S277" s="5"/>
@@ -22564,19 +22576,19 @@
     </row>
     <row r="278" spans="1:42" ht="14.5">
       <c r="A278" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D278" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F278" s="5"/>
       <c r="G278" s="5"/>
@@ -22592,7 +22604,7 @@
         <v>39</v>
       </c>
       <c r="Q278" s="5" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="R278" s="5"/>
       <c r="S278" s="5"/>
@@ -22622,17 +22634,17 @@
     </row>
     <row r="279" spans="1:42" ht="14.5">
       <c r="A279" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C279" s="5"/>
       <c r="D279" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F279" s="5"/>
       <c r="G279" s="5"/>
@@ -22640,7 +22652,7 @@
         <v>59</v>
       </c>
       <c r="I279" s="6" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="J279" s="5"/>
       <c r="K279" s="5"/>
@@ -22652,7 +22664,7 @@
         <v>39</v>
       </c>
       <c r="Q279" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="R279" s="5"/>
       <c r="S279" s="5"/>
@@ -22682,17 +22694,17 @@
     </row>
     <row r="280" spans="1:42" ht="14.5">
       <c r="A280" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C280" s="5"/>
       <c r="D280" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F280" s="5"/>
       <c r="G280" s="5"/>
@@ -22700,7 +22712,7 @@
         <v>59</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="J280" s="5"/>
       <c r="K280" s="5"/>
@@ -22738,31 +22750,31 @@
     </row>
     <row r="281" spans="1:42" ht="14.5">
       <c r="A281" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D281" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>39</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="H281" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="J281" s="5"/>
       <c r="K281" s="5"/>
@@ -22800,19 +22812,19 @@
     </row>
     <row r="282" spans="1:42" ht="14.5">
       <c r="A282" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D282" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F282" s="5" t="s">
         <v>39</v>
@@ -22858,17 +22870,17 @@
     </row>
     <row r="283" spans="1:42" ht="14.5">
       <c r="A283" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C283" s="5"/>
       <c r="D283" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F283" s="5"/>
       <c r="G283" s="5"/>
@@ -22886,7 +22898,7 @@
       <c r="O283" s="5"/>
       <c r="P283" s="5"/>
       <c r="Q283" s="5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="R283" s="5"/>
       <c r="S283" s="5"/>
@@ -22916,17 +22928,17 @@
     </row>
     <row r="284" spans="1:42" ht="43.5">
       <c r="A284" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C284" s="5"/>
       <c r="D284" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F284" s="5"/>
       <c r="G284" s="5"/>
@@ -22934,7 +22946,7 @@
         <v>59</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="J284" s="5"/>
       <c r="K284" s="5"/>
@@ -22946,7 +22958,7 @@
         <v>579</v>
       </c>
       <c r="Q284" s="5" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="R284" s="5"/>
       <c r="S284" s="5"/>
@@ -22976,17 +22988,17 @@
     </row>
     <row r="285" spans="1:42" ht="43.5">
       <c r="A285" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C285" s="5"/>
       <c r="D285" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F285" s="5"/>
       <c r="G285" s="5"/>
@@ -22994,7 +23006,7 @@
         <v>59</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="J285" s="5"/>
       <c r="K285" s="5"/>
@@ -23006,7 +23018,7 @@
         <v>594</v>
       </c>
       <c r="Q285" s="5" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="R285" s="5"/>
       <c r="S285" s="5"/>
@@ -23036,7 +23048,7 @@
     </row>
     <row r="286" spans="1:42" ht="14.5">
       <c r="A286" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>445</v>
@@ -23098,7 +23110,7 @@
     </row>
     <row r="287" spans="1:42" ht="14.5">
       <c r="A287" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>450</v>
@@ -23168,7 +23180,7 @@
     </row>
     <row r="288" spans="1:42" ht="14.5">
       <c r="A288" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>453</v>
@@ -23238,7 +23250,7 @@
     </row>
     <row r="289" spans="1:42" ht="29">
       <c r="A289" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>463</v>
@@ -23308,7 +23320,7 @@
     </row>
     <row r="290" spans="1:42" ht="14.5">
       <c r="A290" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>472</v>
@@ -23378,13 +23390,13 @@
     </row>
     <row r="291" spans="1:42" ht="14.5">
       <c r="A291" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>599</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>85</v>
@@ -23436,7 +23448,7 @@
     </row>
     <row r="292" spans="1:42" ht="43.5">
       <c r="A292" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>603</v>
@@ -23480,7 +23492,7 @@
         <v>55</v>
       </c>
       <c r="U292" s="5" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="V292" s="5"/>
       <c r="W292" s="5"/>
@@ -23506,7 +23518,7 @@
     </row>
     <row r="293" spans="1:42" ht="14.5">
       <c r="A293" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>609</v>
@@ -23550,7 +23562,7 @@
         <v>39</v>
       </c>
       <c r="U293" s="5" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="V293" s="5"/>
       <c r="W293" s="5"/>
@@ -23576,7 +23588,7 @@
     </row>
     <row r="294" spans="1:42" ht="14.5">
       <c r="A294" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>614</v>
@@ -23630,13 +23642,13 @@
     </row>
     <row r="295" spans="1:42" ht="43.5">
       <c r="A295" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>616</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D295" s="5" t="s">
         <v>38</v>
@@ -23700,7 +23712,7 @@
     </row>
     <row r="296" spans="1:42" ht="29">
       <c r="A296" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>621</v>
@@ -23762,13 +23774,13 @@
     </row>
     <row r="297" spans="1:42" ht="43.5">
       <c r="A297" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>546</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D297" s="5" t="s">
         <v>85</v>
@@ -23794,7 +23806,7 @@
         <v>571</v>
       </c>
       <c r="Q297" s="5" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="R297" s="5"/>
       <c r="S297" s="5"/>
@@ -23824,13 +23836,13 @@
     </row>
     <row r="298" spans="1:42" ht="14.5">
       <c r="A298" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>550</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D298" s="5" t="s">
         <v>38</v>
@@ -23856,7 +23868,7 @@
         <v>579</v>
       </c>
       <c r="Q298" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="R298" s="5"/>
       <c r="S298" s="5"/>
@@ -23886,7 +23898,7 @@
     </row>
     <row r="299" spans="1:42" ht="29">
       <c r="A299" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>554</v>
@@ -23944,7 +23956,7 @@
     </row>
     <row r="300" spans="1:42" ht="43.5">
       <c r="A300" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>557</v>
@@ -23976,7 +23988,7 @@
         <v>594</v>
       </c>
       <c r="Q300" s="5" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="R300" s="5"/>
       <c r="S300" s="5"/>
@@ -24006,7 +24018,7 @@
     </row>
     <row r="301" spans="1:42" ht="14.5">
       <c r="A301" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>561</v>
@@ -24060,7 +24072,7 @@
     </row>
     <row r="302" spans="1:42" ht="14.5">
       <c r="A302" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>563</v>
@@ -24114,7 +24126,7 @@
     </row>
     <row r="303" spans="1:42" ht="14.5">
       <c r="A303" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>565</v>
@@ -24172,13 +24184,13 @@
     </row>
     <row r="304" spans="1:42" ht="29">
       <c r="A304" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>568</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D304" s="5" t="s">
         <v>85</v>
@@ -24234,7 +24246,7 @@
     </row>
     <row r="305" spans="1:42" ht="87">
       <c r="A305" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>574</v>
@@ -24304,7 +24316,7 @@
     </row>
     <row r="306" spans="1:42" ht="87">
       <c r="A306" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>587</v>
@@ -24356,7 +24368,7 @@
         <v>39</v>
       </c>
       <c r="AC306" s="7" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="AD306" s="5"/>
       <c r="AE306" s="5"/>
@@ -24374,7 +24386,7 @@
     </row>
     <row r="307" spans="1:42" ht="14.5">
       <c r="A307" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>625</v>
@@ -24426,7 +24438,7 @@
     </row>
     <row r="308" spans="1:42" ht="14.5">
       <c r="A308" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>627</v>
@@ -24478,7 +24490,7 @@
     </row>
     <row r="309" spans="1:42" ht="14.5">
       <c r="A309" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>630</v>
@@ -24530,7 +24542,7 @@
     </row>
     <row r="310" spans="1:42" ht="14.5">
       <c r="A310" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>633</v>
@@ -24584,7 +24596,7 @@
     </row>
     <row r="311" spans="1:42" ht="14.5">
       <c r="A311" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>638</v>
@@ -24638,7 +24650,7 @@
     </row>
     <row r="312" spans="1:42" ht="14.5">
       <c r="A312" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>641</v>

--- a/data/rules/mapping.xlsx
+++ b/data/rules/mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cloned repos\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7111F8-7C08-4E97-A5E6-5A6D0DFCCC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2A4E96-E3D4-4299-9FB1-4C8BDFD72404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2170" yWindow="1850" windowWidth="15680" windowHeight="9430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New Watchlist Mapping" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="1079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4483" uniqueCount="1094">
   <si>
     <t>Entity Category</t>
   </si>
@@ -3439,6 +3439,51 @@
   </si>
   <si>
     <t>detail.race_ethnicity * detail.hair * detail.eyes * detail.weight * detail.height * detail.skin_tone * detail.scar_tattoo * detail.reward * detail.wanted_in * detail.warrant_case_nr</t>
+  </si>
+  <si>
+    <t>US-STATE-TERRORIST-EXCLUSION</t>
+  </si>
+  <si>
+    <t>"US-STATE-TERRORIST-EXCLUSION"</t>
+  </si>
+  <si>
+    <t>"US-STATE"</t>
+  </si>
+  <si>
+    <t>https://www.state.gov/terrorist-exclusion-list/</t>
+  </si>
+  <si>
+    <t>"Terrorist Exclusion List (TEL) - designated under USA PATRIOT ACT section 411"</t>
+  </si>
+  <si>
+    <t>list.primary_name</t>
+  </si>
+  <si>
+    <t>list.alias_blob[]</t>
+  </si>
+  <si>
+    <t>list.alias_blob.type</t>
+  </si>
+  <si>
+    <t>list.alias_blob.value</t>
+  </si>
+  <si>
+    <t>list.section</t>
+  </si>
+  <si>
+    <t>"Immigration exclusion designation (USA PATRIOT ACT section 411)"</t>
+  </si>
+  <si>
+    <t>"Designation Criteria" * "Designation Process" * "Effects of Designation" * "Tag"</t>
+  </si>
+  <si>
+    <t>path * path * path * list_expand</t>
+  </si>
+  <si>
+    <t>list.designation_criteria * list.designation_process * list.effects_of_designation * list.tags</t>
+  </si>
+  <si>
+    <t>US-STATE-TERRORIST-EXCLUSION TYPE</t>
   </si>
 </sst>
 </file>
@@ -3789,7 +3834,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4036,6 +4081,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4259,7 +4307,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AU1030"/>
+  <dimension ref="A1:AW1030"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4300,9 +4348,11 @@
     <col min="45" max="45" width="28.453125" customWidth="1"/>
     <col min="46" max="46" width="40.08984375" style="81" customWidth="1"/>
     <col min="47" max="47" width="34.6328125" style="84" customWidth="1"/>
+    <col min="48" max="48" width="39.1796875" style="89" customWidth="1"/>
+    <col min="49" max="49" width="34.36328125" style="89" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="14.5">
+    <row r="1" spans="1:49" ht="14.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4444,8 +4494,14 @@
       <c r="AU1" s="84" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="2" spans="1:47" ht="29">
+      <c r="AV1" s="77" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AW1" s="77" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" ht="29">
       <c r="A2" s="10" t="s">
         <v>41</v>
       </c>
@@ -4566,7 +4622,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="29">
+    <row r="3" spans="1:49" ht="29">
       <c r="A3" s="10" t="s">
         <v>41</v>
       </c>
@@ -4687,7 +4743,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="58">
+    <row r="4" spans="1:49" ht="58">
       <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
@@ -4785,7 +4841,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="43.5">
+    <row r="5" spans="1:49" ht="43.5">
       <c r="A5" s="10" t="s">
         <v>41</v>
       </c>
@@ -4874,7 +4930,7 @@
       <c r="AT5" s="79"/>
       <c r="AU5" s="82"/>
     </row>
-    <row r="6" spans="1:47" ht="14.5">
+    <row r="6" spans="1:49" ht="14.5">
       <c r="A6" s="10" t="s">
         <v>41</v>
       </c>
@@ -4951,7 +5007,7 @@
       <c r="AT6" s="79"/>
       <c r="AU6" s="82"/>
     </row>
-    <row r="7" spans="1:47" ht="14.5">
+    <row r="7" spans="1:49" ht="14.5">
       <c r="A7" s="10" t="s">
         <v>41</v>
       </c>
@@ -5010,7 +5066,7 @@
       <c r="AT7" s="79"/>
       <c r="AU7" s="82"/>
     </row>
-    <row r="8" spans="1:47" ht="29">
+    <row r="8" spans="1:49" ht="29">
       <c r="A8" s="10" t="s">
         <v>41</v>
       </c>
@@ -5129,7 +5185,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="29">
+    <row r="9" spans="1:49" ht="29">
       <c r="A9" s="10" t="s">
         <v>41</v>
       </c>
@@ -5252,7 +5308,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.5">
+    <row r="10" spans="1:49" ht="14.5">
       <c r="A10" s="10" t="s">
         <v>41</v>
       </c>
@@ -5375,7 +5431,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.5">
+    <row r="11" spans="1:49" ht="14.5">
       <c r="A11" s="10" t="s">
         <v>41</v>
       </c>
@@ -5498,7 +5554,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="38.25" customHeight="1">
+    <row r="12" spans="1:49" ht="38.25" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>41</v>
       </c>
@@ -5621,7 +5677,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="29">
+    <row r="13" spans="1:49" ht="29">
       <c r="A13" s="10" t="s">
         <v>41</v>
       </c>
@@ -5740,7 +5796,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="29">
+    <row r="14" spans="1:49" ht="29">
       <c r="A14" s="10" t="s">
         <v>41</v>
       </c>
@@ -5823,7 +5879,7 @@
       <c r="AT14" s="79"/>
       <c r="AU14" s="82"/>
     </row>
-    <row r="15" spans="1:47" ht="29">
+    <row r="15" spans="1:49" ht="29">
       <c r="A15" s="10" t="s">
         <v>41</v>
       </c>
@@ -5910,7 +5966,7 @@
       <c r="AT15" s="79"/>
       <c r="AU15" s="82"/>
     </row>
-    <row r="16" spans="1:47" ht="43.5">
+    <row r="16" spans="1:49" ht="43.5">
       <c r="A16" s="10" t="s">
         <v>41</v>
       </c>
@@ -13298,7 +13354,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="113" spans="1:47" ht="101.5">
+    <row r="113" spans="1:49" ht="101.5">
       <c r="A113" s="10" t="s">
         <v>41</v>
       </c>
@@ -13371,7 +13427,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="114" spans="1:47" ht="29">
+    <row r="114" spans="1:49" ht="29">
       <c r="A114" s="33" t="s">
         <v>41</v>
       </c>
@@ -13438,7 +13494,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="115" spans="1:47" ht="29">
+    <row r="115" spans="1:49" ht="29">
       <c r="A115" s="33" t="s">
         <v>41</v>
       </c>
@@ -13509,7 +13565,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="116" spans="1:47" ht="26">
+    <row r="116" spans="1:49" ht="26">
       <c r="A116" s="33" t="s">
         <v>41</v>
       </c>
@@ -13580,7 +13636,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="117" spans="1:47" ht="29">
+    <row r="117" spans="1:49" ht="29">
       <c r="A117" s="10" t="s">
         <v>672</v>
       </c>
@@ -13681,8 +13737,14 @@
       <c r="AP117" s="16"/>
       <c r="AQ117" s="16"/>
       <c r="AU117" s="82"/>
-    </row>
-    <row r="118" spans="1:47" ht="29">
+      <c r="AV117" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW117" s="77" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="118" spans="1:49" ht="29">
       <c r="A118" s="10" t="s">
         <v>672</v>
       </c>
@@ -13786,8 +13848,14 @@
       <c r="AS118" s="9"/>
       <c r="AT118" s="79"/>
       <c r="AU118" s="82"/>
-    </row>
-    <row r="119" spans="1:47" ht="43.5">
+      <c r="AV118" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW118" s="12" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="119" spans="1:49" ht="43.5">
       <c r="A119" s="10" t="s">
         <v>672</v>
       </c>
@@ -13876,7 +13944,7 @@
       <c r="AT119" s="62"/>
       <c r="AU119" s="83"/>
     </row>
-    <row r="120" spans="1:47" ht="14.5">
+    <row r="120" spans="1:49" ht="14.5">
       <c r="A120" s="10" t="s">
         <v>672</v>
       </c>
@@ -13961,7 +14029,7 @@
       <c r="AT120" s="79"/>
       <c r="AU120" s="82"/>
     </row>
-    <row r="121" spans="1:47" ht="14.5">
+    <row r="121" spans="1:49" ht="14.5">
       <c r="A121" s="10" t="s">
         <v>672</v>
       </c>
@@ -14020,7 +14088,7 @@
       <c r="AT121" s="79"/>
       <c r="AU121" s="82"/>
     </row>
-    <row r="122" spans="1:47" ht="29">
+    <row r="122" spans="1:49" ht="29">
       <c r="A122" s="10" t="s">
         <v>672</v>
       </c>
@@ -14126,8 +14194,14 @@
       <c r="AS122" s="9"/>
       <c r="AT122" s="79"/>
       <c r="AU122" s="82"/>
-    </row>
-    <row r="123" spans="1:47" ht="29">
+      <c r="AV122" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW122" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:49" ht="29">
       <c r="A123" s="10" t="s">
         <v>672</v>
       </c>
@@ -14241,8 +14315,14 @@
       <c r="AS123" s="9"/>
       <c r="AT123" s="79"/>
       <c r="AU123" s="82"/>
-    </row>
-    <row r="124" spans="1:47" ht="14.5">
+      <c r="AV123" s="89" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW123" s="89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="124" spans="1:49" ht="14.5">
       <c r="A124" s="10" t="s">
         <v>672</v>
       </c>
@@ -14348,8 +14428,14 @@
       <c r="AS124" s="9"/>
       <c r="AT124" s="79"/>
       <c r="AU124" s="82"/>
-    </row>
-    <row r="125" spans="1:47" ht="14.5">
+      <c r="AV124" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW124" s="89" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="125" spans="1:49" ht="14.5">
       <c r="A125" s="10" t="s">
         <v>672</v>
       </c>
@@ -14455,8 +14541,14 @@
       <c r="AS125" s="9"/>
       <c r="AT125" s="79"/>
       <c r="AU125" s="82"/>
-    </row>
-    <row r="126" spans="1:47" ht="130.5">
+      <c r="AV125" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW125" s="89" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="126" spans="1:49" ht="130.5">
       <c r="A126" s="10" t="s">
         <v>672</v>
       </c>
@@ -14562,8 +14654,14 @@
       <c r="AS126" s="9"/>
       <c r="AT126" s="79"/>
       <c r="AU126" s="82"/>
-    </row>
-    <row r="127" spans="1:47" ht="29">
+      <c r="AV126" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW126" s="78" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="127" spans="1:49" ht="29">
       <c r="A127" s="10" t="s">
         <v>672</v>
       </c>
@@ -14669,8 +14767,14 @@
       <c r="AS127" s="9"/>
       <c r="AT127" s="79"/>
       <c r="AU127" s="82"/>
-    </row>
-    <row r="128" spans="1:47" ht="29">
+      <c r="AV127" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW127" s="77" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="128" spans="1:49" ht="38.5">
       <c r="A128" s="10" t="s">
         <v>672</v>
       </c>
@@ -14758,8 +14862,14 @@
       <c r="AS128" s="9"/>
       <c r="AT128" s="79"/>
       <c r="AU128" s="82"/>
-    </row>
-    <row r="129" spans="1:47" ht="29">
+      <c r="AV128" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW128" s="90" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="129" spans="1:49" ht="29">
       <c r="A129" s="10" t="s">
         <v>672</v>
       </c>
@@ -14842,7 +14952,7 @@
       <c r="AT129" s="79"/>
       <c r="AU129" s="82"/>
     </row>
-    <row r="130" spans="1:47" ht="43.5">
+    <row r="130" spans="1:49" ht="43.5">
       <c r="A130" s="10" t="s">
         <v>672</v>
       </c>
@@ -14944,8 +15054,14 @@
       <c r="AS130" s="9"/>
       <c r="AT130" s="79"/>
       <c r="AU130" s="82"/>
-    </row>
-    <row r="131" spans="1:47" ht="58">
+      <c r="AV130" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW130" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="131" spans="1:49" ht="58">
       <c r="A131" s="10" t="s">
         <v>672</v>
       </c>
@@ -15051,8 +15167,14 @@
       <c r="AS131" s="9"/>
       <c r="AT131" s="79"/>
       <c r="AU131" s="82"/>
-    </row>
-    <row r="132" spans="1:47" ht="29">
+      <c r="AV131" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW131" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="132" spans="1:49" ht="29">
       <c r="A132" s="10" t="s">
         <v>672</v>
       </c>
@@ -15109,7 +15231,7 @@
       <c r="AT132" s="79"/>
       <c r="AU132" s="82"/>
     </row>
-    <row r="133" spans="1:47" ht="14.5">
+    <row r="133" spans="1:49" ht="14.5">
       <c r="A133" s="10" t="s">
         <v>672</v>
       </c>
@@ -15166,7 +15288,7 @@
       <c r="AT133" s="79"/>
       <c r="AU133" s="82"/>
     </row>
-    <row r="134" spans="1:47" ht="14.5">
+    <row r="134" spans="1:49" ht="14.5">
       <c r="A134" s="10" t="s">
         <v>672</v>
       </c>
@@ -15223,7 +15345,7 @@
       <c r="AT134" s="79"/>
       <c r="AU134" s="82"/>
     </row>
-    <row r="135" spans="1:47" ht="29">
+    <row r="135" spans="1:49" ht="29">
       <c r="A135" s="10" t="s">
         <v>672</v>
       </c>
@@ -15290,7 +15412,7 @@
       <c r="AT135" s="79"/>
       <c r="AU135" s="82"/>
     </row>
-    <row r="136" spans="1:47" ht="43.5">
+    <row r="136" spans="1:49" ht="43.5">
       <c r="A136" s="10" t="s">
         <v>672</v>
       </c>
@@ -15355,7 +15477,7 @@
       <c r="AT136" s="62"/>
       <c r="AU136" s="83"/>
     </row>
-    <row r="137" spans="1:47" ht="43.5">
+    <row r="137" spans="1:49" ht="43.5">
       <c r="A137" s="10" t="s">
         <v>672</v>
       </c>
@@ -15430,7 +15552,7 @@
       <c r="AT137" s="79"/>
       <c r="AU137" s="82"/>
     </row>
-    <row r="138" spans="1:47" ht="14.5">
+    <row r="138" spans="1:49" ht="14.5">
       <c r="A138" s="10" t="s">
         <v>672</v>
       </c>
@@ -15501,7 +15623,7 @@
       <c r="AT138" s="79"/>
       <c r="AU138" s="82"/>
     </row>
-    <row r="139" spans="1:47" ht="116">
+    <row r="139" spans="1:49" ht="116">
       <c r="A139" s="10" t="s">
         <v>672</v>
       </c>
@@ -15583,7 +15705,7 @@
       <c r="AT139" s="79"/>
       <c r="AU139" s="82"/>
     </row>
-    <row r="140" spans="1:47" ht="14.5">
+    <row r="140" spans="1:49" ht="14.5">
       <c r="A140" s="10" t="s">
         <v>672</v>
       </c>
@@ -15641,7 +15763,7 @@
       <c r="AT140" s="79"/>
       <c r="AU140" s="82"/>
     </row>
-    <row r="141" spans="1:47" ht="14.5">
+    <row r="141" spans="1:49" ht="14.5">
       <c r="A141" s="10" t="s">
         <v>672</v>
       </c>
@@ -15699,7 +15821,7 @@
       <c r="AT141" s="79"/>
       <c r="AU141" s="82"/>
     </row>
-    <row r="142" spans="1:47" ht="14.5">
+    <row r="142" spans="1:49" ht="14.5">
       <c r="A142" s="10" t="s">
         <v>672</v>
       </c>
@@ -15757,7 +15879,7 @@
       <c r="AT142" s="79"/>
       <c r="AU142" s="82"/>
     </row>
-    <row r="143" spans="1:47" ht="72.5">
+    <row r="143" spans="1:49" ht="72.5">
       <c r="A143" s="10" t="s">
         <v>672</v>
       </c>
@@ -15823,7 +15945,7 @@
       <c r="AT143" s="79"/>
       <c r="AU143" s="82"/>
     </row>
-    <row r="144" spans="1:47" ht="130.5">
+    <row r="144" spans="1:49" ht="130.5">
       <c r="A144" s="10" t="s">
         <v>672</v>
       </c>
@@ -17084,7 +17206,7 @@
       <c r="AT160" s="79"/>
       <c r="AU160" s="82"/>
     </row>
-    <row r="161" spans="1:47" ht="14.5">
+    <row r="161" spans="1:49" ht="14.5">
       <c r="A161" s="10" t="s">
         <v>672</v>
       </c>
@@ -17155,7 +17277,7 @@
       <c r="AT161" s="79"/>
       <c r="AU161" s="82"/>
     </row>
-    <row r="162" spans="1:47" ht="14.5">
+    <row r="162" spans="1:49" ht="14.5">
       <c r="A162" s="10" t="s">
         <v>672</v>
       </c>
@@ -17233,8 +17355,14 @@
       <c r="AS162" s="9"/>
       <c r="AT162" s="79"/>
       <c r="AU162" s="82"/>
-    </row>
-    <row r="163" spans="1:47" ht="43.5">
+      <c r="AV162" s="77" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW162" s="77" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="163" spans="1:49" ht="43.5">
       <c r="A163" s="10" t="s">
         <v>672</v>
       </c>
@@ -17316,8 +17444,14 @@
       <c r="AS163" s="9"/>
       <c r="AT163" s="79"/>
       <c r="AU163" s="82"/>
-    </row>
-    <row r="164" spans="1:47" ht="58">
+      <c r="AV163" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW163" s="77" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="164" spans="1:49" ht="58">
       <c r="A164" s="10" t="s">
         <v>672</v>
       </c>
@@ -17399,8 +17533,14 @@
       <c r="AS164" s="9"/>
       <c r="AT164" s="79"/>
       <c r="AU164" s="82"/>
-    </row>
-    <row r="165" spans="1:47" ht="14.5">
+      <c r="AV164" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW164" s="89" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="165" spans="1:49" ht="14.5">
       <c r="A165" s="10" t="s">
         <v>672</v>
       </c>
@@ -17457,7 +17597,7 @@
       <c r="AT165" s="79"/>
       <c r="AU165" s="82"/>
     </row>
-    <row r="166" spans="1:47" ht="14.5">
+    <row r="166" spans="1:49" ht="14.5">
       <c r="A166" s="10" t="s">
         <v>672</v>
       </c>
@@ -17514,7 +17654,7 @@
       <c r="AT166" s="79"/>
       <c r="AU166" s="82"/>
     </row>
-    <row r="167" spans="1:47" ht="14.5">
+    <row r="167" spans="1:49" ht="14.5">
       <c r="A167" s="10" t="s">
         <v>672</v>
       </c>
@@ -17571,7 +17711,7 @@
       <c r="AT167" s="79"/>
       <c r="AU167" s="82"/>
     </row>
-    <row r="168" spans="1:47" ht="43.5">
+    <row r="168" spans="1:49" ht="43.5">
       <c r="A168" s="10" t="s">
         <v>672</v>
       </c>
@@ -17650,7 +17790,7 @@
       <c r="AT168" s="79"/>
       <c r="AU168" s="82"/>
     </row>
-    <row r="169" spans="1:47" ht="29">
+    <row r="169" spans="1:49" ht="29">
       <c r="A169" s="10" t="s">
         <v>672</v>
       </c>
@@ -17721,7 +17861,7 @@
       <c r="AT169" s="79"/>
       <c r="AU169" s="82"/>
     </row>
-    <row r="170" spans="1:47" ht="14.5">
+    <row r="170" spans="1:49" ht="14.5">
       <c r="A170" s="10" t="s">
         <v>672</v>
       </c>
@@ -17812,7 +17952,7 @@
       <c r="AT170" s="79"/>
       <c r="AU170" s="82"/>
     </row>
-    <row r="171" spans="1:47" ht="14.5">
+    <row r="171" spans="1:49" ht="14.5">
       <c r="A171" s="10" t="s">
         <v>672</v>
       </c>
@@ -17903,7 +18043,7 @@
       <c r="AT171" s="79"/>
       <c r="AU171" s="82"/>
     </row>
-    <row r="172" spans="1:47" ht="29">
+    <row r="172" spans="1:49" ht="29">
       <c r="A172" s="10" t="s">
         <v>672</v>
       </c>
@@ -17994,7 +18134,7 @@
       <c r="AT172" s="79"/>
       <c r="AU172" s="82"/>
     </row>
-    <row r="173" spans="1:47" ht="29">
+    <row r="173" spans="1:49" ht="29">
       <c r="A173" s="10" t="s">
         <v>672</v>
       </c>
@@ -18077,7 +18217,7 @@
       <c r="AT173" s="79"/>
       <c r="AU173" s="82"/>
     </row>
-    <row r="174" spans="1:47" ht="29">
+    <row r="174" spans="1:49" ht="29">
       <c r="A174" s="10" t="s">
         <v>672</v>
       </c>
@@ -18148,7 +18288,7 @@
       <c r="AT174" s="79"/>
       <c r="AU174" s="82"/>
     </row>
-    <row r="175" spans="1:47" ht="29">
+    <row r="175" spans="1:49" ht="29">
       <c r="A175" s="10" t="s">
         <v>672</v>
       </c>
@@ -18230,7 +18370,7 @@
       <c r="AT175" s="79"/>
       <c r="AU175" s="82"/>
     </row>
-    <row r="176" spans="1:47" ht="29">
+    <row r="176" spans="1:49" ht="29">
       <c r="A176" s="10" t="s">
         <v>672</v>
       </c>
@@ -19469,7 +19609,7 @@
       <c r="AT192" s="79"/>
       <c r="AU192" s="82"/>
     </row>
-    <row r="193" spans="1:47" ht="14.5">
+    <row r="193" spans="1:49" ht="14.5">
       <c r="A193" s="10" t="s">
         <v>672</v>
       </c>
@@ -19540,7 +19680,7 @@
       <c r="AT193" s="79"/>
       <c r="AU193" s="82"/>
     </row>
-    <row r="194" spans="1:47" ht="43.5">
+    <row r="194" spans="1:49" ht="43.5">
       <c r="A194" s="10" t="s">
         <v>672</v>
       </c>
@@ -19617,7 +19757,7 @@
       <c r="AT194" s="79"/>
       <c r="AU194" s="82"/>
     </row>
-    <row r="195" spans="1:47" ht="43.5">
+    <row r="195" spans="1:49" ht="43.5">
       <c r="A195" s="10" t="s">
         <v>672</v>
       </c>
@@ -19698,7 +19838,7 @@
       <c r="AT195" s="79"/>
       <c r="AU195" s="82"/>
     </row>
-    <row r="196" spans="1:47" ht="14.5">
+    <row r="196" spans="1:49" ht="14.5">
       <c r="A196" s="10" t="s">
         <v>672</v>
       </c>
@@ -19761,7 +19901,7 @@
       <c r="AT196" s="79"/>
       <c r="AU196" s="82"/>
     </row>
-    <row r="197" spans="1:47" ht="43.5">
+    <row r="197" spans="1:49" ht="43.5">
       <c r="A197" s="10" t="s">
         <v>672</v>
       </c>
@@ -19828,7 +19968,7 @@
       <c r="AT197" s="79"/>
       <c r="AU197" s="82"/>
     </row>
-    <row r="198" spans="1:47" ht="130.5">
+    <row r="198" spans="1:49" ht="145">
       <c r="A198" s="10" t="s">
         <v>672</v>
       </c>
@@ -19914,8 +20054,14 @@
       <c r="AS198" s="9"/>
       <c r="AT198" s="79"/>
       <c r="AU198" s="82"/>
-    </row>
-    <row r="199" spans="1:47" ht="43.5">
+      <c r="AV198" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW198" s="69" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="199" spans="1:49" ht="43.5">
       <c r="A199" s="10" t="s">
         <v>672</v>
       </c>
@@ -19997,8 +20143,9 @@
       <c r="AS199" s="9"/>
       <c r="AT199" s="79"/>
       <c r="AU199" s="82"/>
-    </row>
-    <row r="200" spans="1:47" ht="14.5">
+      <c r="AW199" s="69"/>
+    </row>
+    <row r="200" spans="1:49" ht="14.5">
       <c r="A200" s="10" t="s">
         <v>672</v>
       </c>
@@ -20065,7 +20212,7 @@
       <c r="AT200" s="79"/>
       <c r="AU200" s="82"/>
     </row>
-    <row r="201" spans="1:47" ht="43.5">
+    <row r="201" spans="1:49" ht="43.5">
       <c r="A201" s="10" t="s">
         <v>672</v>
       </c>
@@ -20147,8 +20294,14 @@
       <c r="AS201" s="9"/>
       <c r="AT201" s="79"/>
       <c r="AU201" s="82"/>
-    </row>
-    <row r="202" spans="1:47" ht="130.5">
+      <c r="AV201" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AW201" s="69" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="202" spans="1:49" ht="130.5">
       <c r="A202" s="10" t="s">
         <v>672</v>
       </c>
@@ -20226,8 +20379,14 @@
       <c r="AS202" s="9"/>
       <c r="AT202" s="79"/>
       <c r="AU202" s="82"/>
-    </row>
-    <row r="203" spans="1:47" ht="29">
+      <c r="AV202" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW202" s="77" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="203" spans="1:49" ht="29">
       <c r="A203" s="10" t="s">
         <v>672</v>
       </c>
@@ -20298,7 +20457,7 @@
       <c r="AT203" s="79"/>
       <c r="AU203" s="82"/>
     </row>
-    <row r="204" spans="1:47" ht="377">
+    <row r="204" spans="1:49" ht="377">
       <c r="A204" s="10" t="s">
         <v>672</v>
       </c>
@@ -20385,7 +20544,7 @@
       <c r="AT204" s="79"/>
       <c r="AU204" s="82"/>
     </row>
-    <row r="205" spans="1:47" ht="391.5">
+    <row r="205" spans="1:49" ht="391.5">
       <c r="A205" s="10" t="s">
         <v>672</v>
       </c>
@@ -20472,7 +20631,7 @@
       <c r="AT205" s="79"/>
       <c r="AU205" s="82"/>
     </row>
-    <row r="206" spans="1:47" ht="14.5">
+    <row r="206" spans="1:49" ht="14.5">
       <c r="A206" s="10" t="s">
         <v>672</v>
       </c>
@@ -20529,7 +20688,7 @@
       <c r="AT206" s="79"/>
       <c r="AU206" s="82"/>
     </row>
-    <row r="207" spans="1:47" ht="29">
+    <row r="207" spans="1:49" ht="38.5">
       <c r="A207" s="10" t="s">
         <v>672</v>
       </c>
@@ -20589,8 +20748,14 @@
       <c r="AS207" s="9"/>
       <c r="AT207" s="79"/>
       <c r="AU207" s="82"/>
-    </row>
-    <row r="208" spans="1:47" ht="29">
+      <c r="AV207" s="69" t="s">
+        <v>807</v>
+      </c>
+      <c r="AW207" s="89" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="208" spans="1:49" ht="38.5">
       <c r="A208" s="10" t="s">
         <v>672</v>
       </c>
@@ -20650,6 +20815,12 @@
       <c r="AS208" s="37"/>
       <c r="AT208" s="62"/>
       <c r="AU208" s="83"/>
+      <c r="AV208" s="69" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AW208" s="89" t="s">
+        <v>1092</v>
+      </c>
     </row>
     <row r="209" spans="1:47" ht="14.5">
       <c r="A209" s="33" t="s">
@@ -63653,8 +63824,9 @@
     <hyperlink ref="AC221" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="AS12" r:id="rId16" xr:uid="{119AA4A3-C354-4217-9961-39DD8D22FB3D}"/>
     <hyperlink ref="AU12" r:id="rId17" xr:uid="{5089569D-E038-4B81-AB71-AFF709AA618E}"/>
+    <hyperlink ref="AW126" r:id="rId18" xr:uid="{270161FA-D3AF-428D-897A-B60A71D0B1EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>